--- a/英語名言.xlsx
+++ b/英語名言.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nishidetadashi/Desktop/english-learning-portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAE2508-3AE1-A44D-AE74-C2174885FAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA94146-DE7E-6C49-938C-7BEAB829AD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18680" yWindow="880" windowWidth="17320" windowHeight="22600" xr2:uid="{C13B1331-7DAE-814C-BCB3-2047F8D365AC}"/>
+    <workbookView xWindow="28200" yWindow="29580" windowWidth="18000" windowHeight="22600" xr2:uid="{C13B1331-7DAE-814C-BCB3-2047F8D365AC}"/>
   </bookViews>
   <sheets>
     <sheet name="quotes" sheetId="1" r:id="rId1"/>
@@ -4625,21 +4625,6 @@
     <t>【文法：前置詞 with の起点】begins with one step（一歩から始まる）。【語彙・普遍の真理】老子の言葉「千里の道も一歩から」。a thousand miles（果てしなく遠い道のり）という壮大な旅（journey）も、すべては今目の前にある「たった一歩（one step）」を踏み出すことからしか始まらない。365日の学びの最後を飾る、行動への普遍的なエールです。</t>
   </si>
   <si>
-    <t>【文法：SVCと状態継続の動詞】stayはbe動詞と同じく「S=C」の関係を作りますが、「その状態にとどまる」という強い継続の意志が含まれます。【語彙・ニュアンス】hungryは「空腹な」から転じて「（知識や成功に）飢えている、貪欲な」という意味。foolishは「愚かな」ですが、ここでは「世間の常識や既成概念に縛られない純粋さ」を肯定的に表現しています。短い命令文の反復が、強烈なリズムと説得力を生んでいます。</t>
-  </si>
-  <si>
-    <t>【文法：比較級】「A is more [形容詞] than B」。importantは音節が多いため、-erではなくmoreを用います。【語彙・対比の構文】imagination（image「心に描く」+ ation「こと」）と knowledge（know「知る」+ ledge「状態」）という2つの抽象名詞の対比。確定した過去〜現在の枠組みである「知識」よりも、未来を創り出す「想像力」を、is（存在する）という強い断定のbe動詞で際立たせています。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の形容詞的用法と名詞的用法】The wayを後ろから「to get started（始めるための）」が修飾。isの後の「to quit...and begin...」は補語(C)となる名詞的用法です。【語彙・語法】quit（やめる）は後ろに動名詞(-ing)しか取れない動詞。beginはto不定詞も取れますが、ここでは talking と doing を「-ing」で揃えることで、視覚的・聴覚的なリズム（対句表現）を美しく整えています。「get started」は受動態の形を取ることで「自らを始動させる」というニュアンスを含みます。</t>
-  </si>
-  <si>
-    <t>【文法：SVCと時を表す接続詞】It seems impossibleで「〜のように見える（主観的な推測）」。untilは「〜するまでずっと」という継続を表す接続詞。【語彙・受動態】impossibleは in-(否定) + possible(可能な)。it's done の it は前述の「不可能に思えること」を指し、is doneは受動態で「成し遂げられる（客観的な事実）」状態を表します。seem（主観）と is done（客観）の対比が、諦めないことの重要性を際立たせています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の目的格】changeを先行詞とし、that以下が後ろから修飾しています。see（見る）の目的語(O)が欠けており、それが先行詞のchangeです。【語彙・名詞の選択】単に「Change（変われ）」という動詞を使うのではなく、「Be the change（変化そのものになれ）」と名詞を用いることで、「あなた自身の存在が世界の変革の象徴になれ」という非常にスケールの大きい、哲学的で力強いメッセージになっています。</t>
-  </si>
-  <si>
     <t>【文法：基本の第3文型(SVO)】主語(I) + 動詞(have) + 目的語(a dream)という、英語の最も基本かつ力強い文型です。【語彙・冠詞の凄み】注目すべきは不定冠詞の「a」です。dreams（複数の夢）や the dream（特定の夢）ではなく、「a dream（ある一つの明確な夢）」と単数形にすることで、後に語られる具体的な「たった一つの揺るぎない理想」へと聴衆の意識を一気にフォーカスさせる修辞的効果があります。</t>
   </si>
   <si>
@@ -4923,6 +4908,66 @@
   </si>
   <si>
     <t>【文法：関係副詞 Where を使った副詞節】Where S V で「SがVする場所には」。there is 構文を2つ重ねています。【語彙・ニュアンス】ガンジーの言葉。愛が存在する場所（条件）にのみ、真の生命や人生（life）が存在する。愛と生命を不可分のものとして結びつけた、シンプルで美しい哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・stay：[動] 〜のままでいる
+・hungry：[形] 飢えた、貪欲な（ここでは知識や成功への意欲）
+・foolish：[形] 愚かな（ここでは常識にとらわれないこと）
+【文法解説】
+・命令文：動詞の原形（Stay）から始まり、強いメッセージ性を持っています。
+・第2文型(SVC)：Stay（V）+ hungry/foolish（C）。「be動詞」と同じS=Cの関係ですが、「stay」を使うことで「その状態を維持し続けろ」という強い継続の意志が強調されています。
+【背景・ニュアンス】
+スティーブ・ジョブズが2005年のスタンフォード大学卒業式辞の結びで語った有名な言葉。元々は雑誌『全地球カタログ』最終号の裏表紙のメッセージです。現状に満足せず（hungry）、他人の目や常識を気にして縮こまることなく（foolish）、常に新しいことに挑戦し続けよという強烈なエールです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【単語解説】
+・imagination：[名] 想像力
+・important：[形] 重要な
+・knowledge：[名] 知識
+【文法解説】
+・比較級：A is more [形容詞] than B（AはBよりも〜だ）の構文。important は音節が多いため、-er ではなく more を使います。
+・抽象名詞の対比：imagination（心に描くこと）と knowledge（知っている状態）という2つの抽象名詞を対比させています。
+【背景・ニュアンス】
+1929年のインタビューでのアインシュタインの発言。「知識は現在分かっていることに限られるが、想像力は世界を包み込み、進歩を生み出す」と語りました。すでに確定した過去〜現在の枠組みである「知識」よりも、ゼロから未来を創り出す「想像力」の価値を高く評価した深い言葉です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【単語解説】
+・way：[名] 方法、道
+・quit：[動] やめる
+・begin：[動] 始める
+【文法解説】
+・不定詞の用法：The way を to get started（始めるための）が後ろから修飾（形容詞的用法）。is の後は to quit... and begin...（〜をやめて･･･し始めること）となり、補語(C)として機能しています（名詞的用法）。
+・動名詞：quit は後ろに動名詞(-ing)しか取れない動詞です。talking と doing で韻を踏むように形を揃えています。
+【背景・ニュアンス】
+ディズニーリゾートの構想など、数々の夢を現実にしてきたウォルト・ディズニーの行動哲学。「あれこれと口で語るよりも、まず手を動かせ」という、夢を実現するための極めて実務的でストレートなアドバイスです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【単語解説】
+・seem：[動] 〜のように見える、思える
+・impossible：[形] 不可能な
+・until：[接] 〜するまで（ずっと）
+【文法解説】
+・第2文型(SVC)：It seems impossible で「（主観的に）不可能のように思える」。
+・受動態：until it's done の is done は「（客観的な事実として）成し遂げられる」という受動態。seem（主観）と is done（客観）が美しい対比になっています。
+【背景・ニュアンス】
+27年間もの投獄生活を経て、南アフリカの反アパルトヘイト運動を勝利に導いたネルソン・マンデラの言葉。どんなに絶望的で高く見える壁でも、やり遂げてしまえばそれは「当たり前の現実」になる。途中で決して諦めないことの重要性を、自身の壮絶な経験から説いています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【単語解説】
+・change：[名] 変化、変革
+・wish：[動] 願う
+・world：[名] 世界
+【文法解説】
+・関係代名詞（目的格）：that が先行詞 the change を後ろから修飾しています。「wish to see」の目的語(O)が欠けており、それが the change に該当します。
+・名詞の選択：動詞の Change（変われ）ではなく Be the change（変化そのものになれ）と名詞を使うことで、スケールの大きな表現になっています。
+【背景・ニュアンス】
+ガンジーの思想を要約した言葉として広く知られています。世界が変わるのを待ったり、他人に文句を言ったりするのではなく、まず「自分自身の行動やあり方」を変えること。あなた自身の存在が世界の変革の象徴になれという、自己変革こそが社会変革の第一歩であるという深い哲学です。</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -5933,7 +5978,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="105">
+    <row r="2" spans="1:7" ht="336">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5953,10 +5998,10 @@
         <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="105">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="336">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5976,10 +6021,10 @@
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1529</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="126">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="336">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5998,11 +6043,11 @@
       <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="105">
+      <c r="G4" s="2" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="315">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6021,11 +6066,11 @@
       <c r="F5" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>1531</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="105">
+      <c r="G5" s="2" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="336">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6044,8 +6089,8 @@
       <c r="F6" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>1532</v>
+      <c r="G6" s="2" t="s">
+        <v>1627</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="105">
@@ -6068,7 +6113,7 @@
         <v>9</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="126">
@@ -6091,7 +6136,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="126">
@@ -6114,7 +6159,7 @@
         <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="126">
@@ -6137,7 +6182,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="105">
@@ -6160,7 +6205,7 @@
         <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="84">
@@ -6183,7 +6228,7 @@
         <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="105">
@@ -6206,7 +6251,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="105">
@@ -6229,7 +6274,7 @@
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="105">
@@ -6252,7 +6297,7 @@
         <v>9</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="84">
@@ -6275,7 +6320,7 @@
         <v>9</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="105">
@@ -6298,7 +6343,7 @@
         <v>9</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="105">
@@ -6321,7 +6366,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="105">
@@ -6344,7 +6389,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="105">
@@ -6367,7 +6412,7 @@
         <v>9</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="105">
@@ -6390,7 +6435,7 @@
         <v>9</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="105">
@@ -6413,7 +6458,7 @@
         <v>9</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="105">
@@ -6436,7 +6481,7 @@
         <v>9</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="84">
@@ -6459,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="84">
@@ -6482,7 +6527,7 @@
         <v>9</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="84">
@@ -6505,7 +6550,7 @@
         <v>9</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="84">
@@ -6528,7 +6573,7 @@
         <v>9</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="84">
@@ -6551,7 +6596,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="84">
@@ -6574,7 +6619,7 @@
         <v>9</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="84">
@@ -6597,7 +6642,7 @@
         <v>9</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="105">
@@ -6620,7 +6665,7 @@
         <v>9</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="84">
@@ -6643,7 +6688,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="84">
@@ -6666,7 +6711,7 @@
         <v>9</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="84">
@@ -6689,7 +6734,7 @@
         <v>9</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="105">
@@ -6712,7 +6757,7 @@
         <v>9</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="84">
@@ -6735,7 +6780,7 @@
         <v>9</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="84">
@@ -6758,7 +6803,7 @@
         <v>9</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="84">
@@ -6781,7 +6826,7 @@
         <v>9</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="105">
@@ -6804,7 +6849,7 @@
         <v>9</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="84">
@@ -6827,7 +6872,7 @@
         <v>9</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="105">
@@ -6850,7 +6895,7 @@
         <v>9</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="84">
@@ -6873,7 +6918,7 @@
         <v>9</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="84">
@@ -6896,7 +6941,7 @@
         <v>9</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="105">
@@ -6919,7 +6964,7 @@
         <v>9</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="105">
@@ -6942,7 +6987,7 @@
         <v>9</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="84">
@@ -6965,7 +7010,7 @@
         <v>9</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="84">
@@ -6988,7 +7033,7 @@
         <v>9</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="105">
@@ -7011,7 +7056,7 @@
         <v>9</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="105">
@@ -7034,7 +7079,7 @@
         <v>9</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="105">
@@ -7057,7 +7102,7 @@
         <v>9</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="84">
@@ -7080,7 +7125,7 @@
         <v>9</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="105">
@@ -7103,7 +7148,7 @@
         <v>9</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="105">
@@ -7126,7 +7171,7 @@
         <v>9</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="105">
@@ -7149,7 +7194,7 @@
         <v>9</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="84">
@@ -7172,7 +7217,7 @@
         <v>9</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="84">
@@ -7195,7 +7240,7 @@
         <v>9</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="84">
@@ -7218,7 +7263,7 @@
         <v>9</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="105">
@@ -7241,7 +7286,7 @@
         <v>9</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="84">
@@ -7264,7 +7309,7 @@
         <v>9</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="84">
@@ -7287,7 +7332,7 @@
         <v>9</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="84">
@@ -7310,7 +7355,7 @@
         <v>9</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="84">
@@ -7333,7 +7378,7 @@
         <v>9</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="84">
@@ -7356,7 +7401,7 @@
         <v>9</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="84">
@@ -7379,7 +7424,7 @@
         <v>9</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="105">
@@ -7402,7 +7447,7 @@
         <v>9</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="84">
@@ -7425,7 +7470,7 @@
         <v>9</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="84">
@@ -7448,7 +7493,7 @@
         <v>9</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="84">
@@ -7471,7 +7516,7 @@
         <v>9</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="84">
@@ -7494,7 +7539,7 @@
         <v>9</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="84">
@@ -7517,7 +7562,7 @@
         <v>9</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="84">
@@ -7540,7 +7585,7 @@
         <v>9</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="84">
@@ -7563,7 +7608,7 @@
         <v>9</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="84">
@@ -7586,7 +7631,7 @@
         <v>9</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="84">
@@ -7609,7 +7654,7 @@
         <v>9</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="84">
@@ -7632,7 +7677,7 @@
         <v>9</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="84">
@@ -7655,7 +7700,7 @@
         <v>9</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="84">
@@ -7678,7 +7723,7 @@
         <v>9</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="84">
@@ -7701,7 +7746,7 @@
         <v>9</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="84">
@@ -7724,7 +7769,7 @@
         <v>9</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="84">
@@ -7747,7 +7792,7 @@
         <v>9</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="105">
@@ -7770,7 +7815,7 @@
         <v>9</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="105">
@@ -7793,7 +7838,7 @@
         <v>9</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="84">
@@ -7816,7 +7861,7 @@
         <v>9</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="84">
@@ -7839,7 +7884,7 @@
         <v>9</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="105">
@@ -7862,7 +7907,7 @@
         <v>9</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="84">
@@ -7885,7 +7930,7 @@
         <v>9</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="63">
@@ -7908,7 +7953,7 @@
         <v>9</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="84">
@@ -7931,7 +7976,7 @@
         <v>9</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="84">
@@ -7954,7 +7999,7 @@
         <v>9</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="84">
@@ -7977,7 +8022,7 @@
         <v>9</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="84">
@@ -8000,7 +8045,7 @@
         <v>9</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="84">
@@ -8023,7 +8068,7 @@
         <v>9</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="84">
@@ -8046,7 +8091,7 @@
         <v>9</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="84">
@@ -8069,7 +8114,7 @@
         <v>9</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="105">
@@ -8092,7 +8137,7 @@
         <v>9</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="84">
@@ -8115,7 +8160,7 @@
         <v>9</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="84">
@@ -8138,7 +8183,7 @@
         <v>9</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="84">
@@ -8161,7 +8206,7 @@
         <v>9</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="84">
@@ -8184,7 +8229,7 @@
         <v>9</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="84">
@@ -8207,7 +8252,7 @@
         <v>9</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="84">
@@ -8230,7 +8275,7 @@
         <v>9</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="84">

--- a/英語名言.xlsx
+++ b/英語名言.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nishidetadashi/Desktop/english-learning-portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA94146-DE7E-6C49-938C-7BEAB829AD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BE50E5-0C80-F846-A2F9-9E9A070FC3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28200" yWindow="29580" windowWidth="18000" windowHeight="22600" xr2:uid="{C13B1331-7DAE-814C-BCB3-2047F8D365AC}"/>
   </bookViews>

--- a/英語名言.xlsx
+++ b/英語名言.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nishidetadashi/Desktop/english-learning-portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BE50E5-0C80-F846-A2F9-9E9A070FC3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EEBE95-C3A5-D645-B514-327CFCFA3E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28200" yWindow="29580" windowWidth="18000" windowHeight="22600" xr2:uid="{C13B1331-7DAE-814C-BCB3-2047F8D365AC}"/>
+    <workbookView xWindow="18560" yWindow="780" windowWidth="17440" windowHeight="22600" xr2:uid="{C13B1331-7DAE-814C-BCB3-2047F8D365AC}"/>
   </bookViews>
   <sheets>
     <sheet name="quotes" sheetId="1" r:id="rId1"/>
@@ -3830,516 +3830,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【文法：動名詞と名詞節の省略】in knowing の後に that が省略されています。「知らないということを知っていることの中に」。【語彙・逆説】wisdom（知恵）の究極の形が nothing（無）を知ることであるという、ソクラテスの「無知の知」を簡潔な英語で表したパラドックスです。</t>
-  </si>
-  <si>
-    <t>【文法：句動詞 depend upon】upon は on よりもやや硬く強調された表現。「〜に依存する、〜次第である」。【語彙・自律性】ourselves（私たち自身）という再帰代名詞を使い、幸福という状態が外的な要因ではなく、自分の内面でのみ決定されるというアリストテレスの哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の名詞的用法と最上級】To live（生きること）が主語、the rarest（最も稀な）が補語。【語彙・対比】live（意思を持って生きる）と exist（ただ物理的に存在する）。大半の人間は主体的に生きておらず、ただそこにいるだけ（that is all）だと切り捨てるオスカー・ワイルドの鋭い皮肉です。</t>
-  </si>
-  <si>
-    <t>【文法：make A of B】「BからAを作る（変える）」。【語彙・対句と倒置】heaven of hell（地獄から天国を）と a hell of heaven（天国から地獄を）の美しい対句。人間の心（mind）は独立した世界であり、解釈次第で現実をどうとでも反転させられるというミルトンの力強い一節です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what の名詞節】What we achieve inwardly（私たちが内面的に達成するもの）が全体の主語。【語彙・対比】inwardly（内面的に）と outer（外的な）。内側の精神的変化という原因が、目に見える外側の現実を変えるという、心理学的な真理を突いた構造です。</t>
-  </si>
-  <si>
-    <t>【文法：等位接続詞 but による対比】完全な文を but で繋ぎ、対照的な状況を示しています。【語彙・副詞の選択】slowly（ゆっくりと）というペースの遅さを認めつつも、backward（後ろへ）は never（絶対に〜ない）と強く否定。リンカーンの不屈の前進を、歩行の方向で表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：Not A but B と前置詞 in の反復】lies in（〜にある）。「AにあるのではなくBにある」。【語彙・動名詞】falling（転ぶこと）と rising（起き上がること）。every time（〜するたびに）を添え、一度の完璧さよりも何度でも復活する回復力（レジリエンス）を栄光と定義しています。</t>
-  </si>
-  <si>
-    <t>【文法：条件節と don't have to】「もし真実を言えば、何も覚えておく必要はない」。【語彙・ユーモア】嘘をつくと辻褄を合わせるために記憶力が必要だが、真実なら思い出す必要すらない。マーク・トウェインらしい、道徳を実用性の観点からユーモラスに語った名言です。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞 with による修飾】with a deadline（締め切りを伴った）が a dream を後ろから修飾しています。【語彙・頭韻法】dream と deadline で「d」の音を揃える頭韻が使われています。曖昧な「夢」も、時間的制約（deadline）を設けた瞬間に「目標」に変わるという鮮やかな定義です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 that と what】He that... は He who... と同じく「〜する人は」。what he will の will は名詞で「意志、望み」。【語彙・反復】can have を2回繰り返すことで、「忍耐を持てる者は、望むものすべてを持てる」という因果関係をリズミカルに強調したフランクリンの言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：The 比較級, the 比較級】「〜すればするほど、ますます･･･」。コロン（:）で前半の理由を説明しています。【語彙・メタファー】timber（木材）。ease（安楽）の中では良い木は育たない。強い風（困難）が強い木（人間）を育てるという、自然界の法則を人生の教訓に重ねた美しい脚韻（ease/trees）です。</t>
-  </si>
-  <si>
-    <t>【文法：条件節 If と命令文】「もし機会がノックしないなら、ドアを作れ」。【語彙・擬人化とメタファー】opportunity（機会）がやってきてノックするという擬人化。それが来ないなら、自ら受け入れ口（door）を構築せよという、待つことを拒否する圧倒的な能動性を示しています。</t>
-  </si>
-  <si>
-    <t>【文法：否定代名詞 Nothing と 接続詞 unless】「あなたが行動しない限り、何もうまくいかない」。【語彙・代動詞】最後の do は work（機能する、働く）の反復を避ける代動詞です。道具や環境がどれほど完璧でも、人間自身の行動（do）がすべての起動スイッチであるという厳しい事実です。</t>
-  </si>
-  <si>
-    <t>【文法：等位接続詞 but と代動詞 do】前半の last（続く）を、後半では do で受けています。【語彙・多義語の反復】Tough times（困難な時代）と tough people（頑強な人々）。同じ tough という単語を使いながら、時間の儚さと人間の精神のしぶとさを対比させた見事な言葉遊びです。</t>
-  </si>
-  <si>
-    <t>【文法：There is 構文の否定と名詞の並列】no secrets（秘密など一つもない）。It は success を指し、3つの名詞句を等位に並べています。【語彙・現実主義】魔法のような「秘密」を否定し、準備、勤勉、失敗からの学習という泥臭い「結果（result）」こそが成功の正体だとパウエル長官が断定しています。</t>
-  </si>
-  <si>
-    <t>【文法：第2文型(SVC)】A ＝ B。不要なものを削ぎ落とした最も短い文型です。【語彙・逆説的なSとC】Simplicity（単純さ）と sophistication（洗練、複雑さ）。一見相反する2つの概念を結びつけ、無駄をなくした究極の形こそが最も洗練されているという、ダ・ヴィンチの深い美学です。</t>
-  </si>
-  <si>
-    <t>【文法：強調構文 It is...that / 比較級の強調】far more than（〜よりもはるかに）で choices（選択）を abilities（能力）よりも上位に置いています。【語彙・本質】『ハリー・ポッター』のダンブルドアのセリフ。持って生まれた「能力」ではなく、困難な時に何を選ぶかという「選択」こそが人間の真価（what we truly are）を示すという名言です。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞の主語と補語】getting ahead（前進すること）と getting started（始めること）。【語彙・韻とリズム】同じ get の動名詞を使い、secret（秘密）という仰々しい主語に対して、started（ただ始めるだけ）という拍子抜けするほどシンプルな結論をぶつけるマーク・トウェインのユーモアです。</t>
-  </si>
-  <si>
-    <t>【文法：過去分詞の名詞的用法と比較級】Done（完了したこと）と perfect（完璧であること）を比較しています。【語彙・実践主義】完璧主義に陥って何も世に出さないよりも、荒削りでも「終わらせる（Done）」ことの方が価値がある。シリコンバレーなどで好まれる、スピードと実行力を尊ぶスローガンです。</t>
-  </si>
-  <si>
-    <t>【文法：比較級による主語の強調】Doubt（疑念）が、failure（失敗）よりも多くを殺す（kills）。【語彙・擬人化と時制】ever will は will kill の省略で未来への可能性を含みます。挑戦して失敗することよりも、挑戦する前に「自分を疑うこと」の方が夢を破壊するという残酷な真理です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の副詞的用法による倒置的な対比】to start（始めるために）と to be great（偉大になるために）の位置を入れ替えています。【語彙・論理の逆転】偉大さを開始の「条件」にするのではなく、開始を偉大さへの「条件」に反転させる。完璧なタイミングを待つ人の背中を押すジグ・ジグラーの言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：条件節 If と助動詞 can の反復】「もし〜できるなら、･･･できる」。【語彙・シンプルさ】dream（夢見る、想像する）と do（実行する）。ウォルト・ディズニーの言葉として有名ですが、人間の想像力が及ぶ範囲のものはすべて現実化する力を持っているという、圧倒的な全能感を表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の省略】Everything と you の間に that が省略されています。「あなたが想像できるすべてのこと」。【語彙・断定】is real（現実である）。ピカソの言葉。空想や想像（imagine）を単なる幻とせず、それらもまた一つの「現実（real）」であると言い切る芸術家の視点です。</t>
-  </si>
-  <si>
-    <t>【文法：名詞の並列と同格のダッシュ】ダッシュ(—)は前の内容を補足・訂正する役割を果たします。【語彙・再定義】勇気を「恐怖の不在（absence）」ではなく、恐怖に対する「抵抗（resistance）」と「支配（mastery）」に再定義したマーク・トウェインの言葉。恐れを感じること自体は否定していません。</t>
-  </si>
-  <si>
-    <t>【文法：Keep O on〜 の並列】後半は (keep) your feet on the ground と動詞が省略されています。【語彙・対比とバランス】stars（星＝高い理想）と ground（地面＝現実）。ルーズベルト大統領の言葉で、理想を高く持ちながらも、行動は現実的で地に足のついたものであれという、完璧なバランス感覚を説いています。</t>
-  </si>
-  <si>
-    <t>【文法：The 比較級, the 比較級】「〜であればあるほど、ますます･･･」。動詞（is）が省略された簡潔な形です。【語彙・比例関係】conflict（闘争、困難）と triumph（大勝利）。苦難が大きければ大きいほど、それを乗り越えた時の栄光もまた大きくなるという、トマス・ペインの力強い鼓舞です。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞 by + 動名詞 と 進行形】By -ing（〜することによって）。【語彙・言葉遊び(交錯配列法)】fail to prepare（準備を怠る）と prepare to fail（失敗の準備をする）。フランクリンの言葉。意図的であれ無意識であれ、準備不足はすでに「失敗への能動的な準備」なのだという鋭い戒めです。</t>
-  </si>
-  <si>
-    <t>【文法：他動詞と自動詞の使い分け / 使役動詞 make】前半の count は「（日数を）数える」という他動詞。後半の count は「重要である、価値を持つ」という自動詞です。【語彙・意識の転換】モハメド・アリの言葉。受動的に時間が過ぎるのを数えるのではなく、一日一日を自らの手で「意味のあるものにさせよ（make...count）」という命令です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what の主語】What hurts you（あなたを傷つけるもの）が主語。【語彙・逆説のメタファー】hurts（傷つける）と blesses（祝福する）。ルーミー（詩人）の言葉で、苦難こそが魂を成長させる恵みであり、暗闇（Darkness）こそが光の価値を教えるロウソク（candle）であるという神秘的な逆説です。</t>
-  </si>
-  <si>
-    <t>【文法：受動態と Not A but B / 疑問詞 how】is defined by〜（〜によって定義される）。how they can recover は「いかに回復できるか」という名詞節。【語彙・真の価値】セリーナ・ウィリアムズの言葉。勝利（wins）の数ではなく、どん底（fall）からの「回復力（recover）」にこそ王者の真価があるという再定義です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の名詞的用法】to do（〜すること）が補語。【語彙・副詞による強調と対比】the common thing（平凡で当たり前のこと）を uncommonly well（非凡なほどに見事に）やる。ロックフェラーの言葉。特別なことをする必要はなく、基礎や日常の基準を異常なレベルまで引き上げよという成功哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：否定語句(Only)の文頭移動による倒置】Only in the darkness（暗闇の中でのみ）という限定句を前に出したため、you can が can you と疑問文の語順（倒置）になっています。【語彙・希望のメタファー】キング牧師の言葉。絶望や困難（darkness）の最中にあってこそ、真の希望や光（stars）を見出すことができるという詩的な表現です。</t>
-  </si>
-  <si>
-    <t>【文法：受動態と過去分詞の後置修飾】are done（なされる）。brought together（一つにまとめられた）という過去分詞が a series of small things を修飾しています。【語彙・集積の力】ゴッホの言葉。偉業（Great things）は突発的に生まれるのではなく、小さなこと（small things）の連続的な集積によってのみ達成されるという事実です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の省略】person と you の間に that/who が2箇所省略されています。【語彙・運命と意思】destined to become（運命づけられている）自分ではなく、decide to be（決断した）自分が本物である。運命論を否定し、人生の最終決定権は自らの意思（decide）にあることをエマーソンが宣言しています。</t>
-  </si>
-  <si>
-    <t>【文法：第5文型(SVOC)】Make O C で「OをCにせよ」。each day が目的語、your masterpiece が補語です。【語彙・芸術のメタファー】ジョン・ウッデンの言葉。一日一日を、ただの作業の繰り返しではなく、あなた自身の「最高傑作（masterpiece）」として丹念に仕上げるつもりで生きよという美しい命令文です。</t>
-  </si>
-  <si>
-    <t>【文法：No A, no B の省略構文】If there is no pressure, there will be no diamonds. の省略形です。【語彙・科学的メタファー】炭素が極度の「圧力（pressure）」を受けて初めて美しい「ダイヤモンド」に変わるという物理法則を、人間の成長におけるストレスや試練の必要性に例えた短い名言です。</t>
-  </si>
-  <si>
-    <t>【文法：無生物主語の否定文】「穏やかな海は、熟練の船乗りを作らない」。【語彙・苦難の肯定】アフリカの諺。calm（穏やかな、安楽な）状況では技術は磨かれない。skilled（熟練した）な人間になるためには、荒波（試練）という厳しい環境が不可欠であるという、成長への真理です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 those who と too...to 構文】those who は「〜する人々」。too busy to be looking for it は「忙しすぎてそれ（成功）を探す暇がない」。【語彙・アイロニー】ソローの言葉。成功ばかりを追い求める者の元へは来ず、目の前の仕事に無我夢中で没頭している者の元に自然とやって来るという逆説です。</t>
-  </si>
-  <si>
-    <t>【文法：否定副詞 never と前置詞 for】dreamed about（〜について夢見る）を never で全否定し、worked for（〜のために働く）を対置させています。【語彙・現実主義】エスティ・ローダーの言葉。成功をただ頭の中で「夢見る」のではなく、現実の「行動・労働（work）」によって掴み取ったという、強い実務家の誇りです。</t>
-  </si>
-  <si>
-    <t>【文法：条件節 If と過去形 took】take a long time（長い時間がかかる）の過去形。【語彙・矛盾語法(Oxymoron)】overnight success（一晩での成功＝突然のブレイク）という言葉の裏には、実は長い年月の積み重ね（a long time）が隠れている。ジョブズが世間の表面的な見方を戒めた言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：使役動詞 let と句動詞 take up】let O do（Oに〜させる）。take up は「（時間や空間を）占領する、使い果たす」。【語彙・時間の擬人化】過去（yesterday）が現在の貴重な時間（today）を侵食するのを許してはいけない。後悔や過去の栄光にとらわれることを戒める、ウィル・ロジャースの言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：比較級と使役動詞】more from A than from B（BからよりもAから多くを学ぶ）。let it stop you の it は failure です。【語彙・人格形成】build character（人格を形成する）。失敗は単なるミスではなく、人間の精神的な骨格（character）を鍛え上げる建築作業（build）であると肯定しています。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞の主語と前置詞 in + -ing】Setting goals（目標を設定すること）が主語。turning A into B（AをBに変える）。【語彙・抽象から具象へ】the invisible（目に見えないもの＝夢やアイデア）を the visible（目に見えるもの＝現実）へと変換する。アンソニー・ロビンズの、目標設定の実践的価値を説いた言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：自動詞と他動詞の明確な対比】happen（発生する＝自動詞）と create（創り出す＝他動詞）。【語彙・主体性】クリス・グロッサーの言葉。機会（Opportunities）は自然現象のように勝手に「起きる」ものではなく、自らの手で「創る」ものである。待つ姿勢を完全に否定し、人間の主体性を強調しています。</t>
-  </si>
-  <si>
-    <t>【文法：The 比較級, the 比較級】「一生懸命働けば働くほど、より多くの運を持つように思える」。【語彙・運の再定義】トマス・ジェファーソン（または類似の格言）。運（luck）は偶然の産物ではなく、努力（hard work）の量に比例して引き寄せられるものであるという、努力家のための心強い真理です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の名詞的用法と関係代名詞 what】to endeavor to be（〜になるよう努めること）。what you desire to appear は「あなたが（他人に）見られたいと望む姿」。【語彙・誠実さ】ソクラテスの言葉。良い評判（reputation）を得たければ、取り繕うのではなく、実際にその理想の人物像に「なる」努力（endeavor）をせよという本質論です。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 until】「〜するまでずっと（継続）」。【語彙・目標の引き上げ】idols（憧れの偶像）と rivals（対等に競い合う好敵手）。韻を踏みながら、最初は見上げるだけだった存在に肩を並べるレベルまで、圧倒的な努力（Work）を続けよという、非常に高いモチベーションを喚起する言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 till と by -ing】till は until と同じ。make it hot は第5文型（鉄を熱くする）。【語彙・諺の裏返し】「鉄は熱いうちに打て」という諺を逆手に取り、状況が整うのを待つ（wait）のではなく、自ら行動（striking）を起こすことで状況を理想の熱さ（hot）に変えろという、イェイツの能動的な名言です。</t>
-  </si>
-  <si>
-    <t>【文法：Some..., some..., others... の並列】「〜する人もいれば、･･･する人もいて、また別のことをする人もいる」。【語彙・行動の3段階】マイケル・ジョーダンの言葉。want（単なる欲求）、wish（仮定法的な願望）、そして make it happen（使役動詞を使った現実化）。結果を出すのは「自ら起こす（make）」人間だけだという厳しい事実です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what と使役的な動詞】get O started（Oを始めさせる）、keep O -ing（Oに続けさせる）。【語彙・役割分担】ジム・ローン（またはジム・ライアン）の言葉。モチベーションは最初の「点火装置」に過ぎず、実際に長距離を走らせる「エンジン」は毎日の習慣（Habit）であるという、行動心理学の核心です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の副詞的用法と助動詞must】To succeed（成功するために）が目的を表し、主節の must（〜しなければならない）で強い義務や必要性を強調しています。【語彙・ニュアンス】single-minded（ひたむきな、一つのことだけを考える）という形容詞が devotion（献身）を修飾し、目標達成には一点集中が不可欠であることを説いています。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞by + 動名詞の並列】by standing（立つこと）と staring（見つめること）が and で並列されています。【語彙・メタファー】タゴールの言葉。海を渡る（cross the sea ＝ 目標を達成する）には、ただ傍観している（staring at the water）だけでは不可能であり、具体的な行動が必要であるという美しい比喩です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の形容詞的用法と副詞句の追加】the opportunity（機会）を to begin again（再び始めるための）が後ろから修飾しています。【語彙・再定義】ヘンリー・フォードの言葉。Failure（失敗）を、単なる「より賢く（intelligently）やり直す機会」へと鮮やかにポジティブな概念に再定義しています。</t>
-  </si>
-  <si>
-    <t>【文法：助動詞の受動態】cannot be changed（変えられることはできない）。【語彙・対比と前置詞】The past（過去）と The future（未来）。is yet in your power の in は「（影響や力の）範囲内にある」。過去への後悔を断ち切り、まだコントロール可能な未来に焦点を当てる論理的な対比です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what を使った名詞節の対比】What comes easy（簡単に手に入るもの）と What lasts（長続きするもの）。【語彙・交錯配列法】easy と last の位置を反転させて繰り返すことで、「安易な成功は消えやすく、本物の成功は困難を伴う」という真理をリズミカルな格言に仕立てています。</t>
-  </si>
-  <si>
-    <t>【文法：進行形と動名詞】are going through（今まさに〜を通り抜けている）と keep going（行き続ける）。【語彙・ニュアンス】チャーチルの言葉。hell（地獄・苦難）の中にいるなら、そこで立ち止まる（stop）ことは地獄にとどまることを意味する。だからとにかく歩みを止めず抜け出せという切実な命令です。</t>
-  </si>
-  <si>
-    <t>【文法：過去を表す副詞 once】once は「かつて、以前は」。【語彙・ニュアンス】expert（達人）と beginner（初心者）の対比。どんなに才能があるように見える達人も、最初は何もできない初心者だったという歴史的事実を提示し、学習者の背中を強く押してくれる名言です。</t>
-  </si>
-  <si>
-    <t>【文法：when節の対比】when you're tired（疲れた時）と when you're done（終わった時）。【語彙・プロフェッショナリズム】感情や肉体の状態（tired）で行動を停止するのではなく、タスクの完了（done）という客観的な事実をもって停止せよという、自己規律とプロ意識を求める厳しい言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：仮定法過去完了】wish S had + 過去分詞（あの時〜していればよかったのにと思う）。【語彙・時間差の認識】A year from now（今から1年後）という未来の視点に立ち、そこから現在（today）を振り返ったときの後悔を想像させることで、今すぐ始めることの重要性を説得力を持って伝えています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what と 第2文型】We are what we do（私たちは、私たちがすること、そのものである）。【語彙・名詞の再定義】アリストテレスの言葉。Excellence（卓越性）は一回きりの輝かしい行為（act）ではなく、繰り返される習慣（habit）である。日々の継続こそが人間の本質を創るという哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：挿入句と A - not B - is C の構造】主語（Continuous effort）の後に、ダッシュで否定の要素（not strength or intelligence）を挿入しています。【語彙・メタファー】unlocking our potential（私たちの潜在能力を解き放つ）。成功の鍵（key）は、才能や知能ではなく、継続的な努力（Continuous effort）であるという希望の言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 unless】unless you do（あなたが働かない限り）。do は work の代動詞です。【語彙・擬人化】Dreams don't work（夢は自らは働かない）。夢という抽象的な概念を主語にし、夢を実現させるためには、持ち主である人間自身が労働（work）しなければならないという現実的な指摘です。</t>
-  </si>
-  <si>
-    <t>【文法：whether A or B の名詞節】「AかBかということ」。It is not A, it is B の構造です。【語彙・句動詞の対比】get knocked down（打ち倒される）と get up（起き上がる）。人生において倒れることは問題ではなく、その後に立ち上がるかどうかだけが重要であるという不屈の精神を表しています。</t>
-  </si>
-  <si>
-    <t>【文法：代動詞と擬人化】do what it does の it は the clock（時計）を指し、does は watch（見る）ではなく、時計の本来の動き（進み続けること）を指します。【語彙・ニュアンス】時計を気にして（watch）時間をやり過ごすのではなく、時計と同じようにただ黙々と前に進み続けろ（Keep going）という比喩です。</t>
-  </si>
-  <si>
-    <t>【文法：第2文型(SVC)】Every moment（すべての瞬間）＝ a fresh beginning（新鮮な始まり）。【語彙・現在への集中】過去の失敗や栄光にとらわれることなく、今訪れているこの瞬間を常に「新しいスタート」として捉える。心機一転を促す、シンプルで清々しい表現です。</t>
-  </si>
-  <si>
-    <t>【文法：命令文 + and】「〜しなさい、そうすれば･･･」。【語彙・パラドックス】孔子の言葉。愛する仕事（a job you love）を選べば、それはもはや労働や苦痛（work）ではなくなるため、一生「働く」必要がなくなるという、労働の概念を根底から覆す美しい逆説です。</t>
-  </si>
-  <si>
-    <t>【文法：相関接続詞 Either A or B】「AかBかのどちらかだ」。【語彙・主客の逆転】you run the day（あなたが一日を支配する）と the day runs you（一日があなたを支配する）。run は「経営する、管理する」。スケジュールに追われるのではなく、自らが主導権を握るべきだという時間管理の真髄です。</t>
-  </si>
-  <si>
-    <t>【文法：attribute A to B】「A（成功）はB（これ）のおかげだと考える」。コロン（:）以下で this の内容を説明しています。【語彙・強い否定】ナイチンゲールの言葉。never gave or took any excuse（言い訳を決してしなかったし、他人の言い訳も受け入れなかった）。妥協を許さない極めて厳しいプロの姿勢です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の省略】Everything (that) you need。あなたが必要とする全てのもの。【語彙・内省】already inside you（すでにあなたの中にある）。外の世界に答えや助けを求めるのではなく、自分自身の内なる可能性や強さに気づきなさいという、自己肯定とエンパワーメントのメッセージです。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞の補語】doing your best（最善を尽くすこと）。【語彙・時制の対比】tomorrow（明日）の preparation（準備）は、today（今日）の行動によってのみ完了する。未来を案じるよりも、目の前の現在に全力を注ぐことが最大の防御であるという実践的な教えです。</t>
-  </si>
-  <si>
-    <t>【文法：命令文 Put A into B】「AをBの中に注ぎ込め」。【語彙・名詞の並列と強調】heart, mind, and soul（心、精神、そして魂）。人間の内面を構成するすべてを、smallest acts（最も小さな行動）にさえ込めよ。どんな些細な日常の出来事にも全霊を傾けることの美しさを説いています。</t>
-  </si>
-  <si>
-    <t>【文法：not merely A but B】「単にAだけでなくBも」。【語彙・韻を踏んだ対比】マヤ・アンジェロウの言葉。survive（ただ生き延びる、生存する）と thrive（力強く成長する、繁栄する）。同じ「-vive/-rive」の響きを持つ単語を並べ、生命の目的を単なる生存以上の高みに置いています。</t>
-  </si>
-  <si>
-    <t>【文法：挿入句 no matter how...】no matter how small（どんなに小さくても）を挿入し、No act（いかなる行動も〜ない）という主語を強調しています。【語彙・絶対的肯定】イソップの言葉。kindness（親切）は、その規模に関わらず、絶対に無駄になること（wasted）はないという、人間の善意への全幅の信頼です。</t>
-  </si>
-  <si>
-    <t>【文法：代名詞 the one】the one は the journey の繰り返しを避けるための代名詞です。【語彙・内面への探求】リルケの言葉。only（唯一の）という強い限定を用い、地理的な外の世界への旅よりも、within（自分の内側、内面）への探求こそが、人間にとっての真の旅であると語っています。</t>
-  </si>
-  <si>
-    <t>【文法：第2文型(SVC)】The root of suffering（苦しみの根源）＝ attachment（執着）。【語彙・仏教的哲学】ブッダの教えの英訳。attach（くっつける）の名詞形。物事や感情、過去などに「しがみつくこと（執着）」こそが、人間のあらゆる苦しみを生み出しているという、東洋哲学の核心です。</t>
-  </si>
-  <si>
-    <t>【文法：関係副詞 where による副詞節】Where S V, ...（SがVする場所では、･･･）。【語彙・対比と擬人化】words fail（言葉が力尽きる）と music speaks（音楽が語り出す）。アンデルセンの言葉。言語の限界を超えたところに、音楽という普遍的な表現が存在するという、芸術への美しい賛歌です。</t>
-  </si>
-  <si>
-    <t>【文法：否定と肯定の並列】We do not A, we B.（AではなくBだ）。【語彙・単位の対比】days（日々、24時間の塊）と moments（瞬間、印象的な出来事）。人間はカレンダーの数字を記憶するのではなく、心を動かされた「瞬間」だけを記憶に刻むのだという、詩的な時間の捉え方です。</t>
-  </si>
-  <si>
-    <t>【文法：命令文と否定の修飾】tie it to A, not to B（BにではなくAにそれを結びつけよ）。【語彙・幸福の条件】アインシュタインの言葉。幸福（a happy life）を、移ろいやすい people（他者）や things（物質）に依存させるのではなく、自律的な goal（目標）に結びつけるべきだという論理的な提案です。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞 in と句動詞 sum up】In three words（3つの単語で）。sum up は「要約する」。コロン（:）以下がその内容です。【語彙・真理の凝縮】ロバート・フロストの言葉。it goes on（それ（人生）は続いていく）。どんな悲劇や歓喜があろうとも、立ち止まることなく時間は進み続けるという、達観した人生観です。</t>
-  </si>
-  <si>
-    <t>【文法：第2文型(SVC)】A smile ＝ the universal welcome。【語彙・形容詞のスケール】universal は「宇宙の、万国共通の」。言語や文化の壁を越え、笑顔という表情一つが、世界中のどこであっても相手を受け入れる（welcome）最強のコミュニケーションツールであるという事実です。</t>
-  </si>
-  <si>
-    <t>【文法：最上級と代名詞】The most wasted of all days（すべての日の中で最も無駄にされた日）が主語。one は a day を指します。【語彙・価値の基準】without laughter（笑いのない）。生産性や成果ではなく、「笑い」があったかどうかを一日を評価する最重要の基準に置いた、E.E.カミングスの名言です。</t>
-  </si>
-  <si>
-    <t>【文法：Not A but B 構文と前置詞 by】by chance（偶然によって）ではなく by choice（選択によって）。【語彙・頭韻法と主体性】chance と choice で「ch」の音を揃える言葉遊び。幸福は運任せで降ってくるものではなく、自らの意思で「選ぶ」ものであるという、人生のコントロール権の主張です。</t>
-  </si>
-  <si>
-    <t>【文法：形容詞の対比】complicated（複雑な）と simple（単純な）。【語彙・パラドックス】ドクター・スースの言葉。私たちが抱える問題や問い（questions）は非常に複雑に絡み合って見えても、実はその解決策（answers）は拍子抜けするほどシンプルであるという、真理の逆説です。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞 without による限定】without a plan（計画を持たない）が A goal を修飾しています。【語彙・冷徹な定義】サン＝テグジュペリの言葉。ただの願望（wish）と目標（goal）の違いは、「具体的な計画（plan）」の有無に過ぎない。夢見がちな姿勢を正し、行動の設計図を求める厳しい言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：Not A but B 構文】not knowledge but imagination（知識ではなく想像力）。【語彙・真の知性】アインシュタインの言葉。true sign of intelligence（知性の真の証）。すでに知っていること（knowledge）を誇るのではなく、未知のものを作り出す想像力（imagination）こそが天才の条件であるとしています。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 for による理由の補足】for everyone... は「というのは、誰もが〜だからだ」。【語彙・共感とメタファー】fighting a hard battle（困難な戦いを強いられている）。プラトンの言葉。一見平穏に見える人も、内面では見えない苦悩と戦っている。だからこそ無条件に「親切（kind）」であれという深い思いやりです。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の名詞的用法】to be a rainbow（虹になること）を Try（試みよ）。【語彙・美しい比喩】マヤ・アンジェロウの言葉。someone's cloud（誰かの心の暗雲、悲しみ）の中に架かる「虹（rainbow ＝ 希望、喜び）」になれ。他者の暗闇を照らす存在になるよう促す、非常に詩的で優しい表現です。</t>
-  </si>
-  <si>
-    <t>【文法：There is 構文と形容詞の後置修飾】charm を equal to〜（〜に等しい）という形容詞句が後ろから修飾しています。【語彙・最高級の価値】ジェーン・オースティンの言葉。tenderness of heart（心の優しさ、思いやり）に匹敵する魅力（charm）などこの世に存在しない。内面の美しさを最大限に讃えています。</t>
-  </si>
-  <si>
-    <t>【文法：that節内の条件節】「if you...すれば、life will...する、ということ(that)を発見した(found)」。【語彙・擬人化と返報性】人生（life）を擬人化し、こちらが愛せば相手（人生）も愛を返してくれる（love you back）という、世界に対する信頼とポジティブな法則を美しい語順で語っています。</t>
-  </si>
-  <si>
-    <t>【文法：等位接続詞 but による逆接】前半の事実（シンプルである）に対し、後半の人間の行動（複雑にする）を対置させています。【語彙・動詞 insist on】insist on -ing は「どうしても〜したがる、固執する」。孔子の言葉。人生は本来単純（simple）なのに、人間は自らの執着や思考でわざわざ複雑（complicated）にしているという洞察です。</t>
-  </si>
-  <si>
-    <t>【文法：第2文型(SVC)】Love ＝ a serious mental disease。【語彙・シニカルな定義】プラトンの言葉。愛という神聖視されがちな感情を、あえて serious（深刻な） mental disease（精神の病）と定義する。理性を失わせ、人間を狂わせる恋の力強さを逆説的に表現した、古代ギリシャの冷静な観察です。</t>
-  </si>
-  <si>
-    <t>【文法：副詞 through の名詞的・形容詞的用法】out（外へ出る道＝解決策）と through（突き抜けること）の対比。【語彙・困難への対処】ロバート・フロストの言葉。困難や問題から「抜け出す最善の方法（best way out）」は、逃げることではなく、その真っ只中を「突き進んで通り抜ける（through）」ことであるという力強い名言です。</t>
-  </si>
-  <si>
-    <t>【文法：Not A but B 構文と間接疑問文】how high（どれくらい高く）と how you make（どのように作るか）。【語彙・成功の再定義】climbed（登った高さ＝地位や富）ではなく、a positive difference（ポジティブな違い＝世界への貢献）をどれだけ生み出せたかが成功である。矢印を自分から他者へと向けさせています。</t>
-  </si>
-  <si>
-    <t>【文法：名詞＋不定詞の形容詞的用法】a chance（機会）を for you to do your best（あなたがベストを尽くすための）が修飾しています。【語彙・意味の反転】デューク・エリントンの言葉。problem（問題、厄介事）を、自分の実力を試す絶好のチャンス（chance）であると前向きに解釈し直すマインドセットです。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の省略】the things (which/that) you think you cannot do（あなたが「できない」と思っていること）。【語彙・義務の助動詞 must】エレノア・ルーズベルトの言葉。恐怖や限界を感じる「まさにその事」から逃げず、それに立ち向かうこと（must do）こそが成長の条件であるという厳しい教えです。</t>
-  </si>
-  <si>
-    <t>【文法：複合関係代名詞 Whatever】Whatever... で「〜するものは何でも」。it can achieve の it は the mind of man を指します。【語彙・思考の現実化】ナポレオン・ヒルの言葉。conceive（心に抱く、着想する）し、それを believe（信じる）ことができるなら、それは必ず achieve（達成する）できるという成功哲学の金字塔です。</t>
-  </si>
-  <si>
-    <t>【文法：強調構文 It is...that と言葉の反転】the years in your life（人生の中の年月＝寿命の長さ）と the life in your years（年月の中の人生＝生きる充実度）。【語彙・交錯配列法(Chiasmus)】リンカーンの言葉。count は「重要である」。言葉の順序を反転させることで、長さよりも質を重んじる見事な修辞法です。</t>
-  </si>
-  <si>
-    <t>【文法：The 比較級, the 比較級】「使えば使うほど、ますます持つことになる」。【語彙・無限の資源】マヤ・アンジェロウの言葉。use up（使い果たす）。creativity（創造性）は消耗品ではなく、使えば使うほど泉のように湧き出てくる（the more you have）無限の資源であるという、クリエイターへの賛歌です。</t>
-  </si>
-  <si>
-    <t>【文法：when節を用いた時間の論理】「私が彼らを友達にする時、私は敵を滅ぼしている」。【語彙・概念の転換】リンカーンの言葉。destroy（破壊する、滅ぼす）という暴力的な動詞を使いながら、実際の手段は make them my friends（友人に変える）という平和的なもの。最高の勝利とは相手を味方にすることであるという深い政治哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 who】who never gives up（決して諦めない）が a dreamer（夢想家）を修飾しています。【語彙・勝者の定義】ネルソン・マンデラの言葉。winner（勝者）とは、最初から強い人間や才能ある人間ではなく、夢を持ち（dreamer）、何度倒れても「決して諦めない（never gives up）」人間のことであるという感動的な定義です。</t>
-  </si>
-  <si>
-    <t>【文法：自動詞の拡張】fail my way to ... で「失敗しながら（失敗という道を通って）〜にたどり着く」というニュアンス。結果としての成功ではなく、過程としての失敗を肯定する構造です。</t>
-  </si>
-  <si>
-    <t>【文法：代名詞による対比】Only I（自分だけ）と No one（誰も〜ない）。助動詞 can を繰り返すことで、自分の人生の主導権が自分にしかないことを論理的に強調しています。</t>
-  </si>
-  <si>
-    <t>【文法：否定と肯定の並列】品質（Quality）を「一時的な行為（act）」ではなく「継続的な習慣（habit）」と再定義。短い SVC 構文が、その本質を力強く断定しています。</t>
-  </si>
-  <si>
-    <t>【文法：Not only A but also B】この構文を2回重ねることで、外的な行動（act, plan）と内的な精神（dream, believe）の両立が不可欠であることをリズム良く表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：条件の接続詞 as long as】「〜である限りは」。場所（anywhere）を問わず、方向（forward）さえ正しければ進み続けるという、強い意志を will で表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：使役動詞 let と what 節】「let A B（AにBさせる）」。できないこと（what you cannot do）が、できること（what you can do）を邪魔するのを許すな、という高度な対比構造です。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 unless】「〜しない限りは」。敗北（Defeat）という事象そのものではなく、それを「飲み込む（受け入れて屈する）」という自分の態度が苦しさを決めるという論理です。</t>
-  </si>
-  <si>
-    <t>【文法：数詞による対比】文法はシンプルですが、転倒回数より起き上がる回数を1回多くすることで、「最後は立ち上がって終わる」という不屈の精神を象徴的に示しています。</t>
-  </si>
-  <si>
-    <t>【文法：先行詞を含む he who】「〜する人は」。健康 → 希望 → すべて、と A=B, B=C のように繋げていくことで、健康がすべての土台であることを論理的に説明しています。</t>
-  </si>
-  <si>
-    <t>【文法：仮定法過去】「たとえ（実際には起きないが）明日世界が滅びると分かっていても」。would を使うことで、状況に左右されない人間の高潔な決意を表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：部分否定 may not】「毎日が良いわけではない（良い日もあれば悪い日もある）」。後半の there is 構文で視点を変え、どんな日の中にも「良さ（something good）」を見出す姿勢を説いています。</t>
-  </si>
-  <si>
-    <t>【文法：最上級による定義】最も偉大な富（The greatest wealth）＝ 健康。シンプルながらも、価値観の優先順位を明確に打ち出す SVC 構文です。</t>
-  </si>
-  <si>
-    <t>【文法：keep A from -ing】「Aが〜するのを妨げる」。恐怖（fear）によって挑戦（playing the game）を止められてはいけない。使役動詞 let の否定で、強い禁止と励ましを表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：助動詞 must と語法】「expect A of B（BにAを期待する）」。行動（do them）の前に、まず自己への期待（expect）が必要であるという、内面から外への因果関係を示しています。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞 on の焦点】結果（destination）という一点ではなく、過程（journey）という広がりに意識を向けろという対比。on のイメージが「集中」を際立たせています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 that】光を広める2つの手段を不定詞（to be）で説明。能動的なロウソクと、受動的だが忠実な鏡。that節が鏡の役割を詳しく補足しています。</t>
-  </si>
-  <si>
-    <t>【文法：使役動詞の代動詞 let it】let it (change) の略。「もしあなたが人生が（変わるのを）許せば」。自分の心が許可を与えれば、人生の変化は加速するという条件を if で示しています。</t>
-  </si>
-  <si>
-    <t>【文法：too ... to 構文】「〜するにはあまりに･･･すぎる（＝できない）」の否定。「年をとりすぎていてできない、なんてことは決してない（never）」という強い二重否定的な励ましです。</t>
-  </si>
-  <si>
-    <t>【文法：第5文型 want A to be B】A（状況）が B（簡単）であることを求めるのではなく、B（価値がある）であることを求める。困難さを引き受ける覚悟を対比で表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：間接疑問文 who you are】「自分が誰であるか」を突き止める（Find out）。その上で、意図的に（on purpose）その個性を生きろという、自己実現へのステップを命令文で示しています。</t>
-  </si>
-  <si>
-    <t>【文法：動詞 turn の語法】「turn A into B（AをBに変える）」。状況（situation）の形容詞を negative から positive へと反転させることで、捉え方の転換を促しています。</t>
-  </si>
-  <si>
-    <t>【文法：名詞としての副詞】本来副詞である always（いつも）や never（決して〜ない）を名詞として扱い、決めつけや極端な思考を「制限（Limit）」せよと説く、ユニークな表現です。</t>
-  </si>
-  <si>
-    <t>【文法：直喩 like】良い考え（good thoughts）が顔から「輝き出る（shine out）」という内面の反映を、太陽光（sunbeams）に例えて視覚的に表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：過去分詞の後置修飾】lived well（良く生きられた）という過去分詞が life を修飾。幸福は追いかける「目標」ではなく、正しい生き方の「副産物（by-product）」であるという真理です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の先行詞との離反】who 節が修飾しているのは文頭の No one です。他人の重荷を軽くする（lightens the burdens）行為が、存在の価値を決定するという構造です。</t>
-  </si>
-  <si>
-    <t>【文法：名詞の再定義】幸福へたどり着くための「道（path）」を否定し、幸福を感じながら歩むこと自体が「道」であると定義。コロン（:）による劇的な反転です。</t>
-  </si>
-  <si>
-    <t>【文法：複合関係副詞 whenever】「可能なときはいつでも」。後半の It は kind でいることを指し、親切にするチャンスは逃せばないのではなく、常に自分の意志で創れることを示しています。</t>
-  </si>
-  <si>
-    <t>【文法：強調構文と Not A but B】「It is A that ...」の形。重要なのは起きたこと（what happens）ではなく、どう反応するか（how you react）であると、手段と態度を強調しています。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の名詞的用法】勝つこと（To win）＝ 勝利すること（to triumph）。リスクを排除することは、同時に栄光（glory）も排除することになるという、表裏一体の関係を述べています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 he who】勇敢さの定義を「恐怖を感じない（does not feel）」から「克服する（conquers）」へと上書きしています。感情ではなく行動が勇気を決めるという教えです。</t>
-  </si>
-  <si>
-    <t>【文法：形容詞の名詞化 the + 形容詞】the educated で「教育を受けた人々」。自由（free）は特権ではなく、教育によって得られる精神の状態であるという断定的な SVC です。</t>
-  </si>
-  <si>
-    <t>【文法：what節と助動詞 can】「今日の行動」が主語。can（可能性がある）を使うことで、今の自分の一歩が未来のすべてを好転させる希望の因果関係を示しています。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 as if と強調の does】違いを生む（make a difference）かのように振る舞え。最後の It does. は事実であることの念押し（代動詞）です。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞の並列】成功の内容を「転ぶこと（falling）」と「起き上がること（getting up）」のセットとして提示。回数を 9回対10回にすることで、不屈の精神を表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の形容詞的用法】過去の後悔（20 years ago）を認めつつ、現在（now）を「次善の策」として提示。今始めることが最善であると論理的に促しています。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞 by の手段】「夢（dreams）」という手段によって人間は「偉大に育つ（grow great）」。内なるビジョンが外的な成長を導くというシンプルな因果関係です。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞による手段】人生を変える（change your life）方法は、心を変えること（changing your heart）である。原因と結果を同じ動詞 change で繋ぐことで、直結した変化を強調しています。</t>
-  </si>
-  <si>
-    <t>【文法：形式主語 It と不定詞】真の主語は to grow up...。「本当の自分（who you really are）」になることの困難さを it takes（必要とする）という動詞で表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：so ... that 構文】行動があまりにうるさく叫ぶ（speaks so loudly）ので、言葉（what you say）が聞こえない。言葉よりも行動が真実を語るという擬人化を用いた強調です。</t>
-  </si>
-  <si>
-    <t>【文法：what節の対置】成功（Success）と幸福（Happiness）の違いを、get と want の語順を入れ替えるだけで見事に定義。外的な所有と内的な満足の差を説いています。</t>
-  </si>
-  <si>
-    <t>【文法：条件節 If の対比】speed（fast）なら一人（alone）、distance（far）ならチーム（together）。目的によって手段を選ぶべきだという、並列の論理構造です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の受動態】to be lived（生きられるために）。人生は「ある（here）」だけでなく、実際に「生きられる（行動を伴う）」べき対象であるという存在意義を述べています。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の主語】「考えること」と「行動すること」。対照的な形容詞 easy と hard を使うことで、実行の難しさと価値を際立たせています。</t>
-  </si>
-  <si>
-    <t>【文法：名詞の並列】ひらめき（inspiration）と努力（perspiration）の比率を提示。似た響きの単語を使い、成功の大部分が泥臭い努力によって構成されていることを示しています。</t>
-  </si>
-  <si>
-    <t>【文法：接尾辞 -able と動詞の対比】到達可能（attainable）ではない完璧（Perfection）を「追いかける（chase）」ことで、結果として卓越（excellence）を「捕まえる（catch）」ことができるというプロセスです。</t>
-  </si>
-  <si>
-    <t>【文法：同等比較 not so ... as】enthusiasm（熱意）以上に「伝染しやすい（contagious）」ものはない。最上級の意味を比較構文で表現し、熱意の及ぼす影響力を最大化しています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what と前置詞 for】「そのために（for what）」船が造られた。安全（safe）であることよりも、目的（航海）を果たすことこそが本来の存在意義であるという比喩表現です。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞と when 節】人格（Character）とは「正しいことをすること」。他者の目（nobody's looking）という外的要因に関わらず、内面的な正しさを貫くことを定義しています。</t>
-  </si>
-  <si>
-    <t>【文法：関係副詞 where】end up（結局〜になる）。今の方向（direction）のまま進めば、意図せずともその延長線上に着いてしまうという、無意識の慣性への警告です。</t>
-  </si>
-  <si>
-    <t>【文法：倒置】本来 Never leave [that which you can do today] till tomorrow。目的語が長いため後回しにされています。今日できることを明日に回すな、という有名な格言の強調形です。</t>
-  </si>
-  <si>
-    <t>【文法：否定代名詞と前置詞 except】nothing（何もない）と except（〜以外に）を組み合わせることで、「〜以外に･･･なものは何もない（〜だけだ）」という強い肯定の表現を作っています。【語彙・パラドックス】permanent（永久的な）と change（変化）。「変化」という現象だけが唯一変わらないものであるという、ヘラクレイトスの有名な逆説です。</t>
-  </si>
-  <si>
-    <t>【文法：関係副詞 where の副詞節】where the path may lead は「道が導くかもしれない場所（＝すでに敷かれた道）」。【語彙・対比とメタファー】エマーソンの言葉。go と leave（残す）。他人が作った安全な道（path）を進むのではなく、未開の地に自らの足跡（trail）を残せという、フロンティア精神の力強い命令文です。</t>
-  </si>
-  <si>
-    <t>【文法：比較級 make more...than】than he finds（彼が見つけるよりも多くの）。【語彙・主体性の強調】フランシス・ベーコンの言葉。wise man（賢者）。機会（opportunities）は自然に「見つかる（find）」のを待つのではなく、自らの手で「創り出す（make）」ものである。動詞の対比で主体的な行動の価値を説いています。</t>
-  </si>
-  <si>
-    <t>【文法：関係副詞 when の省略】the day (when) you are born と the day (when) you find out why。【語彙・人生の目的】マーク・トウェインの言葉。find out why は「なぜ生まれたのか（その理由）を見つける」。物理的な「誕生」と、精神的な「使命の自覚」を人生の2大イベントとして並列させた名言です。</t>
-  </si>
-  <si>
-    <t>【文法：助動詞 would rather A than B】「BするくらいならAする方がましだ（Aしたい）」。【語彙・究極の選択】ゴッホの言葉。passion（情熱）と boredom（退屈）。die of〜（〜が原因で死ぬ）。退屈で無難な一生を送るくらいなら、情熱に焼かれて滅びる方を選ぶという、芸術家らしい激烈な生き様を表しています。</t>
-  </si>
-  <si>
-    <t>【文法：第3文型(SVO)の対比】A will get you... と B will take you...。【語彙・スケールの違い】アインシュタインの言葉。Logic（論理）は A から B へと確実に運んでくれるが、Imagination（想像力）は everywhere（あらゆる場所）へ連れて行ってくれる。論理の限界と想像力の無限の可能性を端的に示しています。</t>
-  </si>
-  <si>
-    <t>【文法：複合関係代名詞 Whatever】Whatever you do（あなたが何をしようとも）。譲歩の副詞節を作っています。【語彙・プロ意識】リンカーンの言葉。do it well（それを上手く、立派にやれ）。職業や内容の優劣を問わず、目の前の役割にベストを尽くすこと自体に尊厳があるという、極めてシンプルな命令です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の省略と前置詞】the five people (who/whom) you spend the most time with。【語彙・環境の法則】ジム・ローンの言葉。average（平均）。人間の人格や成果は、個人の意志よりも「誰と過ごすか」という環境に強く影響される。付き合う人間を選ぶことの重要性を論理的に解いた表現です。</t>
-  </si>
-  <si>
-    <t>【文法：第3文型(SVO)】Fortune favors...（幸運は〜に味方する）。【語彙・形容詞の名詞化】the bold（the + 形容詞 = 勇敢な人々）。古代ローマの格言。幸運（Fortune）という女神を擬人化し、彼女は安全を好む者ではなく、大胆にリスクを取る者（bold）を好んで微笑むという、勇気を讃える言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 he who と最上級】He who... で「〜する人は」。most と best がそれぞれ動詞を修飾しています。【語彙・学習と感情】笑うこと（laughs）と学ぶこと（learns）。苦行のように学ぶよりも、楽しみながら（笑いながら）取り組む人間が最も効率よく吸収するという、リラックスと好奇心の重要性です。</t>
-  </si>
-  <si>
-    <t>【文法：主語の拡張と can の否定】The beautiful thing about learning（学ぶことの素晴らしい点）が全体の主語。【語彙・永遠の資産】B.B.キングの言葉。take it away from you（あなたからそれを奪い去る）。お金や地位は失う可能性があるが、一度身につけた「学び」だけは誰にも奪えない絶対的な財産であるという真理です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の副詞的用法】To be the best（最高になるためには）。【語彙・両極端の対比】the best（最高のもの）と the worst（最悪の事態）。最高の栄光を手にする資格があるのは、最悪のプレッシャーや失敗に対処（handle）できる覚悟を持った者だけであるという、強い対句表現です。</t>
-  </si>
-  <si>
-    <t>【文法：SVOの3連打とセミコロン】接続詞を使わず、セミコロン（;）で3つの文を並置しています。【語彙・知性のレベル】エレノア・ルーズベルトの言葉。知性の高い順（Great / average / small）に、議論の対象が 概念（ideas）→ 出来事（events）→ 他人の噂（people）へと低下していく様子を鋭く描写しています。</t>
-  </si>
-  <si>
-    <t>【文法：代名詞 those who と how far節】those who will risk -ing で「あえて〜するリスクを取る人々」。【語彙・限界の突破】T.S.エリオットの言葉。行き過ぎる（going too far）という危険を冒した者だけが、自分の本当の限界（how far one can go）を知る（find out）ことができるという、挑戦の独占的価値です。</t>
-  </si>
-  <si>
-    <t>【文法：強調構文 It is...that】It is during our darkest moments that...（･･･なのは、最も暗い時期においてだ）。【語彙・光と闇のメタファー】アリストテレスの言葉。darkest（最悪の絶望）と light（希望）。暗闇の中でこそ、微かな光を見つけるために極限まで集中（focus）しなければならないという力強い教えです。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の名詞的用法と関係代名詞】to be unlike him（彼とは似ていない状態になること）。who performed the injury が him を修飾。【語彙・復讐の再定義】マルクス・アウレリウスの言葉。最高の復讐とは、やり返すことではなく、自分を傷つけた愚かな人間と同類に「ならない（unlike）」ことであるという高潔な哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：直喩(Simile)と if節】like a parachute（パラシュートのようなもの）。【語彙・ユーモアの効いた比喩】アインシュタイン（またはフランク・ザッパ）の言葉。心（mind）もパラシュートも、開いて（open）いなければ落下して死ぬだけで、全く機能しない（doesn't work）。柔軟な思考の必要性をユーモラスに説いています。</t>
-  </si>
-  <si>
-    <t>【文法：命令文と関係代名詞の省略】Everything (that) you need（あなたが必要とするすべて）。【語彙・タイミングへの信頼】Keep going（とにかく進み続けろ）。焦って追いかけなくても、必要なものは「完璧なタイミング（perfect time）」で向こうからやって来る（come to you）。行動を止めないための癒しの言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の省略】the chances (that) we didn't take（私たちが掴まなかったチャンス）。【語彙・後悔の本質】In the end（最後には）。人間は「やって失敗したこと」よりも「やらなかったこと」を後悔（regret）する。挑戦をためらう背中を強く押してくれる、人生の終着点からの逆算思考です。</t>
-  </si>
-  <si>
-    <t>【文法：相関接続詞 either A or B】「AかBかのどちらか」。【語彙・失敗の概念の消去】ネルソン・マンデラの言葉。lose（負ける）という概念を完全に否定し、結果を win（勝つ）か learn（学ぶ）の2択に限定。どんな結果も自己の成長に繋げる無敵のマインドセットです。</t>
-  </si>
-  <si>
     <t>【文法：受動態 be intended to と言葉遊び】are intended to... で「〜することを意図されている」。【語彙・韻を踏んだ対比】better（より良く）と bitter（苦々しく、恨みがましく）。困難は私たちを卑屈にするためではなく、向上させるための試練である。1文字違いの単語で美しいコントラストを作っています。</t>
   </si>
   <si>
@@ -4623,291 +4113,6 @@
   </si>
   <si>
     <t>【文法：前置詞 with の起点】begins with one step（一歩から始まる）。【語彙・普遍の真理】老子の言葉「千里の道も一歩から」。a thousand miles（果てしなく遠い道のり）という壮大な旅（journey）も、すべては今目の前にある「たった一歩（one step）」を踏み出すことからしか始まらない。365日の学びの最後を飾る、行動への普遍的なエールです。</t>
-  </si>
-  <si>
-    <t>【文法：基本の第3文型(SVO)】主語(I) + 動詞(have) + 目的語(a dream)という、英語の最も基本かつ力強い文型です。【語彙・冠詞の凄み】注目すべきは不定冠詞の「a」です。dreams（複数の夢）や the dream（特定の夢）ではなく、「a dream（ある一つの明確な夢）」と単数形にすることで、後に語られる具体的な「たった一つの揺るぎない理想」へと聴衆の意識を一気にフォーカスさせる修辞的効果があります。</t>
-  </si>
-  <si>
-    <t>【文法：現在完了形と関係代名詞の主格】I have not failed は過去から現在までの経験や結果を否定する現在完了。「that won't work」の that は ways を修飾する主格の関係代名詞です。【語彙・語法】work は「働く」だけでなく、物や方法が「機能する、うまくいく」という意味を持つ超重要単語。will not (won't) は「どうしても〜しない」という強い拒絶・確信を表します。fail（失敗する）というネガティブな概念を、find（発見する）というポジティブな行動へと見事に再定義しています。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞のlikeと不定詞の副詞的用法】like は動詞ではなく前置詞（〜のような）で、後ろに動名詞 riding を取ります。To keep は「〜するために」という目的の副詞的用法。【語彙・語法】keep O C（OをCの状態に保つ：keep your balance）と、keep -ing（〜し続ける：keep moving）という2つの異なる keep の語法が巧みに使われています。「バランスを保つ（静）」には「動き続ける（動）」しかないという物理法則を、人生の真理に重ね合わせています。</t>
-  </si>
-  <si>
-    <t>【文法：名詞構文と助動詞will】「realization of tomorrow（明日への実現）」と「doubts of today（今日の疑念）」という名詞の対比。will は単なる未来ではなく「必ず〜になるだろう」という強い確信（推量）を表します。【語彙・前置詞】The only limit to〜 の to は「〜に対する（限界・境界）」という方向性を示します。実現と疑念という対義的な概念を時制（明日/今日）と結びつけ、未来を阻むのは外的要因ではなく現在の自分の内面だけであると論理的に説明しています。</t>
-  </si>
-  <si>
-    <t>【文法：譲歩の複合関係代名詞】Whatever you are は「あなたが何者であろうとも」という譲歩（〜だとしても）の副詞節を作ります。【語彙・代名詞】one は既出の単語の反復を避ける代名詞ですが、ここでは「a person」や「a professional（ある職業の人）」など、あなたが選んだ『どのような立場や役割』でも代入できる器として機能しています。「職業や立場に貴賤はない、選んだ道でベストを尽くせ」という深みを持たせています。</t>
-  </si>
-  <si>
-    <t>【文法：強調構文 It is...that】「〜なのは･･･だ」と、thatの前の言葉（the courage to continue）を強調する構文です。【語彙・修辞技法】final（最終的な）と fatal（致命的な）で「f」と「l」の音を揃える頭韻法（Alliteration）が使われ、美しいリズムを生んでいます。また、最後の count は「数える」ではなく「重要である」という自動詞です。</t>
-  </si>
-  <si>
-    <t>【文法：第1文型(SV)と前置詞with】begin は目的語をとらない自動詞で、「平和のほうから自発的に始まる」というニュアンスを持たせています。【語彙・ニュアンス】前置詞 with は「〜を伴って」という付帯状況を表します。平和という巨大で抽象的な概念が、日常のささやかな「微笑み」と共にあるという、マザー・テレサらしい優しさと力強さが短い文に凝縮されています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 those who】belong to〜（〜の所有物である）。those who は「〜する人々」という頻出構文です。【語彙・語法】believe ではなく believe in を使っているのがポイントです。believe は「（事実だと）信じる」ですが、believe in は「（その存在や価値を）深く信じ込んでいる」という強いニュアンス。夢の「美しさ（beauty）」に全幅の信頼を寄せる姿勢を表しています。</t>
-  </si>
-  <si>
-    <t>【文法：Not A but B 構文】「AではなくB」。judge A by B（AをBの基準で判断する）という熟語と組み合わせています。【語彙・メタファー】harvest（収穫＝結果）と seeds（種＝過程・努力）という農業の比喩（メタファー）です。you reap（刈り取る）と that you plant（植える）という関係代名詞節がそれぞれの名詞を後ろから修飾し、対比構造を際立たせています。</t>
-  </si>
-  <si>
-    <t>【文法：代名詞の強意用法】itself は the word を直後で強調し「その言葉自体が」という意味を作ります。【語彙・言葉遊び】impossible（不可能）という単語を、im-possible ではなく I'm possible（私は可能だ）と分解して読む、見事な言葉遊び（Pun）です。否定的な単語の中に肯定的な宣言が隠れていることを発見する、オードリー・ヘプバーンの名言です。</t>
-  </si>
-  <si>
-    <t>【文法：譲歩の副詞節 whether A or B】「AであろうとBであろうと」。ここでは you think you can と you think you can't という2つの完全な文を対比させています。【語彙・ニュアンス】主節の you're right（あなたは正しい）が非常に短いため、強い断定の響きを持っています。「できると思えばできるし、できないと思えばできない（どちらにせよ、あなたの思い込み通りになる）」というマインドセットの真理です。</t>
-  </si>
-  <si>
-    <t>【文法：命令文 + and】「〜しなさい、そうすれば･･･」。前半の命令が「条件」、後半の and 以下がその「結果」を表します。【語彙・対比】sunshine（太陽の光＝希望・ポジティブなもの）と shadows（影＝過去・ネガティブなもの）の対比。toward（〜の方へ）と behind（〜の後ろに）という方向を表す前置詞が、視点を変えれば現実が変わるという物理法則を見事に表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：名詞節（what節とhow節）】what happens to me（私に起きること）と how I react to it（それに私がどう反応するか）という2つの名詞の塊が、is の補語になっています。【語彙・ニュアンス】人生における「環境や運（10%）」と「自分の態度や解釈（90%）」を数値化して対比させています。react（反応する）という動詞の選択が、出来事に対する人間の主体性を強調しています。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞の主語と助動詞must】Knowing（知っていること）と Willing（意欲があること）を主語に配置。must は強い義務「〜しなければならない」を表します。【語彙・修辞技法】全く同じ文構造を2回繰り返す並行法（Parallelism）が使われています。知識（Know）を応用（apply）し、意欲（Will）を実行（do）に移す。静的な状態から動的なアクションへの移行を強く促しています。</t>
-  </si>
-  <si>
-    <t>【文法：形式主語 It と条件の接続詞 as long as】It は形式主語で、真の主語は how slowly you go（どんなにゆっくり進むか）。as long as は「〜である限りは」という強い条件を示します。【語彙・ニュアンス】matter は「問題である、重要である」という自動詞。他者とのスピード競争を完全に否定し、stop（立ち止まる）ことさえしなければ必ず到達できるという、継続の圧倒的な価値を説いています。</t>
-  </si>
-  <si>
-    <t>【文法：現在完了の受動態】is already taken は「すでに取られてしまっている（予約済みである）」。【語彙・ユーモア】セミコロン（;）は「なぜなら」という理由の接続詞の役割を果たしています。自分以外の誰か（everyone else）になろうとしても、その席はすでに埋まっているという、アイデンティティの尊さをユーモアたっぷりに表現したオスカー・ワイルドの言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：倒置に近い否定と名詞節】本来は Don't ask ですが、あえて古風に Ask not とすることで強い宣言のような響きを作っています。what節の中身を入れ替えています。【語彙・交錯配列法(Chiasmus)】「country - do - you」という順序を、後半で「you - do - country」と交差（Xの字）させるように反転させる高度な修辞技法。ケネディ大統領の就任演説を歴史に刻んだ名文句です。</t>
-  </si>
-  <si>
-    <t>【文法：命令文 + and】「信じなさい、そうすれば･･･」。there は副詞で「そこ（目的地）へ」。【語彙・イディオム】halfway there は「道半ばにいる、目標の半分は達成した」という頻出表現。技術や努力の前に、「自分を信じる」というマインドセットを持つだけで、すでに成功の50%は完了しているという、確信の力を表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：SVO + 補語的な副詞】bring O closer（Oをより近くへ連れて行く）。無生物主語（Every strike）が、私（me）を動かすという英語らしい表現です。【語彙・ニュアンス】strike（空振り）という一見ネガティブな失敗が、home run（成功）への距離を縮める（closer）役割を果たしているという、ベーブ・ルースならではの前向きな解釈です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の名詞的用法】The purpose（目的）＝ to be happy（幸せであること）。非常にシンプルで純度の高い第2文型（SVC）です。【語彙・ニュアンス】lives は life の複数形。私たち全人類に共通する目的は何か？という壮大な問いに対する、ダライ・ラマの迷いのない力強い断定です。</t>
-  </si>
-  <si>
-    <t>【文法：形式主語 It と比較級】2つの It is...to〜（〜することは･･･だ）の構文を but で繋ぎ、more important で後者に重きを置いています。【語彙・語法】heed は「〜に注意を払う、心に留める」という少し硬い、教訓的な動詞。成功を祝う（celebrate）喜びよりも、失敗の教訓（lessons of failure）から学ぶ謙虚さを重視するビル・ゲイツの姿勢です。</t>
-  </si>
-  <si>
-    <t>【文法：変化の動詞 turn の語法】turn A into B（AをBに変える）。【語彙・頭韻法】wounds（傷、トラウマ）と wisdom（知恵、叡智）という「w」の音から始まる単語を対置させています。マイナスの経験を、単なる傷跡で終わらせず、人生を豊かにするプラスの知恵へと昇華させよという、短いながらも力強い命令です。</t>
-  </si>
-  <si>
-    <t>【文法：直喩法（Simile）と命令文】like を使って「〜のように」と他のものに例える修辞技法です。【語彙・対比】float（ふわふわ浮く）と sting（チクリと刺す）、butterfly（美しく舞う蝶）と bee（攻撃的な蜂）。モハメド・アリのボクシングスタイルを表す言葉ですが、相反する2つの性質（軽やかさと鋭さ）を併せ持つことの美学を示しています。</t>
-  </si>
-  <si>
-    <t>【文法：仮定法過去】「もし〜だとしたら、･･･だろうか（いや、そうではない）」。現在の事実に反する仮定を表します。【語彙・不定詞の形容詞的用法】courage を後ろから to attempt anything（何かを試みるための）が修飾しています。勇気がなければ人生は無意味であるという、ゴッホの強烈なメッセージを反語的に表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：仮定法過去】if it weren't で「もし（人生が）〜でなかったら」。be動詞は通常 was ですが、仮定法では伝統的に were が好まれます。【語彙・ニュアンス】tragic（悲劇的な）と funny（滑稽な、面白い）。ホーキング博士の言葉ですが、どんなに過酷な運命であっても、そこにユーモア（funny）を見出すことができれば、人生は悲劇にはならないという救いの表現です。</t>
-  </si>
-  <si>
-    <t>【文法：最上級と不定詞の対比】The best way を to predict が修飾し、結論の補語として to create が置かれています。【語彙・ニュアンス】predict（事前に言う＝予測する）と create（ゼロから創り出す）。未来は受動的に「当てる」ものではなく、自らの手で能動的に「創る」ものであるという、リンカーンの主体性を重んじる哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：条件節と副詞句】in a great way（偉大なやり方で）が、動詞 do を修飾する副詞句として働いています。【語彙・ニュアンス】great things（偉業）と small things（些細なこと）の対比。結果の大小ではなく、取り組む「姿勢（way）」にこそ真の偉大さが宿るという、キング牧師の深く優しいメッセージです。</t>
-  </si>
-  <si>
-    <t>【文法：命令文 + and】「思考を変えよ、そうすれば世界が変わる」。【語彙・原因と結果】thoughts（内面的な思考）という「原因」が、world（自分を取り巻く外的な世界）という「結果」をダイレクトに決定づける。主語の you が2回繰り返され、自分自身の力で現実を変えられることを強調しています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の省略】the shots と you の間に目的格の that/which が省略されています。「あなたが打たないシュート」。【語彙・ニュアンス】miss は「外す、逃す」。スポーツ（アイスホッケー）の文脈ですが、人生全般に当てはまります。「失敗を恐れて行動しないこと」こそが、唯一確実に100%失敗（miss）する方法であるという論理的パラドックスです。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what】what you do は「あなたがすること（＝仕事）」。the thing which と書き換え可能です。【語彙・ニュアンス】is でAとBをイコールで結んでいます。「偉大な仕事をする」ための条件は、才能や努力の前に、まず対象を「愛する（love）」ことであるという、スティーブ・ジョブズの情熱の哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：Not A but rather B】「Aではなく、むしろB」。be of value は「be valuable（価値がある）」と同じ意味の重要な文法（of + 抽象名詞）です。【語彙・ニュアンス】strive は「懸命に努力する」。success（成功という世間的な結果）を否定し、value（他者に提供できる本質的な価値）を肯定するアインシュタインの言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：先行詞を含む関係代名詞 what】become の補語（C）として what 節が丸ごと入っています。「私たちは、私たちが考えていること（そのもの）になる」。【語彙・ニュアンス】思考（think）が現実の存在（become）を形作るという、引き寄せの法則の原点のような言葉。シンプルゆえに、普段自分が何を考えているかの重要性を鋭く突きつけてきます。</t>
-  </si>
-  <si>
-    <t>【文法：分詞構文 -ing】living... は「〜生きながら（生きることで）」という付帯状況。waste it（時間を浪費する）の具体的な手段を説明しています。【語彙・ニュアンス】limited（限られている）という冷徹な事実を提示した上で、someone else's life（他人の期待や常識に沿った人生）を生きる虚しさを説く、ジョブズのスタンフォード大演説の有名な一節です。</t>
-  </si>
-  <si>
-    <t>【文法：名詞句の対置】「I am not A. I am B.」という強い否定と肯定の連続。【語彙・ニュアンス】a product of〜（〜の産物、結果）。circumstances（自分を取り巻く環境・状況）を言い訳にせず、decisions（自らの意思による決断）こそが自分を創ったのだという、自己責任と主体性の極致です。</t>
-  </si>
-  <si>
-    <t>【文法：疑問詞 + 不定詞 / 接続詞 once】how to remain は「どうやって〜のままでいるか」。once は「いったん〜すると」という接続詞。【語彙・ニュアンス】ピカソの言葉。誰もが生まれながらに持つ芸術性（artist）が、成長（grows up）や社会化の過程で失われてしまうことへの警鐘。問題は「なる」ことではなく「あり続ける（remain）」ことだとしています。</t>
-  </si>
-  <si>
-    <t>【文法：最上級と SVC 構文】revenge（復讐）の定義を、be動詞を使って書き換える究極の構文です。【語彙・ニュアンス】massive は「巨大な、圧倒的な」。自分を傷つけた相手に直接やり返すのではなく、自分が圧倒的に成功して幸せになることこそが、相手にとって最大の痛手（復讐）になるという、フランク・シナトラの洗練された反撃論です。</t>
-  </si>
-  <si>
-    <t>【文法：コロン（:）による具体化】コロンは「つまり、具体的に言うと」という役割。後ろに3つの命令文を並べています。【語彙・反復法】nothing（何もない）を3回繰り返すことで、批判（criticism）を避ける人生がいかに空虚で何の意味も持たないものかを、アリストテレスが逆説的に強烈に皮肉っています。</t>
-  </si>
-  <si>
-    <t>【文法：同族目的語 / 関係代名詞の省略】live the life（人生を生きる）は、動詞と名詞が同じ語源を持つ表現。その後ろに that you have imagined が省略されています。【語彙・ニュアンス】confidently（自信を持って）を動詞 go の直後に置き、行動の「質」を指定。頭の中で想像した（imagined）ものを、現実の人生（life）に引きずり下ろせというソローの力強いメッセージです。</t>
-  </si>
-  <si>
-    <t>【文法：現在完了と関係代名詞の省略】Everything (that) you have ever wanted で「あなたがこれまで生きてきて望んだすべてのもの」。【語彙・メタファー】fear（恐怖）を、乗り越えるべき「壁」として視覚化しています。欲しいものはすべて、その壁の「向こう側（on the other side）」にある。恐怖を感じるのは、欲しいものが目の前にある証拠だという励ましです。</t>
-  </si>
-  <si>
-    <t>【文法：関係副詞 where と 関係代名詞 what】3つの短い命令文が、それぞれ「場所」「所有物」「能力」を目的語として取っています。【語彙・ニュアンス】「もっと条件が整ったら」という言い訳をすべて封じる言葉。今いる場所、今ある道具、今できること。足りないものを数えるのではなく、手元にあるリソースを100%使えという実践的な哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：部分否定】not everyone は「全員が〜できるわけではない（見える人もいれば、見えない人もいる）」という重要な文法事項です。【語彙・ニュアンス】beauty（美しさ）は、対象物の中に客観的に存在するのではなく、それを見つめる人間の「目（see）」や「心」に依存しているという、孔子の深い洞察です。</t>
-  </si>
-  <si>
-    <t>【文法：感嘆文と真主語のthat節 / 助動詞need】How wonderful it is...! で「なんて素晴らしいのだろう！」。that以下がその内容です。nobody need wait の need は、否定語とともに使われる「助動詞（〜する必要がある）」です。【語彙・ニュアンス】アンネ・フランクの言葉。a single moment（一瞬たりとも）。世界を良くする（improve）ために、誰かの許可や特別なタイミングを待つ必要はないという、行動への純粋な喜びを表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：what節の対比と助動詞might】what I am（現在の自分）と what I might be（なるかもしれない自分＝可能性）。【語彙・イディオム】let go of〜 は「〜を執着から手放す」。老子の言葉ですが、今の自分（地位やプライド）にしがみついている限り、次のステージへは進めないという、東洋思想の真髄「手放すことの美学」が英語で見事に表現されています。</t>
-  </si>
-  <si>
-    <t>【文法：Not A but B 構文と受動態】「Aによってではなく、Bによって測られる（is measured）」。【語彙・言葉遊びと修辞】breaths we take（私たちがする呼吸＝単なる生存期間）と、take our breath away（息を呑むほどの感動）という、breath/take を使った鮮やかな言葉遊び。人生を「時間の長さ」ではなく「感動の深さ」で測るべきだという詩的な名言です。</t>
-  </si>
-  <si>
-    <t>【文法：後置修飾と代名詞】something を形容詞 readymade（既製品の）が後ろから修飾。It は Happiness を指します。【語彙・ニュアンス】ダライ・ラマの言葉。幸福はどこかの棚に完成品として売られている（readymade）ものではない。自らの行動（actions）によって、部品から組み立てて「生み出す（comes from）」ものであるという論理的な説明です。</t>
-  </si>
-  <si>
-    <t>【文法：受動態と間接疑問文】you're offered は第4文型（offer O1 O2）の受動態で「（あなたが）座席を提示される」。what seat は「どの席か」という間接疑問文です。【語彙・ニュアンス】a rocket ship（ロケット）は「圧倒的な急成長や大チャンス」の比喩。千載一遇のチャンスが来た時に、条件（what seat）を気にしてためらうのではなく、まずは飛び乗れ（Just get on）という勢いを命令文で表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：並列の that 節と挿入句】believe の目的語として2つの that 節が and で結ばれています。at whatever cost（どんな犠牲を払っても）が2つ目の that 節の中に挿入されています。【語彙・語法】gifted は「才能を与えられている（天賦の才がある）」。attain は「（努力の末に）到達する、達成する」。自分の才能を信じ、それを絶対に開花させるというキュリー夫人の強固な信念が must の反復に表れています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what と 第5文型(SVOC)】2つの what 節がそれぞれ「人生を面白くするもの」「人生を意味あるものにするもの」として補語(C)になっています。【語彙・対比】Challenges（困難そのもの）と overcoming them（それを克服すること）が対置されています。困難があるからこそ人生は退屈せず、それを乗り越える「過程」にこそ意味（meaningful）が宿るという構造です。</t>
-  </si>
-  <si>
-    <t>【文法：句動詞 lift up】lift up（持ち上げる、向上させる）。代名詞（yourself）は lift と up の間に挟むのが原則です。【語彙・ニュアンス】「自分を向上させたいなら、まず他人を向上させよ」。利己的な目標（自分を高めること）を達成するための最善の手段が、利他的な行動（他者への貢献）であるという、パラドックス（逆説）を用いた深い教えです。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what と 関係副詞 where】3つの句が並列されています。【語彙・リズム】「できること（能力）を、持っているもの（資源）で、今いる場所（環境）で」。できない理由（お金がない、時間がない、場所が悪い）を完全に封じ込め、手元にあるカードだけで勝負せよという、ルーズベルト大統領の実践的な名言です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 who】who never made a mistake が A person を修飾する長い主語です。【語彙・ニュアンス】never（一度も〜ない）という強い否定を2回使っています。失敗（mistake）と新しい挑戦（tried anything new）は不可分であり、「無傷であること＝何も行動していない証拠」とアインシュタインが喝破しています。</t>
-  </si>
-  <si>
-    <t>【文法：There is/are 構文】no traffic jams（交通渋滞は一つもない）という強い否定。【語彙・イディオム】go the extra mile は「（期待された以上に）もう一歩余分に努力する」という頻出イディオム。普通の人が努力をやめる地点から「さらにその先（the extra mile）」には、ライバルがいない（渋滞していない）ため、実は成功しやすいという秀逸なメタファーです。</t>
-  </si>
-  <si>
-    <t>【文法：too...to構文と助動詞の完了形】might have been は「（過去に）なれたかもしれない状態」。【語彙・ニュアンス】「〜になるのに遅すぎることはない」。過去の可能性（あの時こうしていれば…）を振り返って後悔するのではなく、今からでもその理想の姿を目指せばよいという、時間と可能性に対する究極の肯定です。</t>
-  </si>
-  <si>
-    <t>【文法：同等比較の否定 not as...as】A is not as important as B（AはBほど重要ではない＝Bの方が重要だ）。【語彙・対比】what you get（得る「物」）と what you become（なる「人物像」）。目標達成の真の報酬は、外的な成功（金や地位）ではなく、その過程で変容した内面的な自己成長であるという本質を突いています。</t>
-  </si>
-  <si>
-    <t>【文法：最上級と関係代名詞 which】the most powerful weapon（最も強力な武器）を先行詞とし、which 以下が修飾しています。【語彙・ニュアンス】教育（Education）を、暴力ではなく世界を変革するための「武器（weapon）」と定義。ネルソン・マンデラが、無知こそが差別の温床であり、知性こそが平和的な革命の手段であると宣言した言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞の否定 not -ing】accept not trying で「挑戦しないことを受け入れる」。【語彙・対比】accept failure（失敗を許容する）と can't accept not trying（不挑戦を許容しない）。マイケル・ジョーダンの言葉で、失敗そのものは人間の常（everyone fails）として許せるが、逃げる姿勢だけは絶対に許さないというプロフェッショナルな哲学です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の名詞的用法】To be（存在すること＝生きるか）と not to be（存在しないこと＝死ぬか）。【語彙・ニュアンス】シェイクスピアの『ハムレット』の有名なセリフ。be動詞の最も根源的な意味である「存在する」を使い、人生の究極の選択を、たった6単語で表現した英文学最高峰のフレーズです。</t>
-  </si>
-  <si>
-    <t>【文法：第3文型(SVO)】非常にシンプルで力強い SVO 構文。【語彙・ニュアンス】rules は「支配する、統治する」。ナポレオンの言葉ですが、武力や法律ではなく、「想像力（Imagination）」こそが人間の心を動かし、ひいては世界を動かす原動力であるという洞察です。</t>
-  </si>
-  <si>
-    <t>【文法：条件節 If と 不定詞の形容詞的用法】no time to love them（彼らを愛するための時間がない）。【語彙・ニュアンス】judge は「（固定観念で）人を裁く、評価する」。マザー・テレサの言葉で、他人のアラ探しをして評価を下すことにエネルギーを使っていると、その人を受け入れ愛する余裕がなくなるという、愛と批判のトレードオフを説いています。</t>
-  </si>
-  <si>
-    <t>【文法：受動態の並列】are made（作られる）と (are) born（生まれつく）の対比。【語彙・ニュアンス】天才（Geniuses）は、生まれ持った才能（born）によるものではなく、後天的な努力や環境によって作り上げられる（made）ものだという、成長マインドセットを端的に表した言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：名詞を修飾する形容詞】foundational（基礎となる、根本的な）が key を修飾。【語彙・ニュアンス】ピカソの言葉。どんなに素晴らしいアイデアや計画があっても、「行動（Action）」が伴わなければ何の意味もない。すべての成功のドアを開けるたった一つの鍵は実行力であるという力強い S=C の構文です。</t>
-  </si>
-  <si>
-    <t>【文法：無生物主語と前置詞 with】旅（journey）が自ら「始まる（begins）」という擬人化表現。with は「〜と共に（起点）」を表します。【語彙・ニュアンス】老子の言葉の英訳「千里の道も一歩から」。a thousand miles（果てしなく遠い目標）と one step（今できる最小の行動）の極端なスケールの対比が、最初の一歩の重要性を際立たせています。</t>
-  </si>
-  <si>
-    <t>【文法：倒置構文】本来は Opportunity lies in the middle of difficulty.。場所を示す句を文頭に置き、主語と動詞を倒置させています。【語彙・ニュアンス】lies は「横たわる、存在する」。困難が過ぎ去った後ではなく、まさに「困難のど真ん中（In the middle of）」にこそチャンスが隠れているという、アインシュタインの視点の転換です。</t>
-  </si>
-  <si>
-    <t>【文法：第3文型(SVO)】2つの主語（A and B）が、目的語（all things）を conquer する。【語彙・ニュアンス】Energy（爆発的な活力）と persistence（粘り強さ・持続力）。瞬発力と持久力の両輪があれば、どんな困難（all things）も「征服できる（conquer）」という、ベンジャミン・フランクリンの合理的な成功法則です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 who と名詞化された疑問詞】a why（理由・目的）と any how（どんな手段・苦難）を名詞として使っています。【語彙・ニュアンス】ニーチェの言葉。生きるための「確固たる理由（why）」さえあれば、人間は「どんな過酷な状況や方法（how）」にも耐えられる（bear）という、人間の精神の強靭さを表現した名言です。</t>
-  </si>
-  <si>
-    <t>【文法：強調構文 It is...thatの省略と Not A but B】It is not A (that) we conquer but B。私たちが征服するのはAではなくBだ。【語彙・ニュアンス】the mountain（外的な困難）と ourselves（内的な弱さ）。登山家エドモンド・ヒラリーの言葉ですが、真に打ち勝つべき相手は、目の前の障害物ではなく、諦めようとする自分自身の心であるという真理です。</t>
-  </si>
-  <si>
-    <t>【文法：副詞の反復による強調】否定の命令文 Don't give up を、Never（絶対に〜ない）を使って極限まで強めています。【語彙・ニュアンス】チャーチル首相の伝説的なスピーチ。Never を3回繰り返すという非常にシンプルかつ感情的な修辞法が、国家的危機の最中において人々の心を一つにする圧倒的な力を持ちました。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 what の倒置】本来は You become what you think.。what節を文頭に出して強調しています。【語彙・ニュアンス】ブッダの言葉の英訳。すべては「心（mind）」で決まる。自分が思い描いた思考（What you think）が、そのまま現実の自分（become）を創り出すという、引き寄せの法則の根本思想です。</t>
-  </si>
-  <si>
-    <t>【文法：第2文型(SVC)】SとCをイコールで結ぶ最も短い形。【語彙・メタファー】フランクリンの言葉。「時間は金なり」。時間という目に見えない概念を、お金という目に見える価値に置き換え、時間を浪費することは資産を捨てていることと同義であると警鐘を鳴らしています。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞（能動態と受動態）の並列】To love（愛すること）と (to) be loved（愛されること）。主語が複数に見えますが、一つの概念として is で受けています。【語彙・比喩】feel the sun from both sides（両側から太陽を感じる）。愛し愛されるという双方向の関係性を、温かい太陽の光に全身を包まれる至福の感覚に例えた美しい詩的な表現です。</t>
-  </si>
-  <si>
-    <t>【文法：命令文の3連打】3つの命令文を接続詞なしで並べることで、リズミカルな格言の響きを作っています。【語彙・対比と数詞】all（すべての人）、a few（少数の人）、none（誰にも〜ない）。シェイクスピアの言葉で、博愛を持ちつつも信頼する相手は慎重に選び、誰に対しても害（wrong）は加えないという、人間関係の黄金律です。</t>
-  </si>
-  <si>
-    <t>【文法：worth -ing の構文】be worth -ing は「〜する価値がある」。【語彙・接頭辞】unexamined は un-(否定) + examine(吟味する、考察する) + -ed(過去分詞)。ソクラテスの言葉で、自らの信念や行動を「深く省みることのない（unexamined）」人生は、人間として生きる価値がないという厳しい哲学の宣言です。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 therefore】therefore（それゆえに）が原因と結果を結びつけます。【語彙・ニュアンス】デカルトの「我思う、ゆえに我あり」。すべてを疑ったとしても、「疑っている自分自身の意識（I think）」の存在だけは否定できない。ゆえに、私の存在（I am = I exist）は確実であるという近代哲学の出発点です。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 but と条件節 if】「人生は一度きりだ（YOLO）」というよくあるフレーズに、but で逆説的に条件を加えています。【語彙・語法】do it right の it は「人生を生きること」。「一度しかない」と嘆くのではなく、正しく（right）全力で生きさえすれば、一度（once）で十分に満足できる（enough）という痛快な名言です。</t>
-  </si>
-  <si>
-    <t>【文法：Get + 形容詞 + -ing】be busy -ing（〜するのに忙しい）の be を get（〜になる）に変え、「〜に専念しろ」という強い命令文にしています。【語彙・対比】living（懸命に生きること）と dying（ただ死を待つこと）。映画『ショーシャンクの空に』のセリフ。人生には「全力で生きる」か「死んでいくのと同じように無気力に過ごすか」の2つの選択肢しかないと迫っています。</t>
-  </si>
-  <si>
-    <t>【文法：be composed of と現在分詞の後置修飾】be composed of は「〜で構成されている」。inhabiting（住み着いている）が a single soul を後ろから修飾しています。【語彙・ニュアンス】アリストテレスの言葉。2つの別々の肉体（two bodies）に、たった一つに融合した魂（a single soul）が宿っている状態こそが愛であるという、非常にロマンチックで形而上的な定義です。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞 without を使った仮定法】Without A で「もしAがなければ」。would be は現在の事実に反する仮定の帰結です。【語彙・ニュアンス】ニーチェの言葉。音楽がない世界など「間違い（mistake）」である。音楽が人間の生にとっていかに不可欠な芸術であるかを、仮定法を用いた強烈な言い回しで讃えています。</t>
-  </si>
-  <si>
-    <t>【文法：前置詞 like による直喩(Simile)】A is like B で「AはBのようだ」。【語彙・比喩の構造】room（部屋）と body（肉体）、books（本）と soul（魂）がそれぞれ対応しています。本がない部屋は、生命や知性の宿っていない空っぽの入れ物に過ぎないという、キケロの読書への賛歌です。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞の省略と連鎖関係代名詞】the love (which) we think (that) we deserve。私たちが「自分にふさわしい」と思う愛。【語彙・心理的ニュアンス】deserve は「〜に値する、ふさわしい」。映画『ウォールフラワー』のセリフ。自己肯定感が低い人は、無意識のうちにひどい扱い（劣った愛）を受け入れてしまうという、人間の深層心理を突いた言葉です。</t>
-  </si>
-  <si>
-    <t>【文法：比較の否定構文】nothing ... so much as (forgiving)（許すことほど〜なものはない）。ここでは as 以下が文脈から省略されています。【語彙・ユーモアと皮肉】オスカー・ワイルドの言葉。敵を許すのは「慈悲」のためではなく、相手を最も「イライラさせる（annoys）」ための最高の復讐であるという、皮肉たっぷりのウィットに富んだ表現です。</t>
-  </si>
-  <si>
-    <t>【文法：命令文】状態や役割を指定する be を使った命令文。【語彙・メタファー】人生を「物語（story）」に見立て、他人の人生の脇役として生きるのではなく、自分自身の人生の「主人公（hero）」として主体的に生きよというメッセージです。</t>
-  </si>
-  <si>
-    <t>【文法：第2文型(SVC)】幸福 ＝ 温かい子犬。抽象名詞を極めて具体的な名詞で定義しています。【語彙・イメージ喚起】スヌーピー（ピーナッツ）の作者チャールズ・シュルツの言葉。幸福とは、遠くにある偉大な目標ではなく、「温かい子犬を抱きしめる」ような、日常のささやかな肌の温もりの中にあることを詩的に表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 that の先行詞の離反】that scares you が修飾しているのは everyday ではなく one thing です。【語彙・ニュアンス】scares は「〜を怖がらせる」。エレノア・ルーズベルトの言葉。安全地帯（コンフォートゾーン）にとどまらず、毎日一つ、あえて自分が「怖い」と感じることに挑戦し続けることが成長の秘訣であると説いています。</t>
-  </si>
-  <si>
-    <t>【文法：過去分詞の名詞的用法と比較級】Well done（立派になされたこと＝行動）と well said（立派に語られたこと＝言葉）を比較しています。【語彙・対比と韻】well という共通の副詞を使いながら、done と said の対比で「不言実行」の価値を端的に表したフランクリンの言葉です。口先より行動が優るという普遍的な真理です。</t>
-  </si>
-  <si>
-    <t>【文法：動名詞と前置詞句】is の補語が walking...。with no loss of は「〜を失うことなく」という付帯状況。【語彙・ニュアンス】チャーチルの言葉。成功とは、一直線にゴールへ向かうことではなく、「失敗から次の失敗へと歩き続けること」。その際、唯一の条件は「情熱（enthusiasm）を失わないこと」であると定義しています。</t>
-  </si>
-  <si>
-    <t>【文法：関係代名詞 who による2つの動詞の並列】who が knows と loves という2つの動詞を結んでいます。【語彙・ニュアンス】友人とは、あなたの長所だけでなく、欠点や暗い過去も「すべて（all）」知った上で、それでもなお（still）愛してくれる人のことである。still という副詞が深い無条件の愛を表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：as if + 仮定法過去 / be to不定詞】as if（まるで〜かのように）。were to は「未来の実現性の低い仮定」や「運命」を表します。【語彙・対比の極致】ガンジーの言葉。生きる態度（Live）は「明日死ぬ」という極限の切迫感で。学ぶ態度（Learn）は「永遠に生きる」という悠久のスケールで。対極の仮定を並べた美しい名言です。</t>
-  </si>
-  <si>
-    <t>【文法：使役動詞 make と否定の副詞句】make O C（OをCの状態にさせる）。without は「〜なしに」。【語彙・主体性】inferior は「劣等感」。consent は「同意、許可」。エレノア・ルーズベルトの言葉で、他人があなたを見下そうとしても、あなた自身が心の中で「同意」しない限り、劣等感を感じることはないという自尊心の防壁です。</t>
-  </si>
-  <si>
-    <t>【文法：不定詞の主語と動詞の省略】前半は To err（過ちを犯すこと）is human（人間の性）。後半は To forgive (is) divine と、反復を避けるため is が省略されています。【語彙・対比】err（エラーをする）と forgive（許す）。human（人間の次元）と divine（神の次元）。アレキサンダー・ポープの言葉で、過ちは誰にでもあるが、それを許す行為は神聖な高みに達することだと表現しています。</t>
-  </si>
-  <si>
-    <t>【文法：極小の第2文型(SVC)】名詞 + be動詞 + 名詞。余計な装飾を一切削ぎ落とした形。【語彙・本質】フランシス・ベーコンの有名な言葉「知は力なり」。知識を持つことそのものが、世界をコントロールし、物理的な力や富に匹敵する「権力・力（power）」になるというルネサンス期の強い信念です。</t>
-  </si>
-  <si>
-    <t>【文法：代名詞 one と最上級】one は path を指す反復回避の代名詞。the easiest で「最も簡単な」。【語彙・ニュアンス】正しい道（the right path）と 楽な道（the easiest one）。道徳的な正しさや成長をもたらす選択は、往々にして困難を伴うものであるという、人生の選択における真理を優しく（Sometimesを添えて）諭しています。</t>
-  </si>
-  <si>
-    <t>【文法：接続詞 as】just as you are で「ありのままのあなたで」。as は「〜の状態のまま」という意味を作ります。【語彙・自己肯定】enough は「十分な」。他者と比べたり、何かを付け足したりしなくても、あなたの存在そのものが既に「満ち足りている（enough）」という、究極の自己受容と肯定のメッセージです。</t>
-  </si>
-  <si>
-    <t>【文法：使役動詞 let の命令文】let O do（Oに〜させるままにする）。【語彙・解放】go は「行く、去る」。直訳は「それを去るままにしておけ」。執着、怒り、過去の未練など、自分を縛り付けているあらゆるもの（it）を「手放しなさい、解放しなさい」という意味の、非常にポピュラーで癒しの力を持つフレーズです。</t>
-  </si>
-  <si>
-    <t>【文法：過去形の3連打（並行法）】3つの第1文型（SV）を接続詞なしで並べる「アシュンデトン（接続詞省略）」という修辞技法です。【語彙・リズム】ユリウス・カエサルの「来た、見た、勝った（Veni, vidi, vici）」。同じ代名詞 I と短い過去形の動詞を3回リズミカルに叩きつけることで、電光石火の圧倒的な勝利とスピード感を表現した歴史的な名文句です。</t>
-  </si>
-  <si>
-    <t>【文法：関係副詞 Where を使った副詞節】Where S V で「SがVする場所には」。there is 構文を2つ重ねています。【語彙・ニュアンス】ガンジーの言葉。愛が存在する場所（条件）にのみ、真の生命や人生（life）が存在する。愛と生命を不可分のものとして結びつけた、シンプルで美しい哲学です。</t>
   </si>
   <si>
     <t>【単語解説】
@@ -4919,7 +4124,6 @@
 ・第2文型(SVC)：Stay（V）+ hungry/foolish（C）。「be動詞」と同じS=Cの関係ですが、「stay」を使うことで「その状態を維持し続けろ」という強い継続の意志が強調されています。
 【背景・ニュアンス】
 スティーブ・ジョブズが2005年のスタンフォード大学卒業式辞の結びで語った有名な言葉。元々は雑誌『全地球カタログ』最終号の裏表紙のメッセージです。現状に満足せず（hungry）、他人の目や常識を気にして縮こまることなく（foolish）、常に新しいことに挑戦し続けよという強烈なエールです。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>【単語解説】
@@ -4927,11 +4131,10 @@
 ・important：[形] 重要な
 ・knowledge：[名] 知識
 【文法解説】
-・比較級：A is more [形容詞] than B（AはBよりも〜だ）の構文。important は音節が多いため、-er ではなく more を使います。
+・比較級：「A is more [形容詞] than B」の構文。importantは音節が多いため、-erではなくmoreを用います。
 ・抽象名詞の対比：imagination（心に描くこと）と knowledge（知っている状態）という2つの抽象名詞を対比させています。
 【背景・ニュアンス】
 1929年のインタビューでのアインシュタインの発言。「知識は現在分かっていることに限られるが、想像力は世界を包み込み、進歩を生み出す」と語りました。すでに確定した過去〜現在の枠組みである「知識」よりも、ゼロから未来を創り出す「想像力」の価値を高く評価した深い言葉です。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>【単語解説】
@@ -4939,11 +4142,10 @@
 ・quit：[動] やめる
 ・begin：[動] 始める
 【文法解説】
-・不定詞の用法：The way を to get started（始めるための）が後ろから修飾（形容詞的用法）。is の後は to quit... and begin...（〜をやめて･･･し始めること）となり、補語(C)として機能しています（名詞的用法）。
-・動名詞：quit は後ろに動名詞(-ing)しか取れない動詞です。talking と doing で韻を踏むように形を揃えています。
+・不定詞の形容詞的用法と名詞的用法：The wayを後ろから「to get started（始めるための）」が修飾。isの後の「to quit...and begin...」は補語(C)となる名詞的用法です。
+・動名詞と対句：quitは後ろに動名詞(-ing)しか取れない動詞。talkingとdoingを「-ing」で揃えることで、視覚的・聴覚的なリズムを整えています。
 【背景・ニュアンス】
 ディズニーリゾートの構想など、数々の夢を現実にしてきたウォルト・ディズニーの行動哲学。「あれこれと口で語るよりも、まず手を動かせ」という、夢を実現するための極めて実務的でストレートなアドバイスです。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>【単語解説】
@@ -4951,11 +4153,10 @@
 ・impossible：[形] 不可能な
 ・until：[接] 〜するまで（ずっと）
 【文法解説】
-・第2文型(SVC)：It seems impossible で「（主観的に）不可能のように思える」。
-・受動態：until it's done の is done は「（客観的な事実として）成し遂げられる」という受動態。seem（主観）と is done（客観）が美しい対比になっています。
-【背景・ニュアンス】
-27年間もの投獄生活を経て、南アフリカの反アパルトヘイト運動を勝利に導いたネルソン・マンデラの言葉。どんなに絶望的で高く見える壁でも、やり遂げてしまえばそれは「当たり前の現実」になる。途中で決して諦めないことの重要性を、自身の壮絶な経験から説いています。</t>
-    <phoneticPr fontId="1"/>
+・第2文型(SVC)：It seems impossibleで「（主観的に）不可能のように思える」。
+・受動態：until it's doneのitは前述の「不可能に思えること」を指し、is doneは「（客観的な事実として）成し遂げられる」という受動態。seem（主観）と is done（客観）の対比になっています。
+【背景・ニュアンス】
+27年間もの投獄生活を経て、南アフリカの反アパルトヘイト運動を勝利に導き大統領となったネルソン・マンデラの言葉。どんなに絶望的で高く見える壁でも、やり遂げてしまえばそれは「当たり前の現実」になります。途中で決して諦めないことの重要性を自身の壮絶な経験から説いています。</t>
   </si>
   <si>
     <t>【単語解説】
@@ -4963,11 +4164,2700 @@
 ・wish：[動] 願う
 ・world：[名] 世界
 【文法解説】
-・関係代名詞（目的格）：that が先行詞 the change を後ろから修飾しています。「wish to see」の目的語(O)が欠けており、それが the change に該当します。
-・名詞の選択：動詞の Change（変われ）ではなく Be the change（変化そのものになれ）と名詞を使うことで、スケールの大きな表現になっています。
+・関係代名詞の目的格：changeを先行詞とし、that以下が後ろから修飾しています。see（見る）の目的語(O)が欠けており、それが先行詞のchangeです。
+・名詞の選択：単に動詞で「Change（変われ）」と言うのではなく、「Be the change（変化そのものになれ）」と名詞を用いることで、存在そのものの在り方を問う力強い表現になっています。
 【背景・ニュアンス】
 ガンジーの思想を要約した言葉として広く知られています。世界が変わるのを待ったり、他人に文句を言ったりするのではなく、まず「自分自身の行動やあり方」を変えること。あなた自身の存在が世界の変革の象徴になれという、自己変革こそが社会変革の第一歩であるという深い哲学です。</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【単語解説】
+・have：[動] 持つ、ある
+・dream：[名] 夢
+【文法解説】
+・第3文型(SVO)：主語(I) + 動詞(have) + 目的語(a dream)という、英語の最も基本かつ力強い文型です。
+・冠詞の修辞的効果：不定冠詞の「a」が重要です。dreams（複数の夢）や the dream（特定の夢）ではなく、「a dream（ある一つの明確な夢）」と単数形にすることで、聴衆の意識を一気にフォーカスさせています。
+【背景・ニュアンス】
+1963年のワシントン大行進でのキング牧師の歴史的な演説。人種差別撤廃と平等な社会の実現を、論理的な要求だけでなく、誰もがイメージできる「一つの夢」として語り、アメリカ社会の良心を揺さぶり歴史を動かした名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fail：[動] 失敗する
+・way：[名] 方法
+・work：[動] 機能する、うまくいく
+【文法解説】
+・現在完了形：I have not failed は過去から現在までの全経験における「失敗」を否定しています。
+・関係代名詞の主格：「that won't work」の that は ways を修飾する主格の関係代名詞。won't (will not) は「どうしても〜しない」という強い拒絶を表します。
+【背景・ニュアンス】
+白熱電球の発明などで数千回の試行錯誤を重ねたエジソンの名言。fail（失敗する）というネガティブな概念を、find（発見する）というポジティブな行動へと再定義しています。失敗は成功できない方法を見つけたという「学習」であるという前向きな思考です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・like：[前] 〜のような
+・balance：[名] バランス、均衡
+・keep moving：動き続ける
+【文法解説】
+・前置詞と動名詞：like は動詞ではなく前置詞で、後ろに動名詞 riding を取ります。
+・keepの2つの語法：keep your balance（第5文型：OをCに保つ）と、keep moving（動名詞を目的語に取り「〜し続ける」）という、異なる使われ方が巧みに対比されています。
+【背景・ニュアンス】
+アインシュタインが息子に宛てた手紙の中の言葉。「バランスを保つ（静）」ためには「動き続ける（動）」しかないという物理法則を、立ち止まらずに歩み続けるべき人生の真理に重ね合わせています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・limit：[名] 限界、制限
+・realization：[名] 実現
+・doubt：[名] 疑念、疑い
+【文法解説】
+・名詞構文の対比：「realization of tomorrow（明日への実現）」と「doubts of today（今日の疑念）」という名詞句が美しく対比されています。
+・助動詞will：単なる未来ではなく「必ず〜になるだろう」という強い確信（推量）を表します。
+【背景・ニュアンス】
+第32代大統領F・ルーズベルトの言葉。大恐慌や世界大戦という国難の中で、国民の不安や恐怖こそが未来を創る最大の障害であると説きました。未来を阻む原因は外部の環境ではなく、現在の自分の内面（疑い）にあることを強調しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・whatever：[代] 何であれ
+・good：[形] 立派な、良い
+・one：[代] 者、人、物
+【文法解説】
+・譲歩の複合関係代名詞：Whatever you are は「あなたが何者であろうとも」という譲歩（〜だとしても）の副詞節を作ります。
+・代名詞one：既出の単語の反復を避ける代名詞ですが、ここでは「どのような職業や立場（you are）であっても、その中での最高形」を代入できる器として機能しています。
+【背景・ニュアンス】
+リンカーンの言葉。自分の仕事や立場に貴賤をつけず、どのような環境に置かれてもその選んだ道でベストを尽くし、誠実な人間でありなさいという、職業倫理と人生の矜持を表す短い名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・final：[形] 最終的な、決定的な
+・fatal：[形] 致命的な
+・count：[動] 重要である
+【文法解説】
+・強調構文：It is...thatの構文。「重要（counts）なのは、続ける勇気だ」と、thatの前の言葉（the courage to continue）を強調しています。
+・頭韻法（Alliteration）：final と fatal で「f」と「l」の音を揃え、美しいリズムを生み出しています。
+【背景・ニュアンス】
+第二次世界大戦下のイギリスを導いたチャーチルの不屈の哲学。成功も失敗も一時的な状態に過ぎず、プロセスを継続する意志こそが本質的な価値を持つという、リーダーとしての揺るぎない信念です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・begin：[動] 始まる
+・smile：[名] 微笑み
+【文法解説】
+・第1文型(SV)：begin を自動詞として使い、「平和のほうから自発的に始まる」というニュアンスを持たせています。
+・前置詞with：「〜を伴って」という付帯状況を表します。
+【背景・ニュアンス】
+カトリック修道女マザー・テレサの言葉。平和を国家間の大きな政治問題としてだけでなく、個人の身近な「微笑み」という最小の行動から種をまくべきだという、彼女らしい慈愛と力強さに満ちた教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・belong to：[動] 〜に属する、〜のものである
+・those who：[代] 〜する人々
+・beauty：[名] 美しさ
+【文法解説】
+・関係代名詞の頻出構文：those who は「〜な人々」を表します。
+・believe in の語法：単なる believe（事実だと信じる）を超え、believe in を使うことで「その存在や価値を深く信頼する」という強いニュアンスを出しています。
+【背景・ニュアンス】
+国連人権委員会の初代委員長も務めたエレノア・ルーズベルトの言葉。未来は受動的に待つものではなく、自らの夢の「美しさ」に全幅の信頼を寄せ、行動する人々の手に委ねられるという励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・judge：[動] 判断する
+・harvest：[名] 収穫
+・reap：[動] 刈り取る
+・seed：[名] 種
+【文法解説】
+・Not A but B 構文：「AではなくB」。judge A by B（AをBの基準で判断する）という熟語と組み合わせています。
+・関係代名詞の対比：you reap（刈り取る）と that you plant（植える）という関係代名詞節が、それぞれの名詞（harvest と seeds）を後ろから修飾し対比を際立たせています。
+【背景・ニュアンス】
+『宝島』の著者スティーヴンソンの言葉。農業のメタファーを用いて、結果（収穫）という目に見える果実よりも、その日に行った努力（種まき）という過程こそを重んじるべきだという教訓です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・impossible：[形] 不可能な
+・itself：[代] それ自体（強調）
+・possible：[形] 可能な
+【文法解説】
+・代名詞の強意用法：itself が直前の the word を強調し「その言葉自体が」という意味を作っています。
+・言葉遊び（Pun）：impossible（不可能）という単語を、im-possible ではなく I'm possible（私は可能だ）と分解して読む高度な修辞技法です。
+【背景・ニュアンス】
+女優でありユニセフ親善大使も務めたオードリー・ヘプバーンの言葉。否定的な状況や単語の中にさえ、常に肯定的な可能性や宣言が隠れていることを見出す、彼女の明るくエレガントな精神性が表れています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・whether：[接] 〜であろうと
+・right：[形] 正しい、その通りである
+【文法解説】
+・譲歩の副詞節：「Whether A or B（AかBかどちらでも）」。ここでは you think you can と you think you can't という2つの完全な文を対比させています。
+・短い主節：主節の you're right が非常に短いため、強い断定の響きを持っています。
+【背景・ニュアンス】
+自動車王ヘンリー・フォードの言葉。「できると思えばできるし、できないと思えばできない（どちらにせよ、あなたの思い込み通りになる）」。成功の可否は外部環境ではなく、本人のマインドセットで決まるという信念です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・toward：[前] 〜の方へ
+・sunshine：[名] 日光
+・shadows：[名] 影
+・behind：[前] 〜の後ろに
+【文法解説】
+・命令文 + and：「〜しなさい、そうすれば･･･」。前半の命令が「条件」、後半の and 以下がその「結果」を表します。
+・前置詞の対比：toward（前方へ）と behind（後方へ）という方向を示す前置詞で、視点の転換を物理的に描写しています。
+【背景・ニュアンス】
+アメリカの詩人ホイットマンの言葉。顔を光（希望やポジティブなもの）に向け続ければ、影（悩みや過去のネガティブなもの）は自然と視界から消え、背後に落ちる。どこに意識を向けるかという重要性を説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・happen to：[動] 〜に起こる
+・react to：[動] 〜に反応する
+【文法解説】
+・名詞節の対比：what happens to me（起きること）と how I react to it（どう反応するか）という2つの名詞の塊が、is の補語になっています。
+・数値化：10%と90%という数値の対比が、人生における自己主導権の大きさを明確に視覚化しています。
+【背景・ニュアンス】
+牧師・作家であるチャールズ・スウィンドルの言葉。起きた出来事（自分ではコントロールできない10%）よりも、それに対する自分の態度や解釈（自分で決められる90%）こそが人生の質を決定するという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・enough：[形] 十分な
+・apply：[動] 応用する、適用する
+・willing：[形] 意欲がある
+・do：[動] 実行する
+【文法解説】
+・並行法（Parallelism）：全く同じ構造の文を2回繰り返す修辞技法で、リズミカルな説得力を生んでいます。
+・動名詞と助動詞：Knowing と Willing を主語に置き、must（〜しなければならない）という強い義務でアクションへの移行を促しています。
+【背景・ニュアンス】
+世界的な武道家・俳優のブルース・リーの言葉。頭で理解し、心で願うだけでは不十分であり、それを現実の肉体的なアクション（apply, do）に落とし込んでこそ意味があるという実践的な哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・matter：[動] 重要である、問題である
+・slowly：[副] ゆっくりと
+・as long as：[接] 〜である限り（は）
+【文法解説】
+・形式主語と真主語：It は形式主語で、真の主語は how slowly you go（どんなにゆっくり進むか）という名詞節です。
+・条件の接続詞：as long as は強い条件を示します。否定語が並び「止まらないこと」の価値を際立たせています。
+【背景・ニュアンス】
+古代中国の思想家、孔子の教え。他者との比較やスピード競争に惑わされず、一歩ずつでも「立ち止まらずに継続」し続けることこそが、最終的に目的地に到達するための唯一確実な方法であるという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・yourself：[代] 自分自身
+・everyone else：[名] 他の全員
+・already taken：既に取られている（席が埋まっている）
+【文法解説】
+・命令文：Be yourself（自分自身であれ）。
+・セミコロンと受動態：セミコロン（;）は理由を補足する接続詞（becauseなど）に近い役割を果たします。is already taken は現在完了の受動態で「すでに予約済みの状態である」ことを表します。
+【背景・ニュアンス】
+アイルランドの劇作家オスカー・ワイルドらしい、機知とユーモアに富んだ格言です。他人の真似をして理想の誰かになろうとしても、その人の席はすでに埋まっている。自分にしかなり得ない「オリジナルな自分自身」の価値を逆説的に説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・country：[名] 国、国家
+・ask not：問うなかれ（文語的な否定）
+【文法解説】
+・古風な命令文：本来 Don't ask のところを Ask not とすることで、格調高く宣言的な響きを持たせています。
+・交錯配列法（Chiasmus）：「country - do - you」という順序を、後半で「you - do - country」とX字型に反転させる、演説における最高峰の修辞技法が使われています。
+【背景・ニュアンス】
+ジョン・F・ケネディ大統領の就任演説（1961年）の最も有名な一節。国民に対して、政府へ受動的に依存するのではなく、自発的な貢献と責任を求めることで、国家の新しい時代の幕開けを力強く告げました。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・believe：[動] 信じる
+・halfway there：道半ばにいる、目標の半分は達成した
+【文法解説】
+・命令文 + and：「〜しなさい、そうすれば･･･」。
+・副詞のthere：there は「そこへ（目的地へ）」という副詞として使われ、目標達成のプロセスを空間的なイメージ（道のりの半分まで来ている）で表現しています。
+【背景・ニュアンス】
+第26代アメリカ合衆国大統領セオドア・ルーズベルトの言葉。技術を磨いたり環境を整えたりする前に、まず「自分ならできる」という確信（マインドセット）を持つだけで、成功への道のりの50%はすでに完了しているという力強い教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・strike：[名] ストライク（空振り）
+・bring：[動] 連れてくる、もたらす
+・closer：[副] より近くに
+・home run：[名] ホームラン
+【文法解説】
+・無生物主語のSVO：無生物（Every strike）が me（人）を目的語に取り、closer（補語的な副詞）へ導くという英語特有の構文です。
+・ニュアンス：失敗を「接近」という前進の動作で捉えています。
+【背景・ニュアンス】
+野球界の伝説的打者ベーブ・ルースの言葉。三振（失敗）という一見ネガティブな結果も、それを恐れずバットを振るたびに、次のホームラン（成功）へ確率的にも経験的にも近づいているという、圧倒的にポジティブな解釈です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・purpose：[名] 目的
+・lives：[名] 人生（life の複数形）
+【文法解説】
+・第2文型(SVC)：The purpose（主語）= to be happy（補語）。非常にシンプルで純度の高い文構造です。
+・複数形のlives：特定の個人の人生ではなく、私たち全人類に共通する普遍的な真理であることを lives と複数形にすることで示しています。
+【背景・ニュアンス】
+チベット仏教の最高指導者ダライ・ラマ14世の言葉。人生の複雑な問いや悩みを、ただ一点「幸福であること」に集約させ、慈悲と心の平穏こそが人間の本質的なゴールであると迷いなく断定しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fine：[形] 良い、構わない
+・celebrate：[動] 祝う
+・heed：[動] 耳を傾ける、心に留める
+・lesson：[名] 教訓
+【文法解説】
+・形式主語の対比：2つの形式主語 It's fine to... と it is more important to... を but で繋いで対比させています。
+・比較級：more important を使い、成功の喜びよりも失敗の分析に明確な重きを置いています。
+【背景・ニュアンス】
+Microsoftの共同創業者ビル・ゲイツの言葉。ビジネスの成功に安住して喜ぶのは構わないが、失敗から得られるフィードバック（教訓）に耳を傾ける謙虚さこそが、次なる成長の最大のエンジンであるとする合理主義の姿勢です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・turn：[動] 変える
+・wound：[名] 傷、トラウマ
+・wisdom：[名] 知恵、叡智
+【文法解説】
+・語法：turn A into B（AをBに変える）。
+・頭韻法（Alliteration）：wounds と wisdom で「w」の音から始まる単語を対置させ、短く記憶に残りやすいリズミカルな命令文を作っています。
+【背景・ニュアンス】
+アメリカの圧倒的な影響力を持つ司会者オプラ・ウィンフリーの言葉。自身の過酷な過去を乗り越えた経験から、受けた傷を単なる痛みや恨みで終わらせず、人生の深みや他者への共感という「知恵」に昇華せよというメッセージです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・float：[動] 舞う、ふわふわ浮かぶ
+・butterfly：[名] 蝶
+・sting：[動] チクリと刺す
+・bee：[名] 蜂
+【文法解説】
+・直喩法（Simile）：like（〜のように）を使い、他のものに例える修辞技法です。
+・対比と命令文：float と sting、butterfly と bee。相反する「軽やかさ」と「鋭さ」を具体的イメージで対比させ、命令文の形で表現しています。
+【背景・ニュアンス】
+伝説のプロボクサー、モハメド・アリが自らのボクシングスタイルを形容した有名な言葉。華麗なフットワークと一撃の鋭さを両立させる、プロとしての矜持と究極の美学がたった8単語に凝縮されています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・courage：[名] 勇気
+・attempt：[動] 試みる、挑戦する
+【文法解説】
+・仮定法過去：If we had no...（もし〜がなかったら）と、現在の事実とは異なる仮定の帰結（どうなってしまうだろうか）を表しています。
+・不定詞の形容詞的用法：courage を to attempt anything（何かを試みるための）が後ろから修飾しています。
+【背景・ニュアンス】
+オランダの画家ゴッホの言葉。生前は評価されずとも、恐れずに独自の色彩と筆致を試み（挑戦し）続けた彼にとって、挑戦する勇気のない人生は色彩のない虚無と同じであるという、生に対する切実な反語的メッセージです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・tragic：[形] 悲劇的な
+・funny：[形] 面白い、滑稽な
+【文法解説】
+・仮定法過去：If it weren't funny（もし面白くなければ）。be動詞に was ではなく weren't を使う伝統的な仮定法の用法です。
+・対比：tragic（悲劇）と funny（喜劇）という正反対の概念を if で繋いでいます。
+【背景・ニュアンス】
+車椅子の天才物理学者スティーヴン・ホーキング博士の言葉。ALSという難病と戦いながら宇宙の真理を探求した彼は、どんなに過酷な運命であっても、そこにユーモア（funny）を見出すことが生きる救いになると説きました。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・predict：[動] 予測する
+・future：[名] 未来
+・create：[動] 創り出す
+【文法解説】
+・不定詞の対比：The best way を to predict が修飾し、結論の補語として to create が置かれています。
+・ニュアンス：predict（事前に言う＝当てる）と create（ゼロから創り出す）という動詞の対比が鮮やかです。
+【背景・ニュアンス】
+経営学者ピーター・ドラッカー（エイブラハム・リンカーンなどの言葉としても知られる）の名言。未来は水晶玉を覗き込んで受動的に「当てる」ものではなく、自らの手と行動で能動的に「創る」ものであるという主体性の哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・great：[形] 偉大な
+・small：[形] 小さな、些細な
+・way：[名] やり方、方法
+【文法解説】
+・条件節 If と命令文：「もし〜できないなら、･･･しなさい」。
+・副詞句の修飾：in a great way（偉大なやり方で）が、動詞 do を修飾する副詞句として働いています。結果の大小ではなくプロセスの質を指定しています。
+【背景・ニュアンス】
+成功哲学の提唱者ナポレオン・ヒル（またはキング牧師）の言葉。歴史に残るような偉業（great things）ができなくても嘆く必要はない。目の前の些細な仕事（small things）に、偉大な献身と誇りを持って取り組むことこそが尊いという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・thought：[名] 思考、考え方
+・world：[名] 世界
+【文法解説】
+・命令文 + and：「思考を変えよ、そうすれば世界が変わる」。
+・原因と結果：thoughts（内面的な思考）という「原因」が、world（自分を取り巻く外的な世界）という「結果」をダイレクトに決定づける構造です。
+【背景・ニュアンス】
+「ポジティブ・シンキング」を提唱したノーマン・ヴィンセント・ピールの言葉。現実世界が厳しいから不幸なのではなく、自分の思考の癖が世界を厳しく見せている。内面の捉え方を変えれば、体験する現実（世界）は一変するという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・miss：[動] 外す、逃す
+・shot：[名] シュート、打つこと
+・take：[動] （行動を）起こす、実行する
+【文法解説】
+・関係代名詞の省略：the shots と you の間に目的格の that/which が省略されています。「あなたが打たないシュート」。
+・パラドックス：「失敗を恐れて打たないこと」が、唯一100%確実に失敗（miss）を約束する方法であるという論理的逆説です。
+【背景・ニュアンス】
+「史上最高のアイスホッケー選手」ウェイン・グレツキーの言葉。スポーツの文脈ですが、人生全般の挑戦に当てはまります。失敗を恐れて行動しないことの愚かさを、100%という数字を使って見事に表現しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・only way：[名] 唯一の方法
+・love：[動] 愛する
+【文法解説】
+・関係代名詞 what：what you do は「あなたがすること（＝仕事）」。the thing which と書き換え可能です。
+・第2文型(SVC)：is でAとBをイコールで結んでいます。
+【背景・ニュアンス】
+Apple創業者スティーヴ・ジョブズの言葉。「偉大な仕事をする」ための絶対条件は、才能や努力の前に、まずその対象を心から「愛する（love）」ことである。情熱こそがすべての創造の源泉であるというジョブズの哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・strive：[動] 懸命に努力する
+・success：[名] 成功、成功者
+・value：[名] 価値
+【文法解説】
+・Not A but rather B：「Aではなく、むしろB」。
+・of + 抽象名詞：to be of value は「be valuable（価値がある）」と同じ意味を作る重要な文法事項です。
+【背景・ニュアンス】
+アインシュタインの言葉。strive（懸命に努力する）の方向性を、世間的な地位や名誉（success）に向けるのではなく、自分が他者や世界にどんな本質的な貢献（value）ができるかへ向けなさいという、深い人間性の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・become：[動] 〜になる
+・think about：[動] 〜について考える
+【文法解説】
+・先行詞を含む関係代名詞 what：become の補語（C）として what 節が丸ごと入っています。「私たちは、私たちが考えていること（そのもの）になる」。
+・反復の暗示：普段無意識に何を考えているかが、そのまま存在を決定づける構造です。
+【背景・ニュアンス】
+自己啓発作家アール・ナイチンゲールの言葉。思考（think）が現実の存在（become）を形作るという「引き寄せの法則」の原点です。ネガティブなことばかり考えればそういう人間に、希望を考えれば希望ある人間になるという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・limited：[形] 限られている
+・waste：[動] 無駄にする、浪費する
+・someone else's：[代] 他の誰かの
+【文法解説】
+・分詞構文 -ing：living... は「〜生きながら（生きることで）」という付帯状況。waste it（時間を浪費する）の具体的な手段を説明しています。
+・冷徹な事実提示：まず limited（有限である）という事実を突きつけてから命令しています。
+【背景・ニュアンス】
+ジョブズのスタンフォード大学卒業式辞の有名な一節。死を意識することで、他人の期待や世間の常識（someone else's life）に従って生きる虚しさを説き、自分の内なる声に従う勇気を持てと学生たちに語りかけました。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・product：[名] 産物、結果
+・circumstances：[名] 環境、状況
+・decision：[名] 決断
+【文法解説】
+・名詞句の対置：「I am not A. I am B.」という強い否定と肯定の連続。
+・ニュアンス：a product of〜（〜の産物）。言い訳の対象（環境）と、責任の所在（決断）を明確に対比させています。
+【背景・ニュアンス】
+『7つの習慣』の著者スティーブン・コヴィーの言葉。生まれ育った環境や不運（circumstances）を言い訳にせず、自らの意思による選択と決断（decisions）こそが今の自分を創ったのだという、自己責任と主体性の極致です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・artist：[名] 芸術家、アーティスト
+・remain：[動] 〜のままでいる
+・once：[接] いったん〜すると
+・grow up：[動] 大人になる
+【文法解説】
+・疑問詞 + 不定詞 / 接続詞 once：how to remain は「どうやって〜のままでいるか」。once は条件を示す接続詞。
+・ニュアンス：問題は「なる（become）」ことではなく「あり続ける（remain）」ことだとしています。
+【背景・ニュアンス】
+天才画家ピカソの言葉。誰もが生まれながらに持つ自由な想像力や芸術性（artist）が、常識を学ぶ社会化の過程（grows up）で失われてしまうことへの警鐘。子どものような純粋な目を持ち続けることの難しさと尊さを説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・revenge：[名] 復讐
+・massive：[形] 巨大な、圧倒的な
+・success：[名] 成功
+【文法解説】
+・最上級とSVC構文：revenge（復讐）の定義を、be動詞（is）を使って書き換える、非常にシンプルかつ究極の構文です。
+【背景・ニュアンス】
+フランク・シナトラの洗練された反撃論。自分を傷つけた相手に直接やり返すのではなく、自分が圧倒的に成功（massive success）して幸せになることこそが、相手にとって最大の痛手（復讐）になるという前向きな言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・avoid：[動] 避ける
+・criticism：[名] 批判
+・nothing：[代] 何もないこと
+【文法解説】
+・コロン（:）による具体化：コロンは「つまり、具体的に言うと」という役割。後ろに3つの命令文（do, say, be）を並べています。
+・反復法：nothing（何もない）を3回繰り返すことで、批判を避けるだけの人生がいかに空虚かを強調しています。
+【背景・ニュアンス】
+アリストテレスの言葉。批判（criticism）を避けるには、何もしない・言わない・何者にもならない人生を送るしかない。裏を返せば「何かを成し遂げようとすれば批判は避けられないのだから、恐れず行動せよ」という逆説的な激励です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・confidently：[副] 自信を持って
+・direction：[名] 方向
+・imagine：[動] 想像する、思い描く
+【文法解説】
+・同族目的語：live the life（人生を生きる）は、動詞と名詞が同じ語源を持つ表現。その後ろに that you have imagined が省略されています。
+・副詞の位置：confidently を動詞 go の直後に置き、行動の「質」を指定しています。
+【背景・ニュアンス】
+アメリカの思想家ソローの力強いメッセージ。頭の中で想像した（imagined）ものを、現実の人生（life）に引きずり下ろすように、自信を持って夢の方向へ進めという行動主義の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・everything：[代] すべてのもの
+・the other side：[名] 向こう側、反対側
+・fear：[名] 恐怖
+【文法解説】
+・現在完了と関係代名詞の省略：Everything (that) you have ever wanted で「あなたがこれまで生きてきて望んだすべてのもの」を主語としています。
+・前置詞 on：on the other side of〜 で「〜の向こう側に」。
+【背景・ニュアンス】
+ジョージ・アデアの言葉。fear（恐怖）を、乗り越えるべき「壁」として視覚化しています。欲しいものはすべて、その壁の「向こう側」にある。恐怖を感じるのは、欲しいものが目の前にある証拠だという励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・start：[動] 始める
+・use：[動] 使う
+・do：[動] する、行う
+【文法解説】
+・関係副詞と関係代名詞：3つの短い命令文が、それぞれ「場所（where you are）」「所有物（what you have）」「能力（what you can）」を目的語として取っています。
+【背景・ニュアンス】
+プロテニス選手アーサー・アッシュの言葉。「もっと条件が整ったら」という言い訳をすべて封じ、今いる場所、今ある道具、今できること。足りないものを数えるのではなく、手元にあるリソースを100%使えという実践的な哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・beauty：[名] 美しさ
+・everyone：[代] 誰もが、全員
+【文法解説】
+・部分否定：not everyone は「全員が〜できるわけではない（見える人もいれば、見えない人もいる）」という重要な文法事項です。
+【背景・ニュアンス】
+孔子の深い洞察。beauty（美しさ）は、対象物の中に客観的に存在するのではなく、それを見つめる人間の「目（see）」や「心」に依存している。美しいものを美しいと感じられる心を育てよという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・wonderful：[形] 素晴らしい
+・improve：[動] 良くする、改善する
+・a single moment：一瞬たりとも
+【文法解説】
+・感嘆文と真主語：How wonderful it is...! で「なんて素晴らしいのだろう！」。that以下がその内容です。
+・助動詞need：nobody need wait の need は、否定語とともに使われる「助動詞（〜する必要がある）」です。
+【背景・ニュアンス】
+『アンネの日記』の著者アンネ・フランクの言葉。世界を良くする（improve）ために、誰かの許可や特別なタイミングを待つ必要はない。今すぐ自分の意思で始められるという、行動への純粋な喜びを表現しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・let go of：[動] 〜を手放す
+・might be：〜なるかもしれない
+【文法解説】
+・what節の対比：what I am（現在の自分）と what I might be（なるかもしれない自分＝可能性）が美しい対比をなしています。
+・助動詞might：可能性を表し、未来への広がりを感じさせます。
+【背景・ニュアンス】
+老子の言葉の英訳。今の自分（地位やプライド）にしがみついている限り、次のステージへは進めない。執着を手放した（let go of）ときにこそ、本来の自分の可能性が開花するという、東洋思想の真髄です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・measure：[動] 測る
+・breath：[名] 呼吸
+・moment：[名] 瞬間
+【文法解説】
+・Not A but B 構文と受動態：「Aによってではなく、Bによって測られる（is measured）」。
+・言葉遊びと修辞：breaths we take（私たちがする呼吸）と、take our breath away（息を呑むほどの感動）という、breath と take を使った鮮やかな言葉遊びです。
+【背景・ニュアンス】
+マヤ・アンジェロウの詩的な名言。人生を「単なる生存期間（呼吸の数）」ではなく、「息を呑むほど感動した瞬間の深さ」で測るべきだという、生の豊かさを讃える言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・happiness：[名] 幸せ
+・readymade：[形] 既製品の
+・action：[名] 行動
+【文法解説】
+・後置修飾：something を形容詞 readymade（既製品の）が後ろから修飾しています。「何か既製品のもの」。
+・代名詞：後半の It は Happiness を指します。
+【背景・ニュアンス】
+ダライ・ラマの言葉。幸福はどこかの棚に完成品として売られている（readymade）ものではない。自らの行動（actions）によって、部品から組み立てて「生み出す（comes from）」ものであるという論理的な説明です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・offer：[動] 提供する、与える
+・rocket ship：[名] ロケット
+・get on：[動] 乗り込む
+【文法解説】
+・受動態と間接疑問文：you're offered は第4文型の受動態で「（あなたが）座席を提示される」。what seat は「どの席か」という間接疑問文です。
+【背景・ニュアンス】
+Meta（旧Facebook）の元COOシェリル・サンドバーグの言葉。a rocket ship（ロケット）は圧倒的な急成長や大チャンスの比喩。千載一遇のチャンスが来た時に、条件（what seat）を気にしてためらうのではなく、まずは飛び乗れという勢いを表現しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・gifted：[形] 才能を与えられている、天賦の才がある
+・attain：[動] 達成する、到達する
+・at whatever cost：どんな犠牲を払っても
+【文法解説】
+・並列の that 節と挿入句：believe の目的語として2つの that 節が and で結ばれています。at whatever cost が2つ目の that 節の中に挿入され強調されています。
+【背景・ニュアンス】
+ノーベル賞を2度受賞したキュリー夫人の言葉。自分の才能（gifted）を信じ、それを絶対に開花させるという強固な信念が、2回の must（〜しなければならない）の反復に表れています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・challenge：[名] 困難、試練
+・overcome：[動] 乗り越える、克服する
+・meaningful：[形] 意味のある
+【文法解説】
+・関係代名詞 what と SVC構文：2つの what 節がそれぞれ「人生を面白くするもの」「人生を意味あるものにするもの」として補語(C)になっています。
+【背景・ニュアンス】
+作家ジョシュア・J・マリンの言葉。Challenges（困難そのもの）と overcoming them（それを克服すること）が対置されています。困難があるからこそ人生は退屈せず、それを乗り越える「過程」にこそ意味（meaningful）が宿るという構造です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・lift up：[動] 引き上げる、向上させる
+・someone else：[代] 他の誰か
+【文法解説】
+・句動詞 lift up：代名詞（yourself）は lift と up の間に挟むのが原則です。
+・条件節と命令文：「もし〜したいなら、･･･しなさい」。
+【背景・ニュアンス】
+教育者ブッカー・T・ワシントンの言葉。「自分を向上させたいなら、まず他人を向上させよ」。利己的な目標（自分を高めること）を達成するための最善の手段が、利他的な行動（他者への貢献）であるという、深いパラドックス（逆説）です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・what：[代] 〜するもの、こと
+・where：[副] 〜する場所で
+【文法解説】
+・関係代名詞と関係副詞：3つの句（what you can, with what you have, where you are）が並列され、簡潔なリズムを生み出しています。
+【背景・ニュアンス】
+セオドア・ルーズベルト大統領の実践的な名言。「できること（能力）を、持っているもの（資源）で、今いる場所（環境）で」。できない理由（お金がない、時間がない、場所が悪い）を完全に封じ込め、手元にあるカードだけで勝負せよという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・mistake：[名] 失敗、間違い
+・try：[動] 試す、挑戦する
+・new：[形] 新しい
+【文法解説】
+・関係代名詞 who：who never made a mistake が A person を修飾する長い主語です。
+・強い否定の反復：never（一度も〜ない）という強い否定を2回使っています。
+【背景・ニュアンス】
+アインシュタインの言葉。失敗（mistake）と新しい挑戦（tried anything new）は不可分であり、「無傷であること＝何も行動していない証拠」であると喝破しています。失敗は挑戦者の勲章です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・traffic jam：[名] 交通渋滞
+・extra mile：[名] もう一歩の努力、特別の努力
+【文法解説】
+・There is/are 構文：no traffic jams（交通渋滞は一つもない）という強い否定で作られています。
+【背景・ニュアンス】
+ロジャー・ストーバックの言葉。go the extra mile は「期待された以上にもう一歩余分に努力する」というイディオム。普通の人が努力をやめる地点から「さらにその先（the extra mile）」には、ライバルがいないため実は成功しやすいという秀逸なメタファーです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・late：[形] 遅い
+・might have been：〜だったかもしれない
+【文法解説】
+・too...to構文：「〜するには遅すぎる」の否定で、「遅すぎることは決してない」。
+・助動詞の完了形：might have been は「（過去に）なれたかもしれない状態」を表します。
+【背景・ニュアンス】
+作家ジョージ・エリオットの言葉。「あの時こうしていれば…」と過去の可能性を振り返って後悔するのではなく、今からでもその理想の姿を目指せばよいという、時間と可能性に対する究極の肯定です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・achieve：[動] 達成する
+・goal：[名] 目標
+・important：[形] 重要な
+【文法解説】
+・同等比較の否定 not as...as：A is not as important as B（AはBほど重要ではない＝Bの方が重要だ）。
+・対比：what you get（得る「物」）と what you become（なる「人物像」）。
+【背景・ニュアンス】
+自己啓発作家ジグ・ジグラーの言葉。目標達成の真の報酬は、外的な成功（お金や地位）を手に入れることではなく、その困難な過程を乗り越えることで変容した「内面的な自己成長（どんな人間になるか）」であるという本質を突いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・education：[名] 教育
+・powerful：[形] 強力な
+・weapon：[名] 武器
+【文法解説】
+・最上級と関係代名詞 which：the most powerful weapon（最も強力な武器）を先行詞とし、which 以下が修飾しています。
+【背景・ニュアンス】
+ネルソン・マンデラの言葉。教育（Education）を、暴力ではなく世界を変革するための「武器（weapon）」と定義。無知こそが差別の温床であり、知性こそが平和的な革命の手段であると宣言した言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・accept：[動] 受け入れる
+・fail：[動] 失敗する
+・try：[動] 挑戦する、試みる
+【文法解説】
+・動名詞の否定：not tryingで「挑戦しないこと」。can't accept not trying で「挑戦しないことは受け入れられない」という強い否定を表しています。
+・無代名詞の省略：everyone fails at something（誰もが何かに失敗する）と一般的な事実を挿入しています。
+【背景・ニュアンス】
+「バスケットボールの神様」マイケル・ジョーダンの言葉。失敗そのものは人間の常として許容できるが、失敗を恐れて逃げる姿勢（挑戦しないこと）だけは絶対に許さないという、究極のプロフェッショナルな哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・question：[名] 問題、課題
+【文法解説】
+・不定詞の名詞的用法：To be（存在すること＝生きるか）と not to be（存在しないこと＝死ぬか）。
+・指示代名詞：that is the question の that は、直前の「生きるか死ぬか」という命題全体を指しています。
+【背景・ニュアンス】
+シェイクスピアの『ハムレット』における最も有名なセリフ。be動詞の最も根源的な意味である「存在する」を使い、人生の究極の選択と苦悩をたった6単語で表現した英文学最高峰のフレーズです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・imagination：[名] 想像力
+・rule：[動] 支配する、統治する
+・world：[名] 世界
+【文法解説】
+・第3文型(SVO)：主語(Imagination) + 動詞(rules) + 目的語(the world) という、非常にシンプルで力強い構文です。
+【背景・ニュアンス】
+フランスの皇帝ナポレオン・ボナパルトの言葉。武力や法律といった物理的な力ではなく、「想像力（Imagination）」こそが人間の心を動かし、ひいては世界を動かす最大の原動力であるという深い洞察です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・judge：[動] 批判する、裁く
+・time：[名] 時間
+・love：[動] 愛する
+【文法解説】
+・条件節 If：「もし〜すれば」。
+・不定詞の形容詞的用法：no time to love them で「彼らを愛するための時間がない」。to love them が time を後ろから修飾しています。
+【背景・ニュアンス】
+マザー・テレサの言葉。他人のアラ探しをして固定観念で裁く（judge）ことにエネルギーを使っていると、その人を受け入れて愛する余裕がなくなってしまうという、愛と批判のトレードオフを優しく諭しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・genius：[名] 天才
+・born：[動] 生まれつく（bearの過去分詞）
+【文法解説】
+・受動態の並列：are made（作られる）と (are) born（生まれつく）の対比。not born の前には are が省略されています。
+・複数形：Geniuses と複数形にすることで、特定の誰かではなく「天才と呼ばれる人々全般」を指しています。
+【背景・ニュアンス】
+発明王トーマス・エジソンの言葉。天才は、生まれ持った才能（born）によるものではなく、後天的な努力や環境によって作り上げられる（made）ものだという、成長マインドセットを端的に表した名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・foundational：[形] 基礎となる、根本的な
+・key：[名] 鍵
+・success：[名] 成功
+【文法解説】
+・名詞を修飾する形容詞：foundational が key を修飾しています。
+・第2文型(SVC)：Action ＝ the foundational key。行動こそが鍵であるという断定の構文です。
+【背景・ニュアンス】
+画家パブロ・ピカソの言葉。どんなに素晴らしいアイデアや計画があっても、「行動（Action）」が伴わなければ何の意味もない。すべての成功のドアを開けるたった一つの鍵は実行力であるという力強いメッセージです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・journey：[名] 旅
+・thousand：[数] 千
+・step：[名] 一歩、歩み
+【文法解説】
+・無生物主語と前置詞 with：旅（journey）が自ら「始まる（begins）」という擬人化表現。with は「〜と共に（起点）」を表します。
+【背景・ニュアンス】
+古代中国の哲学者、老子の言葉の英訳「千里の道も一歩から」。a thousand miles（果てしなく遠い目標）と one step（今できる最小の行動）の極端なスケールの対比が、最初の一歩を踏み出すことの重要性を際立たせています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・difficulty：[名] 困難
+・lie：[動] 横たわる、存在する
+・opportunity：[名] 機会、チャンス
+【文法解説】
+・倒置構文：本来は Opportunity lies in the middle of difficulty. という語順ですが、場所を示す句（In the middle of...）を文頭に出し、主語と動詞を倒置させることで劇的な響きを作っています。
+【背景・ニュアンス】
+アインシュタインの言葉。困難が過ぎ去った後ではなく、まさに「困難のど真ん中（In the middle of）」にこそチャンスが隠れているという、ピンチをチャンスに変える視点の転換です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・energy：[名] 活力、エネルギー
+・persistence：[名] 忍耐、粘り強さ
+・conquer：[動] 征服する、打ち勝つ
+【文法解説】
+・第3文型(SVO)：2つの主語（Energy and persistence）が、目的語（all things）を conquer するという力強い構文です。
+【背景・ニュアンス】
+アメリカ建国の父、ベンジャミン・フランクリンの言葉。Energy（爆発的な瞬発力）と persistence（持続的な持久力）の両輪があれば、どんな困難（all things）も征服できるという、合理的な成功法則です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・bear：[動] 耐える
+・almost：[副] ほとんど
+【文法解説】
+・関係代名詞 who と名詞化：He who... で「〜する人は」。また、a why（理由・目的）と any how（どんな手段・苦難）を名詞として使い、対比させています。
+【背景・ニュアンス】
+ドイツの哲学者ニーチェの言葉。生きるための「確固たる理由（why）」さえあれば、人間は「どんな過酷な状況や方法（how）」にも耐えられる（bear）という、人間の精神の強靭さを表現した名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・mountain：[名] 山
+・conquer：[動] 征服する
+・ourselves：[代] 私たち自身
+【文法解説】
+・強調構文 It is...thatの省略と Not A but B：It is not A (that) we conquer but B（私たちが征服するのはAではなくBだ）という構造で、真の目的語を強調しています。
+【背景・ニュアンス】
+人類初のエベレスト登頂者の一人、エドモンド・ヒラリーの言葉。真に打ち勝つべき相手は、目の前の障害物（the mountain）ではなく、諦めようとする自分自身の心や弱さ（ourselves）であるという深い真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・never：[副] 決して〜ない
+・give up：[動] 諦める
+【文法解説】
+・副詞の反復による強調：否定の命令文 Don't give up を、Never を使って極限まで強めています。
+【背景・ニュアンス】
+イギリスのチャーチル首相の伝説的なスピーチ。国家的危機の最中において、Never を3回繰り返すという非常にシンプルかつ感情的な修辞法が、人々の心を一つにする圧倒的な力を持ちました。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・mind：[名] 心、精神
+・become：[動] 〜になる
+【文法解説】
+・関係代名詞 what の倒置：本来は You become what you think. ですが、what節（What you think）を文頭に出して強調しています。
+【背景・ニュアンス】
+ブッダの言葉の英訳。すべては「心（mind）」で決まる。自分が思い描いた思考が、そのまま現実の自分（become）を創り出すという、引き寄せの法則の根本思想を極めて短い言葉で表現しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・time：[名] 時間
+・money：[名] お金
+【文法解説】
+・第2文型(SVC)：SとCをイコールで結ぶ、英語で最も短く直接的な表現の形です。
+【背景・ニュアンス】
+ベンジャミン・フランクリンの有名な言葉「時は金なり」。時間という目に見えない概念を、お金という目に見える価値に置き換え、時間を浪費することは資産を捨てていることと同義であると警鐘を鳴らしています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・love：[動] 愛する
+・both sides：[名] 両側
+【文法解説】
+・不定詞の並列：To love（愛すること：能動態）と (to) be loved（愛されること：受動態）。主語が複数に見えますが、一つの概念として is で受けています。
+【背景・ニュアンス】
+精神科医デイヴィッド・ヴィスコットの言葉。愛し愛されるという双方向の関係性を、温かい太陽の光に全身を包まれる至福の感覚に例えた、美しく詩的な表現です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・trust：[動] 信じる
+・wrong：[名] 悪、害
+・none：[代] 誰も〜ない
+【文法解説】
+・命令文の3連打：3つの短い命令文を接続詞なしで並べることで、リズミカルな格言の響きを作っています。all, a few, none という対比も鮮やかです。
+【背景・ニュアンス】
+シェイクスピアの言葉。すべての人に博愛を持ちつつも、深く信頼する相手は慎重に選び、誰に対しても害（wrong）は加えないという、人間関係におけるバランスの取れた黄金律です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・unexamined：[形] 吟味されていない、省みられない
+・worth：[形] 価値がある
+【文法解説】
+・worth -ing の構文：be worth -ing は「〜する価値がある」。主語の unexamined は un-(否定) + examine(吟味する) + -ed(過去分詞) で構成されています。
+【背景・ニュアンス】
+古代ギリシャの哲学者ソクラテスの言葉。自らの信念や行動を「深く省みることのない（unexamined）」人生は、人間として生きる価値がないという、哲学の原点とも言える厳しい宣言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・therefore：[副] それゆえに、だから
+【文法解説】
+・接続詞的な therefore：原因（I think）と結果（I am）を論理的に結びつけています。
+【背景・ニュアンス】
+フランスの哲学者デカルトの有名な「我思う、ゆえに我あり」。すべてを疑ったとしても、「疑っている自分自身の意識（I think）」の存在だけは否定できない。ゆえに私の存在（I am）は確実であるという近代哲学の出発点です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・once：[副] 一度
+・enough：[形] 十分な
+【文法解説】
+・接続詞 but と条件節 if：「人生は一度きりだ」というよくあるフレーズに、but で逆説的に条件を加えて新しい視点を提供しています。
+【背景・ニュアンス】
+アメリカの女優メイ・ウェストの痛快な名言。「人生は一度しかない」と嘆くのではなく、正しく（right）全力で生きさえすれば、たった一度（once）で十分に満足できるという、人生の圧倒的な肯定です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・busy：[形] 忙しい、専念する
+・living：[名] 生きること
+・dying：[名] 死ぬこと
+【文法解説】
+・Get + 形容詞 + -ing：be busy -ing（〜するのに忙しい）の be を get（〜になる）に変え、「〜に専念しろ」という切迫した強い命令文にしています。
+【背景・ニュアンス】
+映画『ショーシャンクの空に』（スティーヴン・キング原作）の有名なセリフ。人生には「懸命に生きる（living）」か「ただ死を待つように無気力に過ごす（dying）」かの2つの選択肢しかないと迫っています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・be composed of：[熟] 〜から構成されている
+・soul：[名] 魂
+・inhabit：[動] 〜に住む、宿る
+【文法解説】
+・現在分詞の形容詞的用法：inhabiting（宿っている）が、直前の a single soul（一つの魂）を修飾しています。「2つの体に宿っている1つの魂」という構造です。
+・受動態の熟語：Love is composed of... で「愛は〜から成り立っている」と定義しています。
+【背景・ニュアンス】
+古代ギリシャの哲学者アリストテレスの言葉（とされる名言）。真の愛や深い友情とは、別々の肉体（two bodies）を持ちながらも、まるで一つの魂（a single soul）を共有しているかのような精神的な結びつきであるという、究極の愛の定義です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・without：[前] 〜なしで
+・mistake：[名] 間違い、誤り
+【文法解説】
+・仮定法過去：Without music で「もし音楽がなかったら」という条件（If there were no music）を代用。主節は would be と助動詞の過去形を使い、現在の事実とは異なる仮定を表現しています。
+【背景・ニュアンス】
+ドイツの哲学者ニーチェの言葉。非常に音楽を愛した彼にとって、音楽のない世界は単なる退屈ではなく、宇宙や神の「設計ミス（mistake）」であるとまで言い切るほどの、音楽への絶対的な賛美です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・room：[名] 部屋
+・like：[前] 〜のような
+【文法解説】
+・前置詞句による対比：A room without books（本のない部屋）と a body without a soul（魂のない肉体）という同じ構造（A without B）を like で結びつけた、非常に美しい直喩（Simile）です。
+【背景・ニュアンス】
+古代ローマの政治家・哲学者キケロの言葉。人間の精神を形作る知識や物語（books）が欠けた空間は、ただの空っぽの箱（魂のない肉体）に過ぎない。読書が人間の内面にもたらす生命力を説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・accept：[動] 受け入れる
+・deserve：[動] 〜に値する、ふさわしい
+【文法解説】
+・関係代名詞の省略と連鎖関係詞：the love (that) we think we deserve。「私たちが、自分にふさわしいと（we think）思っている愛」。we think が関係代名詞節の中に挿入されています。
+【背景・ニュアンス】
+小説・映画『ウォールフラワー』の有名なセリフ。自己肯定感が低い人は、自分を傷つけるような相手からの愛であっても「自分にはこれくらいが妥当だ（deserve）」と無意識に受け入れてしまうという、人間の心理の痛いところを突いた言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・forgive：[動] 許す
+・enemy：[名] 敵
+・annoy：[動] イライラさせる、苛立たせる
+【文法解説】
+・命令文とセミコロン：Always forgive... という命令の理由を、セミコロン（;）の後ろで説明しています。
+・否定主語と比較：nothing annoys them so much（それほど彼らを苛立たせるものは何もない＝これが一番彼らを苛立たせる）。
+【背景・ニュアンス】
+オスカー・ワイルドの皮肉とユーモアが効いた言葉。「敵を許しなさい」という道徳的な教えを、「その方が相手にとって一番腹立たしいから」という極めて実利的な（？）理由で勧める、彼らしいウィットに富んだ名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・hero：[名] ヒーロー、主人公
+・own：[形] 自分自身の
+【文法解説】
+・命令文：Be the hero で「主人公になれ」。
+・所有格の強調：your story（あなたの物語）の前に own を入れることで、「他の誰でもない、あなた自身の」と強く所有権を主張しています。
+【背景・ニュアンス】
+自分の人生は、自分自身がシナリオを書き、自分自身が主役を演じる映画のようなものだというメッセージ。脇役のように他人の人生を生きたり、被害者ぶったりするのではなく、自分の物語の主導権を握れという励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・happiness：[名] 幸福
+・warm：[形] 温かい
+・puppy：[名] 子犬
+【文法解説】
+・第2文型(SVC)：Happiness（A）= a warm puppy（B）。抽象的で壮大な概念（幸福）を、極めて具体的で日常的なもの（温かい子犬）で定義しています。
+【背景・ニュアンス】
+漫画『ピーナッツ（スヌーピー）』の作者チャールズ・M・シュルツの言葉。幸せとは、莫大な富や名声を手にすることではなく、抱きしめた時の子犬の温もりなど、日常の些細な心地よさの中にこそあるという優しい教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・scare：[動] 怖がらせる、怯えさせる
+・every day：[副] 毎日
+【文法解説】
+・関係代名詞主格 that：one thing を修飾し、「あなたを怖がらせる（一つのこと）」を作っています。scare が他動詞として you を目的語に取っています。
+【背景・ニュアンス】
+エレノア・ルーズベルトの言葉。コンフォートゾーン（快適な安全圏）に留まっていては成長はない。失敗や未知への「恐怖」を感じることにこそ、毎日少しずつでも挑戦しなさいという勇気ある生き方のススメです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・well done：[形] 立派に行われた、よくやった
+・well said：[形] 立派に語られた
+【文法解説】
+・過去分詞の形容詞化と名詞化：well done（よく為されたこと）と well said（よく言われたこと）を対比し、比較級 better than で結んでいます。
+【背景・ニュアンス】
+ベンジャミン・フランクリンの言葉。どれだけ口で立派な計画や理想を語る（said）よりも、不格好であっても実際に行動して結果を出す（done）ことの方が遥かに価値があるという、実学を重んじたアメリカ建国の父らしい教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・loss：[名] 失うこと、喪失
+・enthusiasm：[名] 熱意、情熱
+【文法解説】
+・動名詞と前置詞句：is walking は現在進行形ではなく、「歩き続けること」という動名詞。with no loss of は「〜を全く失うことなしに」という付帯状況を表します。
+【背景・ニュアンス】
+チャーチルの言葉。成功とは、一度も失敗しないことではなく、一つの失敗から次の失敗へと打ちのめされながら歩んでいく間も、決して「情熱（enthusiasm）」の炎を絶やさないことであるという、不屈の精神の定義です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・inferior：[形] 劣った、下等な
+・consent：[名] 同意、承諾
+【文法解説】
+・使役動詞 make：make you feel inferior で「あなたに劣等感を感じさせる」。
+・否定と前置詞：No one can...（誰も〜できない）と without（〜なしには）を組み合わせ、「あなたの同意なしには不可能だ」という強い構造を作っています。
+【背景・ニュアンス】
+エレノア・ルーズベルトの言葉。他人があなたを見下したり傷つけたりしても、あなたが心の中で「その通りだ」と同意（consent）しない限り、誰もあなたに劣等感を持たせることはできないという、自己尊厳の防衛論です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・err：[動] 間違う、過ちを犯す（errorの動詞形）
+・divine：[形] 神の、神聖な
+【文法解説】
+・不定詞の名詞的用法と対句法：To err is human（間違うことは人間的である）と (To) forgive (is) divine（許すことは神聖である）という完璧な対比構造。後半は To と is が省略され、簡潔さを極めています。
+【背景・ニュアンス】
+イギリスの詩人アレキサンダー・ポープの言葉。人間である以上、失敗や過ちを犯すのは避けられない（human）。しかし、その過ちを犯した他者を「許す」という行為は、人間の次元を超えた神聖で崇高な（divine）行いであるという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・knowledge：[名] 知識
+・power：[名] 力、権力
+【文法解説】
+・第2文型(SVC)：無冠詞の抽象名詞2つを be動詞で結んだ、英語の歴史上最もシンプルで有名な格言の一つです。
+【背景・ニュアンス】
+イギリスの哲学者フランシス・ベーコンの「知は力なり」。自然科学の黎明期において、自然を観察し法則（知識）を知ることこそが、自然を支配し人類を豊かにする「力（power）」になるという近代科学の宣言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・sometimes：[副] 時には
+・path：[名] 道、進路
+・easiest：[形] 最も簡単な（easyの最上級）
+【文法解説】
+・最上級の否定：not the easiest one（最も簡単なものとは限らない）。one は path の反復を避ける代名詞。
+・対比の暗示：right（正しい）と easiest（最も楽な）が必ずしも一致しないことを示しています。
+【背景・ニュアンス】
+ディズニー映画『ポカホンタス』などのテーマ。人生の岐路に立ったとき、誘惑や安易な道（the easiest one）に流されず、困難であっても信念に基づいた正しい道（the right path）を選び取る勇気の大切さを説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・let：[動] 〜させる（使役動詞）
+・go：[動] 行く、離れる
+【文法解説】
+・使役動詞の構文：Let + O + 原形不定詞（Oに〜させる）。ここでは it（過去の執着、悩み、自分を縛るもの）を go（行かせる、手放す）という構造です。
+【背景・ニュアンス】
+ディズニー映画『アナと雪の女王』の主題歌。自分を抑えつけ、過去のトラウマや他人の目を気にするのを「手放して（Let it go）」、ありのままの自分を解放して生きるという、世界中の人々の心を軽くした現代のアンセムです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・where：[接] 〜するところには（接続詞的用法）
+【文法解説】
+・Where節とThere is構文：Where there is A, there is B（AがあるところにはBがある）。場所の副詞節 Where が文頭に出て、愛と生命の存在場所が完全に一致していることを示しています。
+【背景・ニュアンス】
+ガンジーの言葉。「愛のあるところに、命がある」。物質的な豊かさや生存本能だけで人は生きているのではなく、他者を慈しむ「愛（love）」が存在して初めて、人間の生は真の「生命（life）」として輝くという平和主義の哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・someone：[代] 誰か、ある人
+・still：[副] それでもなお
+・love：[動] 愛する
+【文法解説】
+・関係代名詞 who：who 以下が先行詞の someone を修飾しています。
+・接続詞 and による対比：knows all about you（あなたの全てを知っている）と still loves you（それでもなお愛している）という、一見相反する要素を and で繋いで深い意味を生んでいます。
+【背景・ニュアンス】
+思想家エルバート・ハバードの言葉。長所も短所も、過去の失敗や醜い部分も「すべて（all）」知った上で、なおかつ見捨てずに愛してくれる存在こそが、真の「友人（friend）」であるという、人間関係の理想と本質を表した名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・as if：[接] まるで〜であるかのように
+・die：[動] 死ぬ
+・forever：[副] 永遠に
+【文法解説】
+・仮定法過去 as if：現在の事実に反する仮定。be動詞は主語に関わらず were を用います。
+・不定詞 to + 原形：were to die / were to live で「未来の実現可能性の低い仮定（万一〜するなら）」を表し、「明日死ぬかのように」「永遠に生きるかのように」という強い表現を作っています。
+【背景・ニュアンス】
+ガンジーの座右の銘として有名な言葉。人生の有限性（明日死ぬかもしれない）を意識して今日を全力で生きることと、学ぶことの無限性（永遠に生き続ける）を信じて自己研鑽に励むこと。この2つの極端な態度を両立させよという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・enough：[形] 十分な
+・just as：[接] まさに〜のように
+【文法解説】
+・副詞句の強調：as you are（そのままのあなたで）を just（まさに、ただ）で強調しています。you are enough は「あなたはそれで十分だ（欠けているものはない）」という完全な状態を表します。
+【背景・ニュアンス】
+現代の自己肯定感を象徴する言葉。もっと賢く、美しく、豊かにならなければ愛されないという思い込みを捨て、「今のありのままの自分（just as you are）」ですでに100点の価値があるという癒しのメッセージです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・came：[動] 来た（comeの過去形）
+・saw：[動] 見た（seeの過去形）
+・conquered：[動] 征服した（conquerの過去形）
+【文法解説】
+・並列とリズム：I [動詞], I [動詞], I [動詞]. という極限まで切り詰められた3つの過去形の並列。接続詞 and すら省くことで、圧倒的なスピード感と行動力を表現しています。
+【背景・ニュアンス】
+古代ローマの英雄ユリウス・カエサル（シーザー）が、ゼラの戦いで勝利した際の報告。「行って、見て、勝った」。苦戦の言い訳も長々とした報告も不要。圧倒的な実力者の自信と成果を端的に示す最高の言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・true：[形] 真の
+・wisdom：[名] 知恵
+・nothing：[代] 何も〜ない
+【文法解説】
+・動名詞と前置詞 in：is in knowing で「〜を知ることの中に（存在する）」。
+・名詞節の省略：knowing の後ろに接続詞 that が省略されています。「自分が何も知らないということを（知る）」。
+【背景・ニュアンス】
+ソクラテスの「無知の知」。真の知恵とは、物事をたくさん知っていることではなく、「自分は何も知らない」という事実を自覚する謙虚さの中にあるという、古代ギリシャから続く哲学の根本思想です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・depend upon：[動] 〜に依存する、〜次第である
+・ourselves：[代] 私たち自身
+【文法解説】
+・自動詞＋前置詞：depend upon（＝depend on）は非常に重要な熟語。主語の Happiness と、前置詞の目的語 ourselves をダイレクトに結びつけています。
+【背景・ニュアンス】
+アリストテレスの言葉。幸福は運や環境、他人の評価といった外部からもたらされるものではなく、自分自身の心や行動（ourselves）によってのみ決定されるという、自己主導権の哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・rare：[形] まれな、珍しい（rarest は最上級）
+・exist：[動] 存在する
+・all：[代] すべて
+【文法解説】
+・不定詞の名詞的用法：To live（生きること）が主語になっています。
+・that is all：直訳は「それがすべてだ」。転じて「ただそれだけだ（それ以上の意味はない）」という冷徹な限定表現。
+【背景・ニュアンス】
+オスカー・ワイルドの言葉。多くの人はただ呼吸し、日々をやり過ごしているだけ（exist）であり、真の意味で情熱や喜びを持って「生きている（To live）」人間はこの世界で最も珍しいという、鋭い社会風刺です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・mind：[名] 心、精神
+・its own：[形] それ自身の
+・heaven / hell：[名] 天国 / 地獄
+【文法解説】
+・make A of B 構文：「BからAを作る」。make a heaven of hell（地獄から天国を作る）、make a hell of heaven（天国から地獄を作る）の対比です。
+【背景・ニュアンス】
+ミルトンの叙事詩『失楽園』より。心（The mind）は外部環境から独立した絶対的な領域であり、心の持ち方次第で、どんな過酷な状況（地獄）も天国に変えられ、逆に恵まれた環境（天国）を地獄にすることもできるという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・achieve：[動] 達成する
+・inwardly：[副] 内面的に
+・outer reality：[名] 外部の現実
+【文法解説】
+・関係代名詞 what の名詞節：What we achieve inwardly（私たちが内面で達成するもの）が文全体の巨大な主語になっています。inwardly（内側）と outer（外側）の対比がポイントです。
+【背景・ニュアンス】
+古代ギリシャの哲学者プルタルコスの言葉。自分の心や人格という「内面（inwardly）」を磨き成長させることが、結果的に自分の外側に広がる「現実世界（outer reality）」を変えていくという、自己修養の哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・slowly：[副] ゆっくりと
+・backward：[副] 後ろへ、逆戻りして
+【文法解説】
+・等位接続詞 but：I walk slowly と I never walk backward の2つの完全な文を対比させています。never（決して〜ない）という強い否定で意志の固さを示しています。
+【背景・ニュアンス】
+リンカーン大統領の言葉。南北戦争や奴隷解放など、歴史的な困難の中で何度も挫折を味わいながらも、歩みは遅くとも（slowly）、決して諦めて後退する（backward）ことはないという、彼の不屈のリーダーシップを表しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・glory：[名] 栄光
+・lie in：[動] 〜にある、〜に存在する
+・rise：[動] 起き上がる
+【文法解説】
+・Not A but B 構文：「AではなくB」。in never falling（決して倒れないこと）と in rising...（起き上がること）が対比されています。
+・動名詞：前置詞 in の後なので、falling や rising と動名詞が使われています。
+【背景・ニュアンス】
+ネルソン・マンデラ（または孔子などの言葉ともされる）の名言。人生の本当の偉大さ（glory）とは、一度も失敗せずに無難に生きることではなく、何度失敗して倒れても、そのたびに立ち上がる強さの中にあるという励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・truth：[名] 真実
+・remember：[動] 覚えている、思い出す
+・anything：[代] 何も（否定文で）
+【文法解説】
+・条件節 if と don't have to：「もし〜すれば」「〜する必要はない」。
+・部分否定と全否定：don't... anything で「何も〜ない」という強い全否定を作っています。
+【背景・ニュアンス】
+マーク・トウェインのウィットに富んだ言葉。嘘をつくと「誰にどんな嘘をついたか」を常に記憶（remember）して辻褄を合わせなければならないが、常に真実（truth）を語っていればその労力は一切不要であるという、正直さの最大のメリットをユーモラスに突いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・goal：[名] 目標
+・deadline：[名] 締め切り、期限
+【文法解説】
+・第2文型(SVC)：A goal（主語）= a dream（補語）。
+・前置詞 with の付帯状況：「〜を持った、〜を伴った」。with a deadline が dream を後ろから修飾しています。
+【背景・ニュアンス】
+ナポレオン・ヒルの言葉。ただの「夢（dream）」を、達成可能な「目標（goal）」に変えるための魔法のスパイスは、いつまでにやるかという「期限（deadline）」を設定することであるという、ビジネスでも使われる極めて実践的な教訓です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・patience：[名] 忍耐、我慢
+・what he will：彼が望むもの
+【文法解説】
+・関係代名詞 that：He that can have patience（忍耐を持つことができる人）が主語です。最近の英語では who が好まれます。
+・関係代名詞 what の名詞節：what he will の will は助動詞ではなく「望む」という動詞的な意味合いを含み、「彼が望むもの」という意味になります。
+【背景・ニュアンス】
+ベンジャミン・フランクリンの言葉。焦らずに耐え忍ぶ力（patience）を持てる人間は、最終的に自分の望むいかなるもの（what he will）をも手に入れることができるという、自制心と忍耐の価値を説いた古典的な名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・timber：[名] 材木、樹木
+・ease：[名] 容易さ、安楽
+・strong：[形] 強い（stronger は比較級）
+【文法解説】
+・The 比較級〜, the 比較級･･･：「〜であればあるほど、ますます･･･だ」。The stronger wind（風が強ければ強いほど）, the stronger trees（木も強くなる）と、be動詞（is/are）が省略されテンポよく韻を踏んでいます。
+【背景・ニュアンス】
+実業家J・ウィラード・マリオットの言葉。温室育ちの木（人）は弱く、厳しい風雪（困難や逆境）に耐えて育った木こそが立派な大木になるという、自然界の法則を人間の成長になぞらえた美しいメタファーです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・opportunity：[名] 機会、チャンス
+・knock：[動] ノックする
+・build：[動] 建てる、作る
+【文法解説】
+・擬人化：Opportunity（機会）を擬人化し、扉を「ノックする」主語として扱っています。
+・対比の命令文：If節（もし〜ないなら）を受けて、自発的な行動（build a door）を促す命令文で結んでいます。
+【背景・ニュアンス】
+コメディアンのミルトン・バールの名言。「チャンスが向こうからやって来るのを待つな。扉がないなら、自分で扉を作ってチャンスを迎え入れよ」という、受け身の姿勢を否定する圧倒的にプロアクティブ（主体的）な精神です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・work：[動] うまくいく、機能する／働く
+・unless：[接] 〜しない限り（if...not）
+【文法解説】
+・work の多義性：Nothing will work（何事も『うまくいかない』）の work と、unless you do (work)（あなたが『働か』ない限り）の work が掛け言葉になっています。
+・代動詞 do：前の動詞 work の反復を避けるための代動詞です。
+【背景・ニュアンス】
+詩人マヤ・アンジェロウの言葉。どんなに素晴らしい計画やアイデアがあっても、あなた自身が汗を流して行動（work）しない限り、それが現実の世界で成果を上げる（work）ことは絶対にないという、厳しい現実主義の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・tough：[形] 困難な、厳しい／（人が）強靭な、たくましい
+・last：[動] 続く、長続きする
+【文法解説】
+・tough の多義性：tough times（『厳しい』時代）と tough people（『強靭な』人々）で意味が異なります。
+・代動詞 do：but tough people do の do は、last（生き残る、長続きする）を指しています。
+【背景・ニュアンス】
+牧師・作家ロバート・シュラーの有名な著書のタイトル。「苦しい時期はずっとは続かないが、精神的にタフな人間はどんな時代でも生き残る」。逆境にあっても心を折らずに耐え抜くことの価値を、見事な言葉遊びで表現しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・secret：[名] 秘密、秘訣
+・preparation：[名] 準備
+・failure：[名] 失敗
+【文法解説】
+・The result of A, B, and C：「AとBとCの結果」。of の後ろに3つの名詞（句）を並列させています。
+・There is no〜：There are no secrets（魔法のような秘密など存在しない）という強い現実の提示から始まります。
+【背景・ニュアンス】
+アメリカの元国務長官コリン・パウエルの言葉。成功を手に入れるための「裏技や近道」を探す人々に対して、地道な準備、猛烈な努力、そして失敗からの学習という、誰もが知る「王道」しか道はないと断言しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・simplicity：[名] 単純さ、簡潔さ
+・ultimate：[形] 究極の
+・sophistication：[名] 洗練、教養深さ
+【文法解説】
+・第2文型(SVC)とパラドックス：Simplicity（単純さ）という一見素朴な概念を、ultimate sophistication（究極の洗練）という高度な概念とイコール（is）で結びつけた逆説（パラドックス）です。
+【背景・ニュアンス】
+レオナルド・ダ・ヴィンチの言葉（とされ、Appleの初期のパンフレットにも使われた名言）。無駄なものを削ぎ落とし、最もシンプルで本質的な形に到達することこそが、最も知性的で高度に洗練された状態であるという美学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・choice：[名] 選択
+・truly：[副] 本当に、真に
+・ability：[名] 能力
+【文法解説】
+・強調構文：It is A that B（BなのはAだ）。our choices を強調しています。
+・far more than：比較級（more than）を far（はるかに）で強調しています。「能力よりも、はるかに選択だ」。
+【背景・ニュアンス】
+『ハリー・ポッター』のダンブルドア校長の有名なセリフ。生まれ持った才能や知能（abilities）がその人を立派にするのではなく、人生の岐路で「何を正しいと信じ、どう行動するか（choices）」こそが、その人の真の価値を決めるという深い教訓です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・getting ahead：[熟] 前進する、成功する、抜け出す
+・getting started：[熟] 始める、着手する
+【文法解説】
+・動名詞の反復：getting ahead（前進すること）と getting started（始めること）。The secret of A is B（Aの秘訣はBである）という構文に動名詞を当てはめています。
+【背景・ニュアンス】
+マーク・トウェインの言葉。ライバルを一歩リードしたり、大きな目標を達成したりするための「最大の秘訣」は、計画を完璧に練ることではなく、とにかく今すぐ「最初の一歩を踏み出す（getting started）」ことであるという行動主義です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・done：[形] 終わった、完了した
+・perfect：[形] 完璧な
+【文法解説】
+・形容詞の比較：A is better than B（AはBより良い）。Done（完了した状態）と perfect（完璧な状態）を比較しています。
+【背景・ニュアンス】
+Meta（旧Facebook）のCOOだったシェリル・サンドバーグが掲げた社訓。完璧（perfect）を目指すあまりにいつまでもリリースできないよりも、60点でもまずは「終わらせて世に出す（Done）」ことの方が、ビジネスにおいても人生においても価値があるというスピード重視の哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・doubt：[名] 疑い、迷い
+・kill：[動] 殺す、台無しにする
+・ever：[副] これまでに、いつか
+【文法解説】
+・無生物主語と擬人化：Doubt（疑念）が dreams を kill（殺す）という表現。
+・比較級を用いた強調：kills more A than B will（Bが殺すであろうAよりも、もっと多く殺す）。
+【背景・ニュアンス】
+作家スージー・カセムの言葉。夢を諦める最大の原因は、挑戦して「失敗（failure）」したからではなく、挑戦する前に「自分には無理だ」と自分の可能性を「疑う（Doubt）」ことである。疑念こそが最大のドリームキラーであるという戒めです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・great：[形] 偉大な、素晴らしい
+・start：[動] 始める
+【文法解説】
+・don't have to... but have to...：〜する必要はないが、･･･しなければならない。
+・交錯配列法（Chiasmus）：「be great to start」と「start to be great」という順序を逆転させて対比する、記憶に残りやすい修辞技法です。
+【背景・ニュアンス】
+自己啓発作家ジグ・ジグラーの言葉。何かを始める時に「まだ自分には実力（great）がないから」と言い訳をする人に対し、偉大になるための唯一の条件は、未熟なままでもまず「始める（start）」ことなのだと背中を押しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・dream：[動] 夢見る、想像する
+・do：[動] 実行する、実現する
+【文法解説】
+・条件節 If と助動詞 can：非常にシンプルな「If you can A, you can B」の構造。主語(you)と目的語(it)も完全に一致させ、dream と do の2語だけを対比させています。
+【背景・ニュアンス】
+ウォルト・ディズニー（またはディズニー社の理念）を象徴する言葉。人間の想像力（dream）が及ぶ範囲のことであれば、それは物理的にも必ず実現可能（do）であるという、人間のポテンシャルへの絶対的な信頼を表しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・imagine：[動] 想像する
+・real：[形] 本物の、現実の
+【文法解説】
+・関係代名詞の省略：Everything (that) you can imagine。主語が「あなたが想像できるすべてのこと」という巨大な名詞の塊になっています。
+【背景・ニュアンス】
+天才画家パブロ・ピカソの言葉。物理的な現実だけが「リアル」なのではなく、人間の頭の中で鮮明に想像されたものは、すでに精神世界において確固たる現実（real）として存在しており、やがて物質世界にも具現化するという芸術家らしい直感です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・courage：[名] 勇気
+・resistance：[名] 抵抗
+・mastery：[名] 支配、克服
+・absence：[名] 不在、ないこと
+【文法解説】
+・Not A but B の変形：Courage is B, not A（勇気とはBであり、Aではない）。3つの抽象名詞（resistance, mastery, absence）を of fear（恐怖の）で結びつけています。
+【背景・ニュアンス】
+マーク・トウェインの言葉。勇気とは「恐怖を感じないこと（absence of fear）」だと思われがちだが、そうではない。恐怖をしっかりと感じた上で、それに立ち向かい（resistance）、コントロールすること（mastery）こそが真の勇気であるという定義です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・keep：[動] 保つ、〜にしておく
+・ground：[名] 地面、現実
+【文法解説】
+・第5文型(SVOC)の命令文：Keep + O + C（OをCの状態にしておけ）。ここでは2つの対象（eyes と feet）にそれぞれ異なる場所（on the stars と on the ground）を指定し、対比させています。
+【背景・ニュアンス】
+第26代大統領セオドア・ルーズベルトの言葉。視線は常に高く星（高い理想や夢）に向けながらも、両足はしっかりと地面（厳しい現実や足元の努力）に踏みしめておけという、理想主義と現実主義の完璧なバランスを説いた名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・conflict：[名] 闘争、困難、試練
+・glorious：[形] 栄光ある、輝かしい
+・triumph：[名] 勝利
+【文法解説】
+・The 比較級〜, the 比較級･･･：「〜であればあるほど、ますます･･･だ」。The harder the conflict (is), the more glorious the triumph (is) と、be動詞が省略された格調高い表現です。
+【背景・ニュアンス】
+アメリカ独立戦争の思想的指導者トマス・ペインの言葉。目の前の困難（conflict）が厳しく、苦しみが大きければ大きいほど、それを乗り越えた先に待っている勝利（triumph）の喜びと価値は輝かしいものになるという、苦境に立つ者への最高の激励です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fail：[動] 失敗する、怠る
+・prepare：[動] 準備する
+【文法解説】
+・言葉遊び（Pun）：failing to prepare（準備することを怠る）と preparing to fail（失敗するための準備をする）という、同じ2つの動詞を反転させて使った痛烈な皮肉の構文です。
+・前置詞 By + -ing：「〜することによって」。
+【背景・ニュアンス】
+ベンジャミン・フランクリンの言葉。物事に着手する前の「準備」を怠ることは、単なるミスではなく、自ら進んで「失敗するための計画を立てている」のと同じことであるという、段取りと準備の重要性を説いた金言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・count：[動] 数える／重要である、価値がある
+・make：[動] 〜させる（使役動詞）
+【文法解説】
+・count の多義性：Don't count the days（日数を『数える』な）、make the days count（日々を『価値あるものに』させよ）という、1つの単語の異なる意味を利用した見事な対句です。
+【背景・ニュアンス】
+伝説のボクサー、モハメド・アリの言葉。「あと何日で終わるか」「あと何日生きられるか」と受動的に日数をカレンダーで数える（消化する）のではなく、主体的に今日という一日を意味のある「価値ある日（count）」に自ら作り変えよという力強い生き方です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・hurt：[動] 傷つける
+・bless：[動] 祝福する、恵みを与える
+・candle：[名] ろうそく
+【文法解説】
+・関係代名詞 what：What hurts you（あなたを傷つけるもの）が主語になり、それが同時にあなたを blesses（祝福する）というSVOの構造です。
+・メタファー：Darkness（暗闇＝苦難）が candle（ろうそく＝光をもたらすもの）であるという隠喩。
+【背景・ニュアンス】
+13世紀のペルシアの神秘主義詩人ルーミーの言葉。あなたに苦痛や悲しみを与える出来事（Darkness）こそが、魂を成長させ、人生の真実に気づかせてくれる光（candle）となる。傷と祝福は表裏一体であるという深いスピリチュアルな洞察です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・champion：[名] チャンピオン、勝者
+・define：[動] 定義する
+・recover：[動] 回復する、立ち直る
+【文法解説】
+・受動態と Not A but B：is defined not by A but by B（Aによってではなく、Bによって定義される）。
+・間接疑問文：how they can recover（彼らがどのように立ち直れるか）が前置詞 by の目的語になっています。
+【背景・ニュアンス】
+テニス界の伝説ビリー・ジーン・キング（またはマンデラ等の類似表現）の言葉。真のチャンピオンの条件は、どれだけ多くの勝利（wins）を収めたかではなく、敗北して地に落ちた（fall）時に、いかに早く見事に立ち直れるか（recover）で決まるというスポーツ精神の真髄です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・secret：[名] 秘密、秘訣
+・common：[形] 普通の、ありふれた
+・uncommonly：[副] 並外れて、非凡に
+【文法解説】
+・不定詞の名詞的用法：is to do で「〜することである」。
+・副詞の修飾と対比：common（ありふれた）という形容詞と、それに否定の接頭辞 un- をつけた uncommonly（非凡に）という副詞を並べ、鮮やかな対比を作っています。
+【背景・ニュアンス】
+石油王ジョン・D・ロックフェラーの言葉。成功の秘訣は、誰もやっていない特別な魔法を使うことではなく、誰もがやっている当たり前のこと（common thing）を、誰にも真似できないほどの圧倒的なレベル（uncommonly well）で徹底的にやり抜くことだという、地に足のついた成功法則です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・darkness：[名] 暗闇
+・star：[名] 星
+【文法解説】
+・否定語（Only）による倒置：文頭に Only in the darkness（暗闇の中でのみ）という限定・否定的な副詞句が出たため、主語と助動詞が倒置し can you see と疑問文の語順になっています。
+【背景・ニュアンス】
+キング牧師の演説にも登場する名言。周囲が明るく順調な時には見えなかった希望や真実（stars）は、人生のどん底や苦難という暗闇（darkness）に落ちた時に初めてはっきりと輝いて見えるという、逆境にいる人に向けられた深い慰めと励ましの言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・series：[名] 連続、一連
+・bring together：[動] 寄せ集める、まとめる
+【文法解説】
+・受動態と過去分詞の後置修飾：are done は受動態。後半の brought together は small things を後ろから修飾する過去分詞句（集められた小さなこと）です。
+【背景・ニュアンス】
+画家ゴッホの言葉。どんなに偉大で途方もない成果（Great things）であっても、それは魔法のように突然現れるのではなく、一つひとつの地道で小さな作業（small things）を何層にも積み重ねた結果に過ぎないという、芸術家ならではの真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・destine：[動] 運命づける
+・decide：[動] 決める、決断する
+【文法解説】
+・関係代名詞の省略：2つの the person の後ろに、それぞれ関係代名詞 (who/whom) が省略されています。
+・受動態：are destined to... は「〜するよう運命づけられている」。
+【背景・ニュアンス】
+思想家エマーソンの言葉。「運命」という言葉を使いながら、運命論を完全に否定しています。私たちが最終的になる人物像は、神や遺伝が予め決めているのではなく、自分自身の「こうありたいという決断（decide）」のみがそれを決めるという主体性の宣言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・masterpiece：[名] 最高傑作、名作
+【文法解説】
+・第5文型(SVOC)の命令文：Make + O(each day) + C(your masterpiece)。「毎日をあなたの最高傑作にせよ」。
+【背景・ニュアンス】
+伝説的なバスケットボールコーチ、ジョン・ウッデンの言葉。人生という長いスパンで傑作を作ろうと焦るのではなく、今日という「この1日（each day）」をどう完璧に生き切るか。その1日の積み重ねが、最終的に傑作と呼ばれる人生を創るという実践哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・pressure：[名] 圧力、重圧
+・diamond：[名] ダイヤモンド
+【文法解説】
+・省略構文：If there is no pressure, there will be no diamonds. のような条件文を、極限まで削ぎ落として対句にしたリズミカルな表現です。
+【背景・ニュアンス】
+思想家トーマス・カーライルらの言葉とされる名言。炭素が地中深くで途方もない「圧力（pressure）」と熱にさらされることで初めて美しいダイヤモンドに変わるという科学的事実を、人間がプレッシャー（重圧や苦難）の中でこそ輝く才能を開花させるという事実に重ね合わせた秀逸な比喩です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・calm：[形] 穏やかな、波のない
+・skilled：[形] 熟練した、腕のいい
+・sailor：[名] 船乗り、水夫
+【文法解説】
+・無生物主語：A calm sea（穏やかな海）が主語になり、「〜を作らない」という構造です。
+【背景・ニュアンス】
+アフリカのことわざ（F・ルーズベルトなども引用）。波風の立たない平穏な環境（calm sea）では、船乗りの真の技術は磨かれない。荒波（困難やトラブル）にもまれて初めて、人は優秀でたくましい実力者（skilled sailor）に成長できるという教訓です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・usually：[副] たいてい、普通は
+・look for：[動] 〜を探す
+【文法解説】
+・too...to構文：「あまりに〜すぎて･･･できない」。too busy to be looking for it（忙しすぎて、それ＝成功を探す暇もない）。
+・関係代名詞 who：those who are... で「〜である人々」。
+【背景・ニュアンス】
+思想家ソローの言葉。成功（お金や地位）そのものを血眼になって追いかけているうちは、それは逃げていく。目の前の自分のやるべき使命や仕事に「無我夢中で没頭している（too busy）」人のもとに、成功は後から自然とやって来るものだという逆説的な真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・dream about：[動] 〜について夢見る
+・work for：[動] 〜のために働く、努力する
+【文法解説】
+・動詞の対比と前置詞：dream と work という対照的な動詞を使い、about（〜についてぼんやりと）と for（〜に向かって具体的に）という前置詞で行動の質の違いを明確にしています。
+【背景・ニュアンス】
+世界的化粧品ブランドの創業者エスティ・ローダーの言葉。「成功したい」と頭の中で夢見ていた（dreamed）のではなく、ただひたすらに手を動かし、成功をつかむために泥臭く働いた（worked）のだという、圧倒的な行動力と現実主義を端的に表しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・closely：[副] 注意深く、綿密に
+・overnight：[形] 一晩の、一夜にしての
+【文法解説】
+・形容詞化された副詞：overnight は「一晩で」という副詞ですが、ここでは successes（成功）を修飾する形容詞として使われています。
+・took a long time：take は時間や労力が「かかる、必要だ」という意味の重要動詞。
+【背景・ニュアンス】
+スティーブ・ジョブズの言葉。世間がもてはやす「一夜にしての大成功（overnight successes）」も、その裏側をよく観察してみれば、何年にもわたる地道で血の滲むような努力や準備の期間が必ず隠されているものだという、成功の裏にある現実を語った言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・yesterday：[名] 昨日、過去
+・take up：[動] （時間や場所を）取る、占める
+【文法解説】
+・使役動詞 let：Don't let + O + 原形不定詞（Oに〜させるな）。yesterday（過去の後悔や栄光）に、today（今日の貴重な時間）を take up（奪う、占有する）させるなという構造です。
+【背景・ニュアンス】
+コメディアンのウィル・ロジャースの言葉。終わってしまった過去の失敗をクヨクヨ悩んだり、逆に過去の成功にすがりついたりすることに「今日のエネルギー」を浪費してはならない。常に視線を「今、ここ」に向けるべきだという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・failure：[名] 失敗
+・build：[動] 築く、形成する
+・character：[名] 人格、性格
+【文法解説】
+・比較級と代名詞：learn more from A than from B（BからよりもAから多くを学ぶ）。後半の Don't let it stop you の it は failure を指します。
+【背景・ニュアンス】
+広く知られる格言。成功は人を傲慢にするが、失敗（failure）は人に謙虚さや痛みを教え、人間の内面的な深みや人格（character）を形成（build）してくれる。だから失敗を恐れて立ち止まるな、という力強い励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・invisible：[形] 目に見えないもの（the + 形容詞で名詞化）
+・visible：[形] 目に見えるもの
+【文法解説】
+・動名詞を主語に：Setting goals（目標を設定すること）が主語。
+・turn A into B：AをBに変える。the invisible（見えない夢や願望）を the visible（目に見える現実）に変える。
+【背景・ニュアンス】
+世界的なコーチ、トニー・ロビンズの言葉。頭の中にあるぼんやりとした「願望（見えないもの）」を、紙に書き出し期限を決めて「目標（設定）」にした瞬間、それは現実世界での「目に見える」達成への第一歩を踏み出すという、目標設定の重要性を説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・opportunity：[名] 機会、チャンス
+・create：[動] 創り出す
+【文法解説】
+・否定文と肯定文の対比：don't happen（自然発生しない）と You create them（あなたが創り出す）という、極めて短く強い対比の2文で構成されています。
+【背景・ニュアンス】
+起業家クリス・グロッサーの言葉。「良いチャンスが巡ってこないかな」と受動的に待っていても、そんなものは永遠に起こらない（don't happen）。チャンスとは、自らの行動や熱意によって能動的に「創り出す（create）」ものだという厳しい指摘です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・seem to：[動] 〜のように思える、〜らしい
+・luck：[名] 運、幸運
+【文法解説】
+・The 比較級〜, the 比較級･･･：「〜すればするほど、ますます･･･だ」。the harder I work（一生懸命働けば働くほど）, the more luck I seem to have（幸運に恵まれるように思える）。
+【背景・ニュアンス】
+トーマス・ジェファーソン（等の言葉とされる）名言。周囲からは「あの人は運がいい」と見られる成功者も、実はその幸運は偶然ではなく、人一倍の猛烈な努力（hard work）によって自ら引き寄せた必然であるという、運と努力の相関関係を表しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・reputation：[名] 評判、名声
+・endeavor：[動] 努力する、試みる
+・appear：[動] 〜のように見える
+【文法解説】
+・関係代名詞 what：what you desire to appear は「あなたが（他人に）見られたいと望んでいる姿（人物像）」。
+・不定詞の連続：The way to gain... is to endeavor to be... と不定詞が重なり、「〜を得る方法は、〜になるよう努力することだ」という論理的な文を作っています。
+【背景・ニュアンス】
+ソクラテスの言葉。良い評判（reputation）を小手先のテクニックで得ようとするのではなく、自分が「こう見られたい」と思う理想の人物像そのものに、自分自身の内面を一致させるよう努力（endeavor）することこそが、一番の近道であるという本質的な教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・idol：[名] 憧れの人、偶像
+・rival：[名] ライバル、好敵手
+【文法解説】
+・接続詞 until：命令文 Work に続き、「〜になるまで（ずっと働き続けろ）」という期間・到達点を示しています。
+・韻を踏む修辞：idols（アイドル）と rivals（ライバル）が美しい脚韻を踏んでおり、スローガンのようなリズミカルな響きを作っています。
+【背景・ニュアンス】
+ヒップホップ界などでよく引用されるフレーズ。雲の上の存在として崇拝している「憧れの人（idols）」を、いつか対等な立場で競い合う「ライバル（rivals）」へと引きずり下ろすまで、圧倒的な努力を続けろという非常にアグレッシブな野心の言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・strike：[動] 打つ、叩く
+・iron：[名] 鉄
+【文法解説】
+・till（＝until）：〜するまで。
+・Not A but Bの変形：Do not wait... but make it hot...（Aを待つな、しかしBをしろ）。by striking は「打つことによって」という手段を表す動名詞です。
+【背景・ニュアンス】
+詩人イェイツの言葉。一般的なことわざである「鉄は熱いうちに打て（好機を逃すな）」をさらに進化させ、「好機（鉄が熱くなるの）を待つな。自ら行動して叩きまくることで、その摩擦と熱意で無理やりにでも好機を作り出せ」という圧倒的に能動的なメッセージです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・wish：[動] 願う（実現の可能性が低いことを）
+・happen：[動] 起こる、実現する
+【文法解説】
+・Some... some... others...：「〜な人もいれば、･･･な人もおり、また別の人は〜する」。
+・使役動詞と仮定法：want it to happen（起こることを望む）、wish it would happen（起きればいいのになあという仮定法の願望）、make it happen（使役動詞：自らの力で無理やり起こす）という3段階の強い対比です。
+【背景・ニュアンス】
+マイケル・ジョーダンの言葉。成功を「ただ待つ人（want）」「夢想するだけの人（wish）」と、自らの手で「現実にする人（make）」の違いを鮮やかに言語化しています。勝者は常に、自らの意志と行動で結果をこじ開ける「others（後者）」なのです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・motivation：[名] 動機づけ、やる気
+・habit：[名] 習慣
+【文法解説】
+・関係代名詞 what の名詞節：what gets you started（あなたに始めさせるもの）と what keeps you going（あなたを継続させるもの）。
+・使役動詞 get と keep の語法：get + O + 過去分詞（Oを〜の状態にする）、keep + O + 現在分詞（Oを〜し続けさせる）。
+【背景・ニュアンス】
+陸上競技選手ジム・リューンの言葉。最初に重い腰を上げるための起爆剤は「やる気（Motivation）」だが、それは感情なので長続きしない。目標まで走り続けるための真のエンジンは、やる気に頼らずとも自動で体が動く「習慣（Habit）」の力であるという極めて本質的な行動心理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・succeed in：[動] 〜に成功する
+・mission：[名] 使命、任務
+・single-minded：[形] 一意専心の、脇目も振らない
+・devotion：[名] 献身、愛情
+【文法解説】
+・不定詞の副詞的用法：To succeed...（成功するためには）。文頭に置くことで目的を強調しています。
+・助動詞 must：強い義務（〜しなければならない）を表し、目標達成の絶対条件を提示しています。
+【背景・ニュアンス】
+インドの第11代大統領であり、宇宙工学の父とも呼ばれるA.P.J.アブドゥル・カラームの言葉。大きな使命を達成するための唯一の条件は、目標に対して一切の妥協やよそ見をせず、「一意専心（single-minded）」の献身と情熱を注ぎ込むことだという、強烈な集中力のススメです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・cross：[動] 渡る、横断する
+・merely：[副] 単に〜するだけ
+・stare at：[動] 〜をじっと見つめる
+【文法解説】
+・前置詞 by + 動名詞：「〜することによって」。by の後ろに standing と staring が並列され、「ただ立って見つめていることによって」という意味の塊を作っています。
+【背景・ニュアンス】
+インドの詩人であり、アジア人初のノーベル文学賞受賞者タゴールの言葉。海（目標や夢）の前に立ち尽くして「どうやって渡ろうか」と思い悩むばかりでは、いつまで経っても対岸には着かない。まずは水に入り行動を起こせという、実践の重要性を説いた美しい比喩です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・failure：[名] 失敗
+・opportunity：[名] 機会、チャンス
+・intelligently：[副] 知的に、賢く
+【文法解説】
+・不定詞の形容詞的用法：the opportunity to begin（始めるための機会）。
+・副詞の比較級：more intelligently（より賢く）。前回の失敗の経験を踏まえ、思考や戦略がアップデートされている状態を表します。
+【背景・ニュアンス】
+自動車王ヘンリー・フォードの言葉。失敗は「ゲームオーバー」ではなく、前回のデータ（教訓）を持ったまま「もう一度コンティニューから始める（begin again）」ための絶好のチャンスであるという、失敗を学習プロセスと捉える究極のポジティブ思考です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・past：[名] 過去
+・future：[名] 未来
+・yet：[副] まだ
+【文法解説】
+・助動詞の受動態：cannot be changed（変えられることはあり得ない）。
+・前置詞 in：in your power で「あなたの力（権限）の及ぶ範囲内に」。
+【背景・ニュアンス】
+絶対に変えられない「過去（past）」を嘆くことにエネルギーを使うのではなく、まだ自分の決断と行動次第でどうにでも形作ることができる「未来（future）」に意識と行動を集中させよという、時間とコントロールに関する現実的な教訓です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・last：[動] 続く、長持ちする
+・easy：[副] 簡単に、楽に（ここでは副詞的に使用）
+【文法解説】
+・関係代名詞 what の名詞節：What comes easy（簡単に手に入るもの）と What lasts（長く続くもの）がそれぞれの文の主語になっています。
+・交錯配列法（Chiasmus）：A-B-Cという要素を、後半でC-B-Aと反転させる修辞技法で、記憶に残りやすいリズムを作っています。
+【背景・ニュアンス】
+スポーツ選手や筋トレ愛好家の間でよく使われる格言。宝くじのように「簡単に手に入ったもの（comes easy）」はすぐに失われ、本物の技術や信頼など「長く残る価値あるもの（lasts）」は、決して簡単には手に入らないという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・go through：[動] 〜を通り抜ける、経験する
+・hell：[名] 地獄
+【文法解説】
+・現在進行形：If you're going through... で、「まさに今、地獄のような苦しみの中にいるなら」という臨場感を表しています。
+・keep -ing：〜し続ける。命令文で「（そのまま）進み続けろ」。
+【背景・ニュアンス】
+イギリスのチャーチル首相の言葉とされる名言。地獄（最悪の状況）のど真ん中で立ち止まったり、座り込んで嘆いたりすれば、ずっと地獄から抜け出せない。どんなに苦しくても足を止めずに「歩き続ける（keep going）」ことだけが、そこから脱出する唯一の方法だという力強い教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・expert：[名] 専門家、熟練者
+・once：[副] かつては、以前は
+・beginner：[名] 初心者
+【文法解説】
+・名詞句の主語：The expert in anything で「どんな分野の専門家であっても（全員）」という普遍的な主語を作っています。
+【背景・ニュアンス】
+アメリカの女優ヘレン・ヘイズの言葉。今輝かしい成果を出しているプロフェッショナルも、最初から完璧だったわけではなく、皆あなたと同じように何もできない「初心者（beginner）」の時代があった。だから恐れずに始めなさい、という励ましの言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・tired：[形] 疲れた
+・done：[形] 終わった、完了した
+【文法解説】
+・when 節の対比：when you're tired（疲れた時）と when you're done（完了した時）。
+・命令文の対比：Don't stop（やめるな）と Stop（やめろ）。
+【背景・ニュアンス】
+スポーツやビジネスにおけるモチベーションを高める格言。困難な作業の途中で「疲労」を理由にギブアップするのではなく、目標を「達成（done）」した時に初めて休む権利が得られるという、最後までやり抜く執念（Grit）の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・a year from now：今から1年後
+・wish：[動] 〜であればいいのにと願う
+【文法解説】
+・wish ＋ 仮定法過去完了：you had started は「（あの時）始めていればよかったのに（実際は始めなかった）」。過去の事実に対する強い後悔を表します。
+・助動詞 may：〜かもしれない。未来の自分の姿を推量しています。
+【背景・ニュアンス】
+カレン・ラムの言葉。「いつかやろう」と先延ばしにしていると、1年後の未来のあなたは確実に「なぜあの時（1年前の今日）行動を起こさなかったのか」と後悔する。だから、今すぐ行動を起こせという、時間に対する鋭い警鐘です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・repeatedly：[副] 繰り返し
+・excellence：[名] 卓越性、優秀さ
+・act：[名] 単発の行動
+・habit：[名] 習慣
+【文法解説】
+・関係代名詞 what：what we repeatedly do は「私たちが繰り返し行っていること（そのもの）」。
+・Not A but B 構文：「AではなくBである」。卓越性は単なる行動(act)ではなく習慣(habit)であると定義しています。
+【背景・ニュアンス】
+歴史家ウィル・デュラントがアリストテレスの哲学を要約した言葉。私たちという人間を形作るのは、たまに起こす素晴らしい「行動（act）」ではなく、毎日無意識に繰り返している「習慣（habit）」である。真の優秀さとは、日々の地道な積み重ねの賜物であるという本質論です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・continuous：[形] 絶え間ない、継続的な
+・effort：[名] 努力
+・intelligence：[名] 知能、知性
+・unlock：[動] 鍵を開ける、解き放つ
+・potential：[名] 潜在能力
+【文法解説】
+・挿入句による対比：ダッシュ(—)で挟んだ部分で、努力（effort）の対極にあるもの（力や知能）を否定し、努力の価値を際立たせています。
+・the key to -ing：この to は不定詞ではなく前置詞なので、後ろに動名詞（unlocking）を取るのが文法的なポイントです。
+【背景・ニュアンス】
+チャーチル首相の言葉。人間の秘められた可能性（potential）のドアを開けるマスターキーは、生まれ持った筋力やIQではなく、諦めずにコツコツと続ける「継続的な努力（Continuous effort）」であるという、凡人への最高のエールです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・work：[動] 機能する、うまくいく／働く
+・unless：[接] 〜しない限り（if...not）
+【文法解説】
+・work の多義性を使った言葉遊び：Dreams don't work（夢は『叶わない』）と unless you do (work)（あなたが『働か』ない限り）。1つの動詞を2つの意味で掛け合わせています。
+【背景・ニュアンス】
+リーダーシップの権威ジョン・C・マクスウェルの言葉。夢を描いて願うだけでは、夢のほうから勝手に叶ってくれることはない。夢を現実のシステムとして機能（work）させるには、あなた自身の具体的な行動と労働（work）が不可欠であるという現実主義の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・whether A or B：AかBか
+・knock down：[動] 打ち倒す
+・get up：[動] 起き上がる
+【文法解説】
+・It is not A... it is B：AではなくBだ。
+・get + 過去分詞の受動態：get knocked down で「（他からの力によって）打ち倒される」。
+・対比：knocked down（受動的な不運）と get up（自発的な行動）を whether 節で美しく対比させています。
+【背景・ニュアンス】
+アメリカンフットボールの伝説的コーチ、ヴィンス・ロンバルディの言葉。生きていれば不運や失敗によって打ち倒される（knocked down）のは当然のこと。問われるべきは、倒れた事実ではなく、そこから「自らの意志で立ち上がる（get up）かどうか」だという不屈の精神です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・watch：[動] じっと見る
+・clock：[名] 時計
+【文法解説】
+・命令文とセミコロン：Don't watch... ; do... と命令文を並べ、セミコロンで「その代わりに」というニュアンスを繋いでいます。
+・関係代名詞 what：what it does は「それ（時計）がしていること」。時計は止まらずに「動き続けて（Keep going）」います。
+【背景・ニュアンス】
+教育者サム・レヴェンソンの名言。「まだ終わらないかな」と時計を気にして時間を無駄にするのではなく、時計そのものの振る舞いを見習いなさい。時計は立ち止まることなく常に前に進み続けているのだから、あなたも歩みを止めるな（Keep going）という機知に富んだアドバイスです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・moment：[名] 瞬間
+・fresh：[形] 新鮮な、まっさらな
+・beginning：[名] 始まり
+【文法解説】
+・Every + 単数名詞：Every moment で「すべての瞬間」という全体を指しますが、文法的には単数扱いとなり、動詞は is を用います。
+【背景・ニュアンス】
+詩人T.S.エリオットの言葉。過去の失敗に囚われたり、未来を憂いたりする必要はない。人間はいつだって、今のこの瞬間（moment）から、まっさらな新しい人生をやり直す（fresh beginning）ことができるという、今を生きる力強さを説いた言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・choose：[動] 選ぶ
+・never：[副] 決して〜ない
+・have to：〜しなければならない
+【文法解説】
+・命令文 + and：「〜しなさい、そうすれば･･･」。
+・関係代名詞の省略：a job (which/that) you love。
+・否定の強調：not have to（しなくてよい）を never でさらに強めて「一生〜しなくて済む」としています。
+【背景・ニュアンス】
+古代中国の思想家、孔子の言葉。自分が心から愛し、没頭できることを職業（job）にすれば、それはもはや苦痛を伴う「労働（work）」ではなく喜び（遊び）になる。つまり、一生「働かされた」と感じる日は来ないという、天職を見つけることの価値です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・either A or B：AかBのどちらか
+・run：[動] （事業や予定を）管理する、支配する
+【文法解説】
+・run の多義性（他動詞）：you run the day（あなたが1日を支配する）か、the day runs you（1日にあなたが支配されるか）。主語と目的語を反転させて、主導権の所在を問うています。
+【背景・ニュアンス】
+起業家ジム・ローンの言葉。朝起きて自分の明確な意志と計画で1日をコントロール（run）するか、それとも流されるままにタスクや時間に追い回される（run）か。人生の主導権を握るための、タイムマネジメントの究極の原則です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・attribute A to B：Aの原因はBだと考える、AをBのせい（おかげ）にする
+・excuse：[名] 言い訳
+【文法解説】
+・コロン（:）による具体化：this（これ）の内容を、コロンの後ろの文で具体的に説明しています。
+・give or take：自分から言い訳を「言う（give）」ことも、他人からの言い訳を「受け入れる（take）」ことも決してしなかった。
+【背景・ニュアンス】
+近代看護教育の母ナイチンゲールの言葉。自らの輝かしい成功の理由はたった一つ。自分が失敗した時に環境のせいにせず、他人が失敗した時の甘えも許さなかった。言い訳（excuse）を一切排除する、プロフェッショナルとしての凄まじい覚悟です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・need：[動] 必要とする
+・already：[副] すでに
+・inside：[前] 〜の内部に
+【文法解説】
+・関係代名詞の省略：Everything (that) you need（あなたが必要とするすべてのもの）。
+・副詞の位置：already は通常be動詞の後ろに置かれ、「もう既に」という完了の状態を強調します。
+【背景・ニュアンス】
+多くの自己啓発の文脈で語られる言葉。自信、才能、答え、幸せ。私たちが探し求めているものは、外の世界（他人の承認や物質的な豊かさ）にあるのではなく、すでに自分の内側（inside）に完璧に備わっているのだから、自分の内面に目を向けよという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・preparation：[名] 準備
+・tomorrow：[名] 明日
+・do one's best：最善を尽くす
+【文法解説】
+・動名詞 doing：doing your best で「最善を尽くすこと」という名詞句になり、is の補語として機能しています。
+・対比：tomorrow（未来）と today（現在）。
+【背景・ニュアンス】
+作家H.ジャクソン・ブラウン・Jrの言葉。まだ見ぬ明日を案じて不安になったり、過剰な計画を立てたりするよりも、目の前にある「今日」という1日を全力で生き切ること（doing your best）こそが、結果的に最高の未来への準備になるという実践的なアドバイスです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・put A into B：[熟] AをBに注ぎ込む
+・act：[名] 行為、行動
+・even：[副] 〜でさえも
+【文法解説】
+・並列：your heart, mind, and soul（心、精神、そして魂）という3つの名詞をカンマと and で並べて A の部分を作っています。
+・強調：even your smallest acts（あなたの最も小さな行為にさえも）と、最上級に even をつけることで極限まで強調しています。
+【背景・ニュアンス】
+インドの指導者スワミ・シヴァナンダの言葉。大きな偉業を成し遂げる時だけでなく、日常の些細な「小さな行為（smallest acts）」のすべてに、自分の全身全霊を注ぎ込みなさい。それこそが人生を輝かせる秘訣であるという、深い精神性の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・mission：[名] 使命
+・merely：[副] 単に、ただの〜にすぎない
+・survive：[動] 生き残る
+・thrive：[動] 繁栄する、力強く成長する
+【文法解説】
+・Not merely A but B：「単にAだけでなくBも」。
+・不定詞の対比：to survive と to thrive が、AとBの位置で美しく対比され、韻（rive）を踏んでいます。
+【背景・ニュアンス】
+詩人マヤ・アンジェロウの言葉。私の人生の使命は、ただ息をして無難に「生き延びる（survive）」ことではなく、情熱やユーモアを持って力強く「開花し、繁栄する（thrive）」ことであるという、人生に対する貪欲で前向きな宣言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・act of kindness：親切な行為
+・waste：[動] 無駄にする、浪費する
+【文法解説】
+・譲歩の挿入句：no matter how small（それがどんなに小さくても）が、主語と動詞の間に挿入されています。
+・全否定：No act... is ever wasted（いかなる行為も、決して無駄にされることはない）。No と ever を組み合わせて強い否定を作っています。
+【背景・ニュアンス】
+イソップ寓話（ライオンとネズミなど）の教訓として知られる言葉。誰かに対する「親切な行為」は、たとえそれがどんなに些細なものであっても、巡り巡って必ず意味を持つ（決して無駄にはならない）という、利他的な行動へのエールです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・journey：[名] 旅
+・within：[副] 内側へ、心の中へ
+【文法解説】
+・代名詞 one：the one は the journey の反復を避ける代名詞。
+・前置詞の副詞的用法：within は通常前置詞ですが、ここでは「内なる場所」という副詞（または名詞的）に働き、the one を後ろから修飾しています。
+【背景・ニュアンス】
+詩人リルケ（またはそれに類する東洋思想）の言葉。世界中を旅して回る外的・物理的な探求よりも、自分自身の心や精神の奥深くへと潜っていく「内なる旅（journey within）」こそが、人間にとって唯一にして最大の真の探求であるという哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・root：[名] 根、根本
+・suffering：[名] 苦しみ、苦悩
+・attachment：[名] 執着、愛着
+【文法解説】
+・第2文型(SVC)：The root（根本原因）= attachment（執着）。A is B という最もシンプルで断定的な文型です。
+【背景・ニュアンス】
+仏教の開祖ブッダ（釈迦）の根本的な教え（四苦八苦）の英訳。人間が人生で感じるあらゆる「苦悩（suffering）」の根源は、物、地位、人、あるいは自分自身の思い込みに対する「執着（attachment）」から生まれている。執着を手放すことが悟りへの道であるという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fail：[動] 失敗する、役に立たなくなる
+・speak：[動] 話す、語る
+【文法解説】
+・副詞節 Where：Where words fail は「言葉が失敗する（通用しなくなる）場所（状況）において」という意味の副詞節を作っています。
+【背景・ニュアンス】
+童話作家アンデルセンの言葉。人間の深い悲しみや圧倒的な喜びなど、言語（words）の表現力だけでは限界があり「伝えきれない（fail）」感情を、音楽（music）は直接心に響き「雄弁に語る（speaks）」ことができるという、音楽の持つ魔法への賛辞です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・remember：[動] 記憶する、思い出す
+・moment：[名] 瞬間
+【文法解説】
+・否定文と肯定文の並列：We do not... と we... をコンマで繋ぎ、AではなくBである、という対比をリズミカルに作っています。
+【背景・ニュアンス】
+イタリアの詩人チェーザレ・パヴェーゼの言葉。私たちが人生を振り返る時、カレンダーの「何月何日（days）」という数字を思い出しているわけではない。息を呑むような感動や、心が震えた「瞬間（moments）」の連続こそが、私たちの記憶であり人生そのものであるという詩的な表現です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・tie A to B：[熟] AをBに結びつける、縛り付ける
+・goal：[名] 目標
+【文法解説】
+・代名詞 it：tie it の it は、前半の a happy life（幸せな人生）を指しています。
+・否定の並列：not to people or things（人や物にではなく）。to a goal と対比させています。
+【背景・ニュアンス】
+アインシュタインの言葉。自分の幸福を「他人の評価や行動（people）」や「お金や地位（things）」に依存させると、それらが変化した時に幸福も失われる。自分の幸福は、自分自身でコントロールできる「目標や情熱（goal）」に紐づけるべきだという自立の哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・sum up：[動] 要約する
+・go on：[動] 続く、進み続ける
+【文法解説】
+・関係代名詞の省略：everything (that) I've learned（私がこれまでに学んだすべてのこと）。
+・コロン（:）：コロンの後ろの it goes on（それは続いていく）が、前文の everything の具体的な内容（答え）となっています。
+【背景・ニュアンス】
+アメリカの詩人ロバート・フロストの言葉。人生について数多くの複雑なことを経験し学んできたが、最終的に出た結論はたったの3語（it goes on）。どんな悲劇があろうと、どんな成功があろうと、人生という時間はただ「容赦なく前へ進み続ける」という真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・universal：[形] 普遍的な、万国共通の
+・welcome：[名] 歓迎、挨拶
+【文法解説】
+・名詞化：welcome を動詞ではなく名詞として使っています。「A smile = the universal welcome」という第2文型のシンプルな断定です。
+【背景・ニュアンス】
+作家マックス・イーストマンの言葉。言葉が通じない異国であっても、文化的背景が全く異なる相手であっても、「笑顔（smile）」さえあれば、それは相手を受け入れる「万国共通の歓迎のサイン（universal welcome）」として完全に機能するという、笑顔の偉大な力です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・wasted：[形] 無駄にされた
+・laughter：[名] 笑い、笑い声
+【文法解説】
+・最上級を用いた主語：The most wasted of all days（すべての日々の中で最も無駄にされた日）。
+・代名詞 one：one without laughter の one は a day（1日）を指します。
+【背景・ニュアンス】
+フランスの詩人シャンフォール（またはE.E.カミングス）の言葉。お金を無駄にしたり、仕事が進まなかったりした日ではなく、心から「笑う（laughter）」ことが一度もなかった日こそが、人生において最も「無駄にされた（wasted）」悲しい1日であるという、人生の豊かさの定義です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・by chance：[熟] 偶然に
+・by choice：[熟] 選択によって
+【文法解説】
+・Not A but B 構文：「AではなくBである」。
+・頭韻法（Alliteration）：chance と choice という、似た響きを持つ2つの名詞を並べることで、短くリズミカルで記憶に残りやすい格言になっています。
+【背景・ニュアンス】
+起業家ジム・ローンの言葉。幸福（Happiness）は、宝くじのように運良く空から降ってくる「偶然（chance）」の産物ではない。日々自分が何を考え、どう行動するかという、自らの主体的で連続的な「選択（choice）」の結果として創り出されるものであるという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・complicated：[形] 複雑な
+・simple：[形] 単純な
+【文法解説】
+・対義語の並列：questions（問い）と answers（答え）、complicated（複雑な）と simple（単純な）という2組の対義語を and で結んで対比させています。
+【背景・ニュアンス】
+絵本作家ドクター・スースの言葉。私たちが直面する人生の悩みや問題（questions）は、一見すると糸が絡まり合ったように「複雑（complicated）」に見える。しかし、それを解きほぐした一番奥底にある真理や解決策（answers）は、驚くほど「シンプル（simple）」なものであるという本質論です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・plan：[名] 計画
+・wish：[名] 願い、願望
+【文法解説】
+・前置詞句による限定：A goal without a plan で「計画を伴わない目標」という一つの名詞の塊（主語）を作っています。
+・just の強調：just a wish（ただの願い事に過ぎない）と、現実味のなさを強調しています。
+【背景・ニュアンス】
+『星の王子さま』の作者サン＝テグジュペリの言葉。いつかこうなりたいという「目標（goal）」を掲げても、それをいつ、どうやって実現するかの具体的な「計画（plan）」がなければ、それはサンタクロースに祈るような単なる「願望（wish）」に過ぎないという、実践的なビジネスの格言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・sign：[名] 兆候、しるし、証拠
+・intelligence：[名] 知性
+・imagination：[名] 想像力
+【文法解説】
+・Not A but B 構文：not knowledge but imagination（知識ではなく想像力）。
+・形容詞 true：true sign で「真の（本質的な）証拠」と強調しています。
+【背景・ニュアンス】
+アインシュタインの言葉。「知性（intelligence）」が高いとは、学校のテストのように単に過去のデータや事実を多く知っている（knowledge）ことではない。まだ見ぬ未来や新しい概念を、ゼロから脳内に描き出す力（imagination）を持っていることこそが真の天才であるという定義です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・battle：[名] 戦い、闘争
+・kind：[形] 親切な、優しい
+【文法解説】
+・接続詞 for：for everyone... は「というのも、誰もが〜だからだ」と、前の命令文（Be kind）の理由を説明する文語的な接続詞です。
+・関係代名詞の省略：everyone (who/whom) you meet（あなたが出会うすべての人が）。
+【背景・ニュアンス】
+古代の哲学者プラトン（またはジョン・ワトソン）の言葉。他人に「優しくしなさい（Be kind）」。なぜなら、あなたの目の前にいる人は、一見平穏そうに見えても、心の中では誰にも言えない悩みや病気、人生の「過酷な戦い（hard battle）」を必死に生き抜いている最中だからだという、深い共感と思いやりを促す名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・rainbow：[名] 虹
+・cloud：[名] 雲
+【文法解説】
+・不定詞の名詞的用法：Try to be...（〜になろうと努めなさい）。
+・メタファー（隠喩）：someone's cloud は「誰かの心に立ち込める悲しみや暗闇」、rainbow は「そこに光を差し込む希望や喜び」の比喩です。
+【背景・ニュアンス】
+マヤ・アンジェロウの詩的な言葉。悲しみや絶望の「雲（cloud）」に覆われて泣いている人がいたら、あなたがその人を照らす光となり、空に架かる美しい「虹（rainbow）」のような存在になってあげなさいという、無償の愛とサポートの重要性を説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・charm：[名] 魅力
+・equal to：[形] 〜に等しい、〜に匹敵する
+・tenderness：[名] 優しさ、柔らかさ
+【文法解説】
+・後置修飾：There is no charm の後ろから、形容詞句 equal to... が charm を修飾しています。「〜に等しいような魅力は存在しない」。
+【背景・ニュアンス】
+イギリスの作家ジェーン・オースティンの言葉。外見の美しさや、知性、ユーモア、財産など、人間には様々な魅力（charm）があるが、心の底から他者を思いやる「優しさ（tenderness of heart）」に勝る魅力は、この世に一つも存在しないという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・find that：[動] 〜ということに気づく、発見する
+・love back：[動] 愛し返す
+【文法解説】
+・現在完了形：I have found that...（過去から色々と経験してきた結果、私は〜という結論を見つけ出した）と、人生の教訓として語っています。
+・条件節と擬人化：if you love life（人生を愛するなら）。life（人生）を「愛し返してくれる（love you back）」存在として擬人化しています。
+【背景・ニュアンス】
+ピアニストのアルトゥール・ルービンシュタインの言葉。「人生はつらい」と文句を言いながら生きるのではなく、まず自分からこの「人生（life）」というものを丸ごと愛して楽しむこと。そうすれば、人生のほうからも素晴らしい出会いや幸運という形で「愛し返してくれる」という美しい相互作用です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・insist on -ing：[熟] 〜することに固執する、どうしても〜しようとする
+・complicated：[形] 複雑な
+【文法解説】
+・使役・状態の make：making it complicated。Make + O + C（OをCの状態にする）で、it（＝人生）を complicated（複雑な状態）にする、という構造です。
+【背景・ニュアンス】
+古代中国の思想家、孔子の言葉。「人生（Life）」の本質や、幸せに生きるためのルールは本当は驚くほど「シンプル（simple）」なのだ。それなのに、私たち人間はわざわざ見栄を張ったり、余計な心配をしたりして、自らの手で人生を「複雑（complicated）」にして苦しんでいるという、人間の愚かさを突いた言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・serious：[形] 深刻な、重度の
+・mental：[形] 精神的な
+・disease：[名] 病気、疾患
+【文法解説】
+・第2文型(SVC)：Love（愛）= a serious mental disease（深刻な精神疾患）という、非常にシンプルかつ衝撃的な断定です。
+【背景・ニュアンス】
+古代ギリシャの哲学者プラトンの言葉。愛という感情は、人間から理性を奪い、狂気のような状態に陥らせるものであるという、恋愛の圧倒的で抗いがたい力を「深刻な病」に例えた冷徹でシニカルな名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・way out：[名] 出口、抜け道
+・through：[前] 〜を通り抜けて
+【文法解説】
+・前置詞の副詞的用法：through は「（困難や障害の中を）通り抜けて」という方向やプロセスを表します。be動詞の後ろで補語のように働いています。
+【背景・ニュアンス】
+アメリカの詩人ロバート・フロストの言葉。困難な状況から逃げ出すための「最善の出口（best way out）」は、逃げ回ったり迂回したりすることではなく、真正面からその困難の「ど真ん中を突っ切る（through）」ことだという力強い教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・climb：[動] 登る
+・make a difference：[熟] 違いをもたらす、貢献する
+・positive：[形] 肯定的な、良い
+【文法解説】
+・Not A but B 構文：AではなくBである。
+・間接疑問文：how high you have climbed（あなたがどれだけ高く登ったか）と how you make a...（あなたがどのように〜をもたらすか）という2つの名詞節を対比させています。
+【背景・ニュアンス】
+作家ロイ・T・ベネットの言葉。成功の定義を「自分自身がどれだけ高い地位や富を得たか（climb）」という利己的な尺度ではなく、「他者や世界にどれだけ良い影響（positive difference）を与えたか」という利他的な尺度へと転換する教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・problem：[名] 問題、困難
+・chance：[名] 機会、チャンス
+・do one's best：[熟] 最善を尽くす
+【文法解説】
+・不定詞の形容詞的用法：a chance for you to do... で「あなたが最善を尽くすための機会」。for you は不定詞の上の意味上の主語です。
+【背景・ニュアンス】
+ジャズ界の巨匠デューク・エリントンの言葉。目の前に立ちはだかる「問題（problem）」を厄介な障害物としてではなく、自分の能力を最大限に発揮し、成長するための「絶好のステージ（chance）」として歓迎するポジティブなマインドセットです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・must：[助] 〜しなければならない
+・think：[動] 思う、考える
+【文法解説】
+・関係代名詞の省略：the things (that/which) you think you cannot do。「あなたが『自分にはできない』と思っていること」。you think が関係代名詞節の中に挿入されています。
+【背景・ニュアンス】
+エレノア・ルーズベルトの言葉。「自分には無理だ」と勝手に限界を決めているその事柄（things you cannot do）にこそ、あえて挑戦し、乗り越えなければ（must do）本当の成長や自信は得られないという厳しい愛のムチです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・whatever：[代] 〜するものは何でも
+・conceive：[動] 心に抱く、思いつく
+・achieve：[動] 達成する
+【文法解説】
+・複合関係代名詞と頭韻：Whatever... が巨大な主語の塊。conceive, believe, achieve という「-eve」で終わる3つの動詞で美しい韻を踏み、リズミカルなスローガンになっています。
+【背景・ニュアンス】
+成功哲学の祖ナポレオン・ヒルの有名な法則。人間の心が明確に「思い描き（conceive）」、それが実現可能だと「信じる（believe）」ことができるものは、物理的にも必ず「達成できる（achieve）」という、人間の潜在能力への絶対的な信頼です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・count：[動] 重要である、価値がある
+・years：[名] 年数、年齢
+【文法解説】
+・It is... that の強調構文：It’s not A that count. It’s B (that count). 「重要なのはAではなく、Bである」という対比構造です。
+・言葉遊び：the years in your life（人生における年数＝寿命）と the life in your years（年数における生命力＝生きる質）を入れ替えています。
+【背景・ニュアンス】
+リンカーン（またはA.E.スティーブンソン）の言葉。人生の価値は「何年長く生きたか（長さ）」で決まるのではなく、その与えられた時間の中で「どれだけ濃密に、命を燃やして生きたか（深さ）」で決まるという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・use up：[動] 使い果たす
+・creativity：[名] 創造性、クリエイティビティ
+【文法解説】
+・The 比較級〜, the 比較級･･･：「〜すればするほど、ますます･･･だ」。The more you use（使えば使うほど）, the more you have（より多くを持つことになる）。
+【背景・ニュアンス】
+作家マヤ・アンジェロウの言葉。お金や体力は使えば減って（use up）しまうが、「創造性（creativity）」という魔法の泉は、使ってアウトプットすればするほど、逆に湧き出て豊かになっていくという、人間の知性の素晴らしい性質を表しています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・destroy：[動] 破壊する、滅ぼす
+・enemy：[名] 敵
+【文法解説】
+・第5文型(SVOC)：make them(O) my friends(C) で「彼らを私の友達にする」。
+・逆説的構造：destroy（破壊する）という攻撃的な動詞の後に、make...friends（友達にする）という平和的な手段を持ってきています。
+【背景・ニュアンス】
+リンカーン大統領の言葉。「敵を滅ぼす最高の方法は何か？」という問いに対し、武力や憎しみで打ち負かすのではなく、対話によって「彼らを味方（友達）に変えてしまうこと」だと答えた、彼の偉大な包容力と政治的知性を示す名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・winner：[名] 勝者
+・dreamer：[名] 夢見る人
+・give up：[動] 諦める
+【文法解説】
+・関係代名詞 who：who never gives up が a dreamer を修飾しています。never で「決して〜しない」という強い意志を表しています。
+【背景・ニュアンス】
+ネルソン・マンデラの言葉。最終的に勝利を手にする「勝者（winner）」の正体は、特別な才能や権力を持った人間ではなく、どんなに打ちのめされても決して夢を「諦めなかった（never gives up）」ただの夢想家（dreamer）に過ぎないという希望の言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fail：[動] 失敗する
+・way：[名] 道、道のり
+【文法解説】
+・副詞句への転用：failed my way to success で「失敗しながら成功への道を進んだ」というニュアンス。本来自動詞である fail を「〜の道を進む」という文脈で用いた特有の表現です。
+【背景・ニュアンス】
+発明家エジソンの言葉。「失敗せずに成功した」のではなく、「数え切れないほどの失敗を意図的に積み重ねた結果として、ようやく成功（電球の発明など）に辿り着いた」という、失敗を成功の必要条件とみなす彼の哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・change：[動] 変える
+【文法解説】
+・Onlyの限定と代名詞の対比：Only I（私だけが）と No one（誰も〜ない）を対比させています。it は change my life を指し、for me は「私の代わりに」という意味です。
+【背景・ニュアンス】
+アメリカのコメディアン、キャロル・バーネットの言葉。自分の人生を良くしてくれない環境や他人を嘆いても無駄である。自分の人生のハンドルを握って「変える（change）」ことができるのは、親でも恋人でもなく「自分自身（Only I）」だけだという自立の宣言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・quality：[名] 品質、質
+・act：[名] （単発の）行為
+・habit：[名] 習慣
+【文法解説】
+・Not A, but B 構文の変形：is not an act, it is a habit（Aではなく、Bである）。
+【背景・ニュアンス】
+アリストテレスの哲学を要約した言葉。製品の品質や人間の質の高さ（Quality）は、思いつきで1回だけ素晴らしいこと（an act）をしたから得られるものではなく、毎日当たり前のように高い基準で繰り返す「習慣（habit）」の結果としてのみ現れるという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・accomplish：[動] 成し遂げる、達成する
+・great things：偉大なこと
+【文法解説】
+・not only A, but also B：「AだけでなくBも」。act（行動する）と dream（夢見る）、plan（計画する）と believe（信じる）という、論理的思考と感情的思考の両方を並列させています。
+【背景・ニュアンス】
+作家アナトール・フランスの言葉。偉大なことを成し遂げるには、現実的な「行動や計画（act, plan）」はもちろん必要だが、それと同じくらい、大きな「夢や確信（dream, believe）」という目に見えない情熱が不可欠であるという両輪の法則です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・anywhere：[副] どこへでも
+・as long as：[接] 〜である限り
+・forward：[副] 前へ
+【文法解説】
+・条件の接続詞：as long as は、行動に対する「唯一の条件」を提示する時に使われます。it は進む方向や状況を指します。
+【背景・ニュアンス】
+探検家デヴィッド・リヴィングストンの言葉。未知の世界へ進むとき、目的地がどこであろうと、どんな困難な道（anywhere）であろうと構わない。ただ一つ、「前に進んでいる（forward）」ことさえ確かならば、私はどこへでも行くという圧倒的な前進への渇望です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・interfere with：[動] 〜を妨げる、邪魔をする
+【文法解説】
+・関係代名詞 what の名詞節：what you cannot do（あなたにできないこと）と what you can do（あなたにできること）の対比。
+・使役動詞 let：Do not let A interfere with B で「AにBの邪魔をさせるな」。
+【背景・ニュアンス】
+名将ジョン・ウッデン監督の言葉。私たちはつい「自分には才能がない、お金がない（cannot do）」ことばかりに気を取られてしまう。しかし、その不満にエネルギーを奪われ、今手元にある「自分にできること（can do）」をおろそかにしてはならないという戒めです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・defeat：[名] 敗北
+・bitter：[形] 苦い
+・unless：[接] 〜しない限り
+・swallow：[動] 飲み込む
+【文法解説】
+・条件節 unless の働き：「もし〜しない限り、･･･ない」。
+・メタファー（隠喩）：敗北（defeat）を「苦い薬や毒（bitter）」に例え、それを心の中に「飲み込む（swallow＝屈服する、自信を失う）」かどうかは自分の選択だと表現しています。
+【背景・ニュアンス】
+作家ジョー・クラーク（またはブルース・リーなどの言葉とされる）。試合や勝負で「敗北（defeat）」を味わうことはある。しかし、その事実を自分の中で「私はダメな人間だ」と深く飲み込んでしまわない限り、敗北はただのデータに過ぎず、あなた自身を傷つけることはないという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fall：[動] 倒れる、転ぶ
+・stand up：[動] 立ち上がる
+【文法解説】
+・命令文の並列：Fall と stand up。
+・数字の非対称性：seven times（7回）と eight（8回）。転んだ回数よりも、必ず「1回多く」立ち上がるという事実を数字だけで表現しています。
+【背景・ニュアンス】
+日本のことわざ「七転び八起き」の英訳。何度失敗して打ちのめされようとも、最後に必ずもう一度だけ立ち上がれば、結果としてそれは敗北ではなくなるという、世界中で愛される不屈の精神の象徴です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・health：[名] 健康
+・hope：[名] 希望
+【文法解説】
+・代名詞 He + 関係代名詞 who：He who... で「〜する人は」。
+・並列表現：前半の結論（健康な人は希望を持つ）を、後半の前提（希望を持つ人はすべてを持つ）へと見事に繋げて論理を展開しています。
+【背景・ニュアンス】
+アラブのことわざ。どんなに富や名声があっても、心身の「健康（health）」がなければ希望は持てない。そして「希望（hope）」さえあれば、人は何度でも立ち上がり、あらゆるもの（everything）を手に入れることができるという、健康の絶対的な価値を説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・even if：[接] たとえ〜だとしても
+・go to pieces：[熟] 粉々になる、崩壊する
+・plant：[動] 植える
+【文法解説】
+・仮定法過去：Even if I knew...（たとえ知っていたとしても）、the world would go...（世界が滅亡するだろうということを）、I would still plant...（それでも私は植えるだろう）。実現可能性が低くても変わらない強烈な意志を表します。
+【背景・ニュアンス】
+宗教改革者マルティン・ルター（とされる）名言。「明日世界が終わる（世界の終わり、結果の無意味さ）」と分かっていても、私は今日、自分の使命である「リンゴの木を植える（希望の種をまくこと）」という日々の営みを決してやめない。結果に左右されない崇高な生き方です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・every day：[名] 毎日（1日1日）
+・something：[代] 何か
+【文法解説】
+・部分否定：may not be... は「〜ではないかもしれない」という推量。
+・There is 構文と後置修飾：there's something good は「何か良いことがある」。something などの -thing で終わる代名詞は、形容詞（good）が後ろから修飾します。
+【背景・ニュアンス】
+作者不詳（不思議の国のアリス等の言葉ともされる）のポジティブな名言。毎日が最高で素晴らしい日（good day）であるとは限らない。しかし、どんなに最悪な1日の中にも、探せば必ず「小さな良いこと（something good）」が一つは隠れているという、視点の転換を促す優しい言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・greatest：[形] 最大の、最高の（greatの最上級）
+・wealth：[名] 富、財産
+・health：[名] 健康
+【文法解説】
+・第2文型(SVC)：The greatest wealth（最大の富）= health（健康）。
+・韻（Rhyme）：wealth と health は綴りも発音もよく似ており、見事な脚韻を踏んで覚えやすい格言の響きを作っています。
+【背景・ニュアンス】
+古代ローマの詩人ウェルギリウスの言葉。お金や地位など様々な「富」の形があるが、結局のところ、それらを楽しむための「健康（health）」こそが、人間にとって最も価値があり、失ってからその重大さに気づく最大の財産であるという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fear：[名] 恐怖
+・strike out：[動] 三振する
+・keep A from -ing：[熟] Aに〜させない、Aが〜するのを妨げる
+【文法解説】
+・使役動詞 let の否定命令：Never let A keep...（Aに妨げさせるな）。the fear of striking out（三振する恐怖）という巨大な名詞句が A に当たります。
+【背景・ニュアンス】
+映画『シンデレラ・ストーリー』などでも引用されるベーブ・ルースの名言。「三振（失敗）したらどうしよう」という恐怖心に支配されて、バッターボックスに立つこと（挑戦すること＝playing the game）自体を放棄してはならないという、勇気と挑戦へのエールです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・expect：[動] 期待する、予期する
+・great things：偉大なこと、素晴らしいこと
+・before：[接] 〜する前に
+【文法解説】
+・expect A of B：BにAを期待する。expect great things of yourself（自分自身に偉大なことを期待する）。
+・助動詞 must：〜しなければならないという強い条件。
+【背景・ニュアンス】
+「バスケットボールの神様」マイケル・ジョーダンの言葉。高い目標を実際に「達成できる（can do）」ようになるための絶対の前提条件（before）は、まだ実力がない段階から「自分なら素晴らしいことができるはずだ」と、自分自身に高い期待をかける（expect）ことだというマインドセットです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・focus on：[動] 〜に集中する、焦点を合わせる
+・journey：[名] 旅、道のり（プロセス）
+・destination：[名] 目的地（結果）
+【文法解説】
+・命令文と対比の省略：Focus on A, (and) not (on) B。BではなくAに集中せよという構造です。
+【背景・ニュアンス】
+神学者グレッグ・アンダーソンの言葉。人生や仕事において、最終的な結果や「目的地（destination）」ばかりにとらわれるのではなく、そこへ至るまでの過程や成長、日々の「旅のプロセス（journey）」そのものを味わい、集中せよというマインドフルネスの教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・spread：[動] 広げる、まき散らす
+・candle：[名] ろうそく
+・mirror：[名] 鏡
+・reflect：[動] 反射する
+【文法解説】
+・コロン（:）による具体化：two ways（2つの方法）をコロンの後ろで具体的に説明しています。
+・関係代名詞 that：that reflects it が the mirror を後ろから修飾しています（光を反射する鏡）。
+【背景・ニュアンス】
+アメリカの小説家イーディス・ウォートンの言葉。暗闇に光（希望や喜び）をもたらすには2つの生き方がある。自らが燃えて光を発する「ろうそく（candle）」のような天才やリーダーになるか、あるいはその光を受け止めて周囲に反射し、広げる「鏡（mirror）」のような支援者になるか、という美しい比喩です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・quickly：[副] 早く、急速に
+・positive：[形] 肯定的な、良い
+・let：[動] 〜させる（使役）
+【文法解説】
+・in a ... way：〜な方法で、〜な方向に。in a very positive way（非常に良い方向に）。
+・条件節 if you let it：もしあなたがそれを許す（受け入れる）なら。it は Life changes を指します。
+【背景・ニュアンス】
+スキー選手リンゼイ・ボンの言葉。人生は恐ろしいほど急激に変化していくが、変化を恐れて抵抗するのではなく、「変化してもいいのだ」と心を開いて受け入れ（let it）さえすれば、それは驚くほど素晴らしい方向（positive way）へと転がっていくという言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・never：[副] 決して〜ない
+・set a goal：[熟] 目標を立てる
+【文法解説】
+・too...to構文：You are never too old to... で「〜するには決して年をとりすぎているということはない（いつだって〜できる）」。
+・不定詞の並列：to set... と to dream... が or で結ばれています。
+【背景・ニュアンス】
+『ナルニア国物語』の作者C.S.ルイスの言葉。新しい目標を立てたり、全く新しい夢を見たりするのに「もう遅すぎる」という年齢の壁は存在しない。人間の精神や挑戦の権利には、肉体的な年齢（old）は一切関係ないという力強い励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・need A to be B：AにBであることを求める
+・worth it：[熟] それだけの価値がある
+【文法解説】
+・対比の構文：I don't need... と I need... の強い対比。
+・worth の用法：be worth it で「（苦労や時間に見合う）価値がある」。it は前述の苦労などを漠然と指します。
+【背景・ニュアンス】
+多くの挑戦者が口にする格言。これから挑む道が「楽で簡単なもの（easy）」である必要は全くない。困難や苦痛が伴っても構わないから、ただ、その苦労を乗り越えた先に「それだけの価値（worth it）」があることだけを求めるという、圧倒的な覚悟の言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・find out：[動] 見つけ出す、正体を知る
+・on purpose：[熟] わざと、意図的に、目的を持って
+【文法解説】
+・間接疑問文：who you are（あなたが本当は何者であるか）が find out の目的語になっています。
+・命令文の並列：Find out（見つけ出せ）と do it（それをやれ）。
+【背景・ニュアンス】
+カントリー歌手ドリー・パートンの名言。他人の期待や世間の常識を剥ぎ取り、まず「本当の自分（who you are）」の性質や才能を見つけ出しなさい。そして、それに気づいたら、今度は恥ずかしがらずに「意図的かつ大げさに（on purpose）」その自分らしさを発揮して生きよという痛快なアドバイスです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・negative：[形] 否定的な、マイナスの
+・situation：[名] 状況
+・positive：[形] 肯定的な、プラスの
+【文法解説】
+・turn A into B：AをBに変える。
+・命令文と対義語：Always turn（常に変えろ）。negative と positive という分かりやすい対義語を配置し、シンプルな原則を提示しています。
+【背景・ニュアンス】
+「バスケットボールの神様」マイケル・ジョーダンの言葉。ピンチや不運、失敗といった「マイナスの状況（negative situation）」に直面したとき、それを嘆くのではなく、自らの力と思考で強引に「プラスの状況（学びや逆転のチャンス）」へと変換してしまえという、王者のメンタリティです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・limit：[動] 制限する、減らす
+・always：[副] いつも、常に
+・never：[副] 決して〜ない
+【文法解説】
+・副詞の名詞化：通常は副詞である 'always' と 'nevers' に s をつけて複数形の名詞として扱い、「『いつも〜だ』という決めつけ」と「『絶対に〜ない』という否定」を表しています。
+【背景・ニュアンス】
+作家エイミー・ポーラーの言葉。「彼は『いつも』遅刻する」「私には『絶対に』無理だ」といった、極端で限定的な言葉遣い（always / never）は、人間の可能性や思考の柔軟性を奪ってしまう。白黒思考を手放し、人生のグレーゾーンを許容せよという心理学的な教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・thought：[名] 思考、考え
+・shine out of：[動] 〜から輝き出る
+・sunbeam：[名] 太陽の光、陽射し
+【文法解説】
+・直喩（Simile）：like sunbeams で「太陽の光のように」と例えています。
+・代名詞 they：good thoughts（良い思考）を指します。
+【背景・ニュアンス】
+児童文学『チョコレート工場の秘密』の作者ロアルド・ダールの言葉。心の中に優しく美しい「良い考え（good thoughts）」を持っている人は、それが内側から溢れ出し、まるで太陽の光のように「顔の表情（face）」を輝かせる。内面の美しさが外見の美しさを創るという素敵な表現です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・by-product：[名] 副産物
+・well lived：よく生きられた、充実した
+【文法解説】
+・後置修飾の過去分詞：a life well lived で「（立派に）よく生きられた人生」。
+・否定と肯定の対比：is not A... it's B（AではなくBである）。
+【背景・ニュアンス】
+エレノア・ルーズベルトの言葉。幸福（Happiness）とは、それ自体を「目標（goal）」として追い求めて手に入るものではない。目の前の仕事に打ち込み、他者を愛し、1日1日を「充実して生き抜いた（well lived）」結果として、あとから自然についてくる「副産物（by-product）」に過ぎないという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・useless：[形] 役に立たない、無用な
+・lighten：[動] 軽くする
+・burden：[名] 重荷、負担
+【文法解説】
+・関係代名詞の分離：who lightens... の先行詞は No one ですが、主語が長くなるのを避けるため、述語 is useless in this world の後ろに配置されています。
+・二重否定のニュアンス：No one is useless who...（〜する人で、無用な人は一人もいない＝〜する人は誰でも価値がある）。
+【背景・ニュアンス】
+イギリスの作家チャールズ・ディケンズの言葉。自分は社会の役に立っていないと落ち込む必要はない。他人の苦しみや荷物（burdens）をほんの少しでも「軽くしてあげる（lighten）」心と思いやりがある人間は、この世界において絶対に「無価値（useless）」ではないという温かい励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・path：[名] 道、道のり
+・happiness：[名] 幸福
+【文法解説】
+・There is no 構文：There is no path to happiness（幸福へと続く『道』は存在しない）。
+・コロン（:）による言い換え：コロンの前後で A to B（BへのA）と B is A（BこそがA）という反転構造（happiness is the path）を作っています。
+【背景・ニュアンス】
+ベトナムの禅僧ティク・ナット・ハンの言葉。多くの人は、苦難の道を歩き続けた「ゴール（目的地）」に幸福があると思っている。しかし、幸福とは目的地ではなく、今この瞬間の歩き方、心の在り方そのもの（道そのもの）であるという、マインドフルネスの真髄です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・whenever：[接] 〜する時はいつでも
+・possible：[形] 可能な
+【文法解説】
+・副詞節の省略：whenever (it is) possible（可能な時はいつでも）。
+・断定の文：It is always possible.（それは『常に』可能である）。この短い2文目が強力なパンチラインになっています。
+【背景・ニュアンス】
+ダライ・ラマ14世の言葉。「可能な限り、他人に優しく（kind）しなさい」。この一見普通の道徳的アドバイスに、「そして、優しくすることは『常に（always）』可能である」という一文を付け加えることで、どんな状況でも愛と思いやりを選択できる人間の心の自由と強さを説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・happen to：[動] 〜の身に起こる
+・react to：[動] 〜に反応する
+・matter：[動] 重要である
+【文法解説】
+・It is... that の強調構文：It is not A but B that matters.（重要なのはAではなくBだ）。
+・名詞節の対比：what happens to you（あなたに起きる出来事）と how you react to it（それにあなたがどう反応するか）を対比させています。
+【背景・ニュアンス】
+古代ギリシャのストア派哲学者エピクテトスの言葉。自分の身に降りかかる不運や災害（起きる出来事）はコントロールできない。しかし、それをどう解釈し、どう行動するか（自分の反応）は100%コントロールできる。人生の質を決めるのは後者であるという究極の自己責任論です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・without：[前] 〜なしで
+・risk：[名] 危険、リスク
+・triumph：[動] 勝利する、打ち勝つ
+・glory：[名] 栄光
+【文法解説】
+・不定詞の名詞的用法：To win（勝つこと）is to triumph（勝利することである）。
+・前置詞句の対比：without risk（リスクなしで）と without glory（栄光なしで）を美しい対句として配置しています。
+【背景・ニュアンス】
+フランスの劇作家ピエール・コルネイユの言葉。傷つくことや失敗すること（risk）を極度に恐れて安全圏で手にした勝利には、人々の心を打つ「栄光（glory）」は宿らない。挑戦と痛みの大きさが、成功の輝きと価値を決定づけるという勇敢な騎士道の精神です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・brave：[形] 勇敢な
+・conquer：[動] 征服する、打ち勝つ
+【文法解説】
+・代名詞 he + 関係代名詞 who：he who...（〜する人）。
+・Not A but B 構文：not he who... but he who...（Aな人ではなく、Bな人である）。
+・feel afraid と fear の対応：afraid（形容詞：恐れて）と fear（名詞：恐怖）を結びつけています。
+【背景・ニュアンス】
+ネルソン・マンデラの言葉。「勇敢な人間（The brave man）」とは、生まれつき恐怖を一切感じない鈍感な人間のことではない。足がすくむような「恐怖（fear）」を心の中にしっかりと認識しながらも、逃げ出さずにその感情を「ねじ伏せて行動する（conquers）」人間のことであるという、真の勇気の定義です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・educated：[形] 教育を受けた、教養のある
+・free：[形] 自由な
+【文法解説】
+・The + 形容詞：The educated で「教育を受けた人々」という複数扱いになります。そのため、続くbe動詞は is ではなく are になっています。
+【背景・ニュアンス】
+古代ギリシャのストア派哲学者エピクテトスの言葉。人間を不自由にしているのは鎖ではなく、無知や偏見である。真の教育（知性）を得て初めて、人は他人の意見や迷信から解放され、精神的な「自由（free）」を手に入れることができるという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・improve：[動] 向上させる、良くする
+・tomorrow：[名] 明日、未来
+【文法解説】
+・関係代名詞 what：What you do today（あなたが今日すること）が文全体の主語。
+・複数形の tomorrow：all your tomorrows と複数形にすることで、単なる「明日」ではなく「これからのあなたの未来全体」を表しています。
+【背景・ニュアンス】
+作家ラルフ・マーストンの言葉。過去を変えることはできず、遠い未来を直接操作することもできないが、「今日（today）」という1日の行動を変えることさえできれば、それはドミノ倒しのように「これからのすべての未来（all your tomorrows）」を向上させるという励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・act：[動] 行動する
+・as if：[接] まるで〜であるかのように
+・make a difference：[熟] 違いを生む、影響を与える
+【文法解説】
+・仮定の接続詞：as if の後ろに what you do（あなたの行動）という主語が続きます。
+・代動詞 does：It does の does は makes a difference の反復を避けた表現で、「（現実に）違いを生むのだ」という強い断定です。
+【背景・ニュアンス】
+アメリカの心理学者ウィリアム・ジェームズの言葉。自分の小さな行動なんて世界には影響しないと諦めるのではなく、世界を変える力がある「かのように」行動しなさい。そう信じて動くことで、実際に現実（It does）が変わっていくという自己効力感の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fall：[動] 転ぶ、落ちる
+・get up：[動] 起き上がる
+【文法解説】
+・動名詞の並列：falling（転ぶこと）と getting up（起き上がること）を and で繋いでいます。
+・数字の対比：nine（9）と ten（10）。転んだ回数よりも必ず「1回多く」起き上がるという構造です。
+【背景・ニュアンス】
+ミュージシャンのジョン・ボン・ジョヴィ（または日本の「七転び八起き」の派生）の言葉。成功の定義を「一度も転ばないこと」とするのではなく、「何度打ちのめされても、その回数プラス1回立ち上がること」とする、シンプルで力強い不屈の精神です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・plant：[動] （植物を）植える
+・second best：2番目に良い
+【文法解説】
+・不定詞の形容詞的用法：The best time を to plant a tree（木を植えるための）が修飾。
+・序数 + 最上級：The second best time（2番目に良いタイミング）という英語特有の表現です。
+【背景・ニュアンス】
+中国のことわざ。「もっと早く（20年前に）始めていればよかった」と過去を後悔するのは無意味である。過ぎ去った最良のタイミングの次に良いのは「今（now）」なのだから、後悔している暇があるなら今すぐ種をまき（始め）なさいという実践的な教訓です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・grow：[動] 成長する、〜になる
+・great：[形] 偉大な
+【文法解説】
+・第2文型(SVC)の派生：grow は後ろに形容詞（great）を取り、「〜（の状態）になる」という変化のプロセスを表します。
+・前置詞 by：手段（〜によって）を表します。
+【背景・ニュアンス】
+アメリカ第28代大統領ウッドロウ・ウィルソンの言葉。人間が偉大な存在（great）へと成長できるのは、偶然や生まれ持った才能によるものではなく、「夢を見る（dreams）」という行為を通してのみ可能になるという、想像力と野心への賛歌です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・change：[動] 変える
+・heart：[名] 心、精神
+【文法解説】
+・前置詞 by + 動名詞：by changing... で「〜を変えることによって」。手段を明確に示しています。
+・反復と対比：change という動詞を繰り返し、your life（外側の世界）と your heart（内側の世界）を対比させています。
+【背景・ニュアンス】
+自分の人生（life）がうまくいかないとき、環境や他人のせいにしたくなるが、外側の世界を直接変えることはできない。唯一の確実な方法は、物事を捉える自分自身の「心（heart）」のあり方を変えることであるという、内面変革の真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・courage：[名] 勇気
+・grow up：[熟] 成長する、大人になる
+・really：[副] 本当に
+【文法解説】
+・It takes... to構文：It takes courage to... で「〜するには勇気が必要だ」。
+・関係代名詞（疑問詞）：who you really are は「あなたが本当は何者であるか（本当の自分）」。
+【背景・ニュアンス】
+アメリカの詩人E.E.カミングスの言葉。他人の期待や社会のレールに従って生きることは実は簡単である。そこから抜け出し、自分自身の本質（who you really are）と向き合って「本当の自分」になるためには、多大な「勇気（courage）」が必要であるという自己探求の励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・loudly：[副] 大声で、騒々しく
+・hear：[動] 聞こえる
+【文法解説】
+・so... that... 構文：「とても〜なので･･･だ」。so loudly（あまりに大きな声で[語る]ので）that I cannot hear（私には聞こえない）。
+・対比：What you do（あなたの行動）と what you say（あなたの言葉）。
+【背景・ニュアンス】
+思想家エマーソンの言葉。「行動は言葉よりも雄弁である」という真理を見事に表現しています。口でどんなに立派なこと（say）を言っても、実際の行動（do）が伴っていなければ説得力はない。人はあなたの言葉ではなく「行動」を見ているという戒めです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・success：[名] 成功
+・happiness：[名] 幸福
+【文法解説】
+・交錯配列法（Chiasmus）：getting what you want と wanting what you get という、動詞（get/want）をX字型に交差・反転させる修辞技法で、記憶に残りやすい対比を作っています。
+【背景・ニュアンス】
+デール・カーネギーの言葉。成功とは「望むものを手に入れる（野心）」ことだが、幸福とは「今自分が手に入れている現状を、これでいいのだと望む（足るを知る）」ことである。成功と幸福は似て非なるアプローチであるという深い分析です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fast：[副] 速く
+・far：[副] 遠くへ
+・alone：[副] 一人で
+・together：[副] 一緒に
+【文法解説】
+・対句法：If you want to go... という全く同じ条件節の構造を用いて、fast / alone と far / together という対照的な副詞を見事に対比させています。
+【背景・ニュアンス】
+アフリカのことわざ。「スピード（fast）」を求めるなら、意見を調整する手間のない一人が良い。しかし、困難を乗り越えて「はるか遠くの大きな目標（far）」に到達したいのであれば、互いを支え合う仲間（together）が不可欠であるという、チームワークの本質です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・short：[形] 短い
+・live：[動] 生きる
+【文法解説】
+・不定詞の受動態：to be lived（生きられるために）。it is here (人生はここにある) の存在目的・運命を表しています。
+【背景・ニュアンス】
+女優ケイト・ウィンスレット（等）の言葉。人生はあまりにも短く、いつ終わるか分からない。だからこそ、過去を悔やんだり未来を恐れて躊躇したりするのではなく、ただ全身全霊で「生き切る（be lived）」ためにこそ、今ここにあるのだというストレートな力強さです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・think：[動] 考える
+・act：[動] 行動する
+・hard：[形] 難しい、困難な
+【文法解説】
+・不定詞の名詞的用法：To think と To act がそれぞれの文の主語になっています。極限まで削ぎ落とされた、無駄のない対比構造です。
+【背景・ニュアンス】
+ドイツの文豪ゲーテの言葉。頭の中で理想や素晴らしい計画を「考える（think）」のは簡単である。しかし、それを物理的な現実に落とし込み「行動する（act）」ことは極めて困難である。だからこそ、行動する人間に価値があるという実践の哲学です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・genius：[名] 天才
+・inspiration：[名] ひらめき、インスピレーション
+・perspiration：[名] 汗、努力
+【文法解説】
+・脚韻（Rhyme）：in-spiration と pers-piration という、語尾が全く同じ響きの単語を並べることで、リズミカルな言葉遊び（ダジャレ）になっています。
+【背景・ニュアンス】
+発明王トーマス・エジソンの最も有名な言葉。「天才」とは、魔法のような突然のひらめき（1%）だけで成り立っているのではなく、そのアイデアを形にするための圧倒的で泥臭い努力と汗（99%）の結晶であるという、努力の天才ならではの定義です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・perfection：[名] 完璧
+・attainable：[形] 達成可能な
+・chase：[動] 追いかける
+・excellence：[名] 卓越性、素晴らしさ
+【文法解説】
+・not attainable の強調：unattainable と一語で言わず、not を独立させることで否定を強めています。
+・動詞の呼応：chase（追いかける）と catch（捕まえる）という動作の繋がり。
+【背景・ニュアンス】
+伝説のアメフトコーチ、ヴィンス・ロンバルディの言葉。人間に「完璧（perfection）」は不可能である。しかし、妥協せずに完璧を追い求め続ける（chase）その過程で、私たちは完璧に近い「卓越した素晴らしい結果（excellence）」を掴むことができるという向上心の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・contagious：[形] 伝染性の、うつりやすい
+・enthusiasm：[名] 熱意、情熱
+【文法解説】
+・否定主語の原級比較：Nothing is so... as 〜 で「〜ほど･･･なものは何もない（＝〜が一番･･･だ）」。最上級と同じ意味を、否定語を使ってよりドラマチックに表現しています。
+【背景・ニュアンス】
+イギリスの詩人コールリッジの言葉。どんな強力なウイルスよりも、あるいは論理的な説得や恐怖よりも、一人の人間が持つ本気の「熱意（enthusiasm）」こそが、最も強く人から人へと伝染し（contagious）、人を動かす力を持っているというリーダーシップの真髄です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・harbor：[名] 港
+・safe：[形] 安全な
+・build for：[熟] 〜のために造る
+【文法解説】
+・関係代名詞 what と前置詞 for：what ships are built for は「船が造られた目的（もの）」。
+【背景・ニュアンス】
+作家ジョン・A・シェッドの言葉。港（安全地帯）に停泊していれば、船が傷つくことはない。しかし、船は荒波の海へ出ていくために造られたのだ。人間も同じで、傷つくことを恐れて安全圏にいるだけでは、命の目的を果たしていないという挑戦のメタファーです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・character：[名] 人格、性格
+・right thing：正しいこと
+【文法解説】
+・when 節の現在進行形：when nobody's (nobody is) looking で「誰も見ていない時に（現在進行中で）」。
+【背景・ニュアンス】
+政治家J.C.ワッツ（またはC.S.ルイス等）の言葉。真の「人格（Character）」とは、他人に褒められたり評価されたりする場面で作られるものではない。完全に一人きりで、誰も見ていない時に「正しい行動（right thing）」をとれるかどうかで決まるという、高い道徳的基準です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・direction：[名] 方向
+・end up：[熟] 最終的に〜になる、行き着く
+・head：[動] 向かう、進む
+【文法解説】
+・end up + 副詞節 where：where you are heading で「あなたが現在向かっている（進行形の）場所へ」行き着いてしまう、という構造です。
+【背景・ニュアンス】
+古代中国の哲学者、老子の言葉の英訳。今、間違った方向に進んでいると気づいているなら、すぐに軌道修正（change direction）をしなければならない。そのまま歩き続ければ、当然望まない破滅的な結果にたどり着いてしまうという、当然だが忘れがちな警告です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・leave：[動] 残す、そのままにしておく
+・till：[前] 〜まで（untilと同じ）
+・tomorrow：[名] 明日
+【文法解説】
+・関係代名詞 which の分離：本来は leave [that which you can do today] till tomorrow という語順ですが、目的語が長すぎるため till tomorrow が間に挟まっています。「今日できること（that which）を明日まで残すな」。
+【背景・ニュアンス】
+アメリカ建国の父ベンジャミン・フランクリンの言葉。先延ばし癖を戒める最も有名な格言の一つです。今日できることを「明日でいいや」と残して（leave）しまうことは、時間の貴重さを無視した怠慢であり、成功を逃す最大の原因であると説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・permanent：[形] 永久の、不変の
+・except：[前] 〜を除いて
+・change：[名] 変化
+【文法解説】
+・否定語 + except：「〜を除いて何もない（＝〜だけである）」。nothing permanent（永遠なものは何もない）と except change（変化を除いて）を組み合わせて強い断定を作っています。
+・名詞の後置修飾：-thing で終わる代名詞は、形容詞（permanent）を後ろに置きます。
+【背景・ニュアンス】
+古代ギリシャの哲学者ヘラクレイトスの言葉「万物は流転する」の英訳。この世界に永遠に変わらないものなど一つも存在しない。唯一「常に変化し続ける」という事実だけが永遠不変の真理であるという、深い哲学的な洞察です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・path：[名] 道、軌道
+・lead：[動] 導く、つながる
+・instead：[副] 代わりに
+・trail：[名] （自分が歩いてできた）跡、足跡
+【文法解説】
+・関係副詞 where の副詞節用法：「〜する場所へ」。where the path may lead（すでにある道が導く場所へ）と where there is no path（道がない場所へ）が対比されています。
+・命令文の並列：Do not go（行くな）、go instead（代わりに行け）、and leave（そして残せ）。
+【背景・ニュアンス】
+思想家エマーソンの言葉。誰かがすでに作ってくれた安全な道（path）をただ歩くのではなく、まだ誰も足を踏み入れていない未開の地へ進み、そこにあなた自身の新しい道（trail）を切り拓けという、開拓者精神（フロンティア・スピリット）を説いた名言です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・wise：[形] 賢い、賢明な
+・opportunity：[名] 機会、チャンス
+【文法解説】
+・比較級を用いた対比：make more A than he finds（彼が見つけるAよりも、多くのAを作る）。
+・助動詞 will：ここでは「（賢明な人なら）〜するものだ」という強い習性や確信を表しています。
+【背景・ニュアンス】
+イギリスの哲学者フランシス・ベーコンの言葉。成功のチャンスが向こうから偶然やって来るのを待ったり「見つけたり（finds）」するのではなく、真に賢い人間は、自らの知恵と行動でチャンスそのものを「創り出す（make）」のだという主体性の教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・find out：[熟] 見つけ出す、気づく
+・why：[副] なぜ（存在理由）
+【文法解説】
+・関係副詞 when の省略：the day (when) you are born と the day (when) you find out で、それぞれ「〜した日」という名詞句を作っています。
+・間接疑問文の省略：why の後ろに you were born が省略され、「なぜ自分が生まれたのか」という究極の問いを表しています。
+【背景・ニュアンス】
+作家マーク・トウェインの言葉。人生で最も重要なのは「この世に生を受けた日」。そして次に重要なのは、自分の才能や情熱を注ぐべき使命（なぜ生まれたのか＝why）を発見した日であるという、人生の意味に関する美しく力強いメッセージです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・passion：[名] 情熱
+・boredom：[名] 退屈
+【文法解説】
+・would rather A than B：BするくらいならAしたい。
+・die of：〜（病気や感情など）が原因で死ぬ。die of passion（情熱によって死ぬ）と die of boredom（退屈によって死ぬ）を鮮やかに対比させています。
+【背景・ニュアンス】
+画家ゴッホの言葉。波風の立たない安全で退屈（boredom）な人生を長く生き延びるよりも、たとえ身を滅ぼすことになっても、自分の絵や信念に対する燃えるような情熱（passion）に命を捧げたいという、芸術家としての凄まじい覚悟です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・logic：[名] 論理、理屈
+・imagination：[名] 想像力
+【文法解説】
+・get A to B：AをBへ到着させる、連れて行く。get you from A to B は「あなたをA地点からB地点へ（予測通りに）連れて行く」。
+・take A to B：AをBへ連れて行く。take you everywhere で「あなたを（論理の枠を超えた）どこへでも連れて行く」。
+【背景・ニュアンス】
+アインシュタインの言葉。論理（Logic）は確かに便利で、私たちを確実な「正解（AからB）」へと導いてくれる。しかし、未知の世界を切り拓き、無限の可能性（everywhere）へと私たちを飛ばしてくれるのは、理屈ではなく「想像力（Imagination）」なのだという科学者の直感です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・whatever：[代] 〜するものは何でも
+・well：[副] 上手に、立派に
+【文法解説】
+・複合関係代名詞の譲歩用法：Whatever you do で「あなたが何をしようとも」。
+・代名詞 it：it は直前の Whatever you do（あなたがやることになったその行為）を指しています。
+【背景・ニュアンス】
+ウォルト・ディズニー（またはリンカーン等の言葉とされる）。仕事の規模や種類に貴賤はない。与えられた役割がどんなに些細なことであっても、それに全力で取り組み「立派にやり遂げなさい（do it well）」という、誠実さと職業倫理の基本を説いています。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・average：[名] 平均
+・spend time with：[熟] 〜と一緒に時間を過ごす
+【文法解説】
+・関係代名詞の省略：the five people (who/whom) you spend the most time with。the most は time にかかる形容詞の最上級で「最も多くの時間」。前置詞 with が最後に残るのが文法的なポイントです。
+【背景・ニュアンス】
+起業家ジム・ローンの有名な言葉。人間の思考や習慣は、環境（周囲の人間）に大きく影響される。あなたが一番長く一緒にいる5人の友人や同僚を思い浮かべれば、その「平均値」がそのまま現在のあなたのレベル（収入や幸福度）になるという、人間関係の法則です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・fortune：[名] 運命の女神、幸運
+・favor：[動] 好む、〜に味方する
+・bold：[形] 大胆な、勇敢な
+【文法解説】
+・The + 形容詞：the bold で「大胆な人々（the bold people）」という複数名詞の扱いになります。
+・擬人化：Fortune（幸運）を主語にし、自らの意志で味方を選ぶ女神のように扱っています。
+【背景・ニュアンス】
+古代ローマの詩人ウェルギリウスらが残したラテン語の格言（Audentes fortuna iuvat）の英訳。運命や幸運というものは、安全地帯で怯えている人間には決して微笑まない。リスクを取って「大胆に行動する者（the bold）」にこそ味方をするという力強い教訓です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・laugh：[動] 笑う
+・learn：[動] 学ぶ
+【文法解説】
+・代名詞 He + 関係代名詞 who：He who... で「〜する人は」。He who laughs most が主語の塊です。
+・副詞の最上級：most（最も多く）と best（最も上手に）が、短い対句の中で美しく対応しています。
+【背景・ニュアンス】
+コメディアンのジョン・クリーズ（等の類似の格言）。学習というとしかめっ面で机に向かうイメージがあるが、実は人間が一番効率よく深く学べるのは、リラックスして「最も笑っている（楽しんでいる）」時であるという、教育やユーモアの本質を突いた言葉です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・take away：[熟] 奪い去る、持ち去る
+【文法解説】
+・名詞節の省略：is の後ろに接続詞 that が省略されています。「学ぶことの素晴らしさは、誰もそれをあなたから奪えない（ということ）だ」。
+・代名詞 it：learning（学んだ知識や経験）を指します。
+【背景・ニュアンス】
+ブルースの王様B.B.キングの言葉。お金や家、地位などの「物質的な財産」は、災害や不運によって他人に奪われたり失ったりする可能性がある。しかし、一度自分の頭と体で「学んだこと（learning）」は、一生誰にも奪われない最高の財産であるという真理です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・handle：[動] 扱う、対処する
+・worst：[名] 最悪の事態（bad の最上級）
+【文法解説】
+・不定詞の副詞的用法：To be the best で「最高（の存在）になるためには」。
+・The + 最上級の名詞化：the best（最高のもの）と the worst（最悪のもの）を対比させています。
+【背景・ニュアンス】
+ウィルソン・カナディの言葉。「頂点（best）」に立つ人間は、単に調子が良い時に素晴らしいパフォーマンスを出せる人間のことではない。絶不調の時や「最悪のトラブル（worst）」が起きた時に、冷静にそれに対処（handle）できる人間のことであるという厳しい教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・mind：[名] 精神、知性、人
+・discuss：[動] 議論する
+・event：[名] 出来事
+【文法解説】
+・3段構成の対比：Great / average / small という3つのレベルの minds（人々）が、それぞれ ideas（思想） / events（出来事） / people（他人の噂話）を議論するという、見事な段階的対比の構文です。
+【背景・ニュアンス】
+エレノア・ルーズベルトの言葉。人間の精神のレベルは、普段何を話しているかで決まる。次元の低い人は「他人の噂話」をし、普通の人は「起きたニュース」を話す。しかし優れた人物は、未来を創る「思想やアイデア」について語り合うという、会話の質に関する戒めです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・risk -ing：[熟] 〜する危険を冒す
+・go too far：行き過ぎる
+・possibly：[副] ひょっとすると、何とかして（canと結びついて「〜できるかもしれない」）
+【文法解説】
+・those who：〜する人々（主語）。
+・間接疑問文：find out の目的語として how far one can go（人はどこまで遠くへ行けるか）が入っています。代名詞 one は「（一般に）人」を表します。
+【背景・ニュアンス】
+詩人T.S.エリオットの言葉。「これ以上行ったら危ない（行き過ぎだ）」という限界の境界線を、あえて踏み越えるリスクを取った人間だけが、自分（人間）の本当の限界地点がどこにあるのかを知ることができるという、挑戦者への強烈なメッセージです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・during：[前] 〜の間
+・focus：[動] 集中する、ピントを合わせる
+【文法解説】
+・It is... that の強調構文：「私たちが集中しなければならないのは、まさに最悪の暗闇の時（during our darkest moments）だ」と、前置詞句を強調しています。
+・不定詞の副詞的用法：to see the light（光を見るために）。
+【背景・ニュアンス】
+大富豪アリストテレス・オナシスの言葉。人生のどん底や絶望の「暗闇（darkest moments）」にいる時こそ、パニックにならずに目を凝らし、かすかな希望の「光（light）」を見つけるために全神経を集中（focus）させなければならないという、逆境でのマインドセットです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・revenge：[名] 復讐
+・unlike：[前] 〜とは違って
+・perform：[動] 行う、実行する
+・injury：[名] 害、傷
+【文法解説】
+・不定詞の名詞的用法：is to be unlike...（〜と違っていることだ）。
+・関係代名詞 who：him who... は「〜した彼（その人）」。文語的な表現です。
+【背景・ニュアンス】
+ローマ皇帝にしてストア派哲学者マルクス・アウレリウスの言葉。自分を傷つけた相手に対して同じレベルに降りていってやり返すのではなく、そんな卑劣な人間とは「全く違う高潔な自分であり続ける（unlike him）」ことこそが、相手への最大の復讐であるという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・parachute：[名] パラシュート
+【文法解説】
+・直喩法（Simile）：is like a parachute（パラシュートのようだ）。
+・条件の副詞節と代名詞：if it is not open の it は A mind（人間の心や精神）を指します。
+【背景・ニュアンス】
+音楽家フランク・ザッパの言葉。人間の「心（mind）」をパラシュートに例えた見事なジョークと真理。パラシュートは「開いて（open）」いなければ墜落してしまうのと同じで、人間の心や頭脳も、新しい意見に対して「オープン（開かれた状態）」でなければ全く機能しないという教えです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・keep going：[熟] 進み続ける
+・perfect：[形] 完璧な
+【文法解説】
+・関係代名詞の省略：Everything (that) you need（あなたが必要とするすべてのもの）。
+・未来形 will：必ず〜やって来るだろうという確信を表します。
+【背景・ニュアンス】
+広く共有されている自己啓発の言葉。今は結果が出なくて焦っていても、決して足を止めてはならない（Keep going）。あなたが望むものや必要なスキル、人脈は、早すぎず遅すぎず、あなたの人生において最も「完璧なタイミング（perfect time）」で必ず引き寄せられるという励ましです。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・regret：[動] 後悔する
+・chance：[名] 機会、チャンス
+【文法解説】
+・関係代名詞の省略：the chances (that/which) we didn't take。
+・take a chance：チャンスを掴む、思い切ってやってみる。
+【背景・ニュアンス】
+ルイス・キャロルなどの言葉とされる名言。人生の最期（In the end）に人間が深く後悔するのは、「挑戦して失敗したこと」ではない。「あの時やっておけばよかった」と、挑戦のチャンスを「見送ってしまったこと（didn't take）」だけであるという、死生観から逆算した行動の原則です。</t>
+  </si>
+  <si>
+    <t>【単語解説】
+・lose：[動] 負ける、失う
+・either A or B：[熟] AかBのどちらか
+【文法解説】
+・never による全否定：I never lose（私は絶対に負けない）。
+・等位接続詞 or：win（勝つ）と learn（学ぶ）という2つの動詞を並列させています。
+【背景・ニュアンス】
+ネルソン・マンデラの言葉。人生におけるすべての挑戦の結果は、成功して「勝利する（win）」か、失敗から教訓を「学ぶ（learn）」かの2つに1つしかない。つまり、「敗北（lose）」という概念自体が自分の人生には存在しないという、究極のポジティブなマインドセットです。</t>
   </si>
 </sst>
 </file>
@@ -5998,7 +7888,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1623</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="336">
@@ -6021,10 +7911,10 @@
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="336">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="315">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6044,10 +7934,10 @@
         <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="315">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="336">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6067,10 +7957,10 @@
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1626</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="336">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="357">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6090,10 +7980,10 @@
         <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1627</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="105">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="315">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6113,10 +8003,10 @@
         <v>9</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="126">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="315">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6136,10 +8026,10 @@
         <v>9</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1529</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="126">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="294">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6159,10 +8049,10 @@
         <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="126">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="315">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6182,10 +8072,10 @@
         <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1531</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="105">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="315">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6205,10 +8095,10 @@
         <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1532</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="84">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="315">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6228,10 +8118,10 @@
         <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="105">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="273">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6251,10 +8141,10 @@
         <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="105">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="294">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6274,10 +8164,10 @@
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1535</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="105">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="336">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6297,10 +8187,10 @@
         <v>9</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1536</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="84">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="315">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6320,10 +8210,10 @@
         <v>9</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="105">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="273">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6343,10 +8233,10 @@
         <v>9</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="105">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="336">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6366,10 +8256,10 @@
         <v>9</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="105">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="294">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6389,10 +8279,10 @@
         <v>9</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="105">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="336">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6412,10 +8302,10 @@
         <v>9</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="105">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="315">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6435,10 +8325,10 @@
         <v>9</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="105">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="315">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6458,10 +8348,10 @@
         <v>9</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="105">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="294">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6481,10 +8371,10 @@
         <v>9</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1544</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="84">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="273">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6504,10 +8394,10 @@
         <v>9</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="84">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="315">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6527,10 +8417,10 @@
         <v>9</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="84">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="294">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6550,10 +8440,10 @@
         <v>9</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1547</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="84">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="336">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6573,10 +8463,10 @@
         <v>9</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="84">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="294">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6596,10 +8486,10 @@
         <v>9</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="84">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="315">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6619,10 +8509,10 @@
         <v>9</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="84">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="294">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6642,10 +8532,10 @@
         <v>9</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="105">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="273">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6665,10 +8555,10 @@
         <v>9</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1552</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="84">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="315">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6688,10 +8578,10 @@
         <v>9</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1553</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="84">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="294">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6711,10 +8601,10 @@
         <v>9</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1554</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="84">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="273">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6734,10 +8624,10 @@
         <v>9</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1555</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="105">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="315">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6757,10 +8647,10 @@
         <v>9</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1556</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="84">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="273">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6780,10 +8670,10 @@
         <v>9</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="84">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="294">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6803,10 +8693,10 @@
         <v>9</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1558</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="84">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="273">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6826,10 +8716,10 @@
         <v>9</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1559</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="105">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="315">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6849,10 +8739,10 @@
         <v>9</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="84">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="294">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6872,10 +8762,10 @@
         <v>9</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1561</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="105">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="336">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6895,10 +8785,10 @@
         <v>9</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1562</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="84">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="273">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6918,10 +8808,10 @@
         <v>9</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1563</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="84">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="315">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6941,10 +8831,10 @@
         <v>9</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1564</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="105">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="294">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6964,10 +8854,10 @@
         <v>9</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1565</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="105">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="294">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6987,10 +8877,10 @@
         <v>9</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1566</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="84">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="273">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7010,10 +8900,10 @@
         <v>9</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1567</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="84">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="252">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7033,10 +8923,10 @@
         <v>9</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1568</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="105">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="315">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7056,10 +8946,10 @@
         <v>9</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1569</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="105">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="273">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7079,10 +8969,10 @@
         <v>9</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="105">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="294">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7102,10 +8992,10 @@
         <v>9</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1571</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="84">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="294">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7125,10 +9015,10 @@
         <v>9</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1572</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="105">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="273">
       <c r="A52">
         <v>51</v>
       </c>
@@ -7148,10 +9038,10 @@
         <v>9</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1573</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="105">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="273">
       <c r="A53">
         <v>52</v>
       </c>
@@ -7171,10 +9061,10 @@
         <v>9</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1574</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="105">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="273">
       <c r="A54">
         <v>53</v>
       </c>
@@ -7194,10 +9084,10 @@
         <v>9</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="84">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="252">
       <c r="A55">
         <v>54</v>
       </c>
@@ -7217,10 +9107,10 @@
         <v>9</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="84">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="252">
       <c r="A56">
         <v>55</v>
       </c>
@@ -7240,10 +9130,10 @@
         <v>9</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1577</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="84">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="273">
       <c r="A57">
         <v>56</v>
       </c>
@@ -7263,10 +9153,10 @@
         <v>9</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1578</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="105">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="252">
       <c r="A58">
         <v>57</v>
       </c>
@@ -7286,10 +9176,10 @@
         <v>9</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1579</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="84">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="273">
       <c r="A59">
         <v>58</v>
       </c>
@@ -7309,10 +9199,10 @@
         <v>9</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1580</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="84">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="294">
       <c r="A60">
         <v>59</v>
       </c>
@@ -7332,10 +9222,10 @@
         <v>9</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1581</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="84">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="273">
       <c r="A61">
         <v>60</v>
       </c>
@@ -7355,10 +9245,10 @@
         <v>9</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1582</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="84">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="315">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7378,10 +9268,10 @@
         <v>9</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1583</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="84">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="273">
       <c r="A63">
         <v>62</v>
       </c>
@@ -7401,10 +9291,10 @@
         <v>9</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1584</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="84">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="273">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7424,10 +9314,10 @@
         <v>9</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1585</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="105">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="294">
       <c r="A65">
         <v>64</v>
       </c>
@@ -7447,10 +9337,10 @@
         <v>9</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1586</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="84">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="294">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7470,10 +9360,10 @@
         <v>9</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1587</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="84">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="294">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7493,10 +9383,10 @@
         <v>9</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1588</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="84">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="273">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7516,10 +9406,10 @@
         <v>9</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1589</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="84">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="294">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7539,10 +9429,10 @@
         <v>9</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="84">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="273">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7562,10 +9452,10 @@
         <v>9</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1591</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="84">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="252">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7585,10 +9475,10 @@
         <v>9</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1592</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="84">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="273">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7608,10 +9498,10 @@
         <v>9</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="84">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="252">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7631,10 +9521,10 @@
         <v>9</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1594</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="84">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="252">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7654,10 +9544,10 @@
         <v>9</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="84">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="231">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7677,10 +9567,10 @@
         <v>9</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1596</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="84">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="231">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7700,10 +9590,10 @@
         <v>9</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1597</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="84">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="273">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7723,10 +9613,10 @@
         <v>9</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1598</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="84">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="252">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7746,10 +9636,10 @@
         <v>9</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1599</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="84">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="210">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7769,10 +9659,10 @@
         <v>9</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="84">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="252">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7792,10 +9682,10 @@
         <v>9</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="105">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="273">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7815,10 +9705,10 @@
         <v>9</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="105">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="315">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7838,10 +9728,10 @@
         <v>9</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="84">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="273">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7861,10 +9751,10 @@
         <v>9</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>1604</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="84">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="273">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7884,10 +9774,10 @@
         <v>9</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>1605</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="105">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="273">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7907,10 +9797,10 @@
         <v>9</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1606</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="84">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="315">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7930,10 +9820,10 @@
         <v>9</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="63">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="273">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7953,10 +9843,10 @@
         <v>9</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>1608</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="84">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="273">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7976,10 +9866,10 @@
         <v>9</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1609</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="84">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="252">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7999,10 +9889,10 @@
         <v>9</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="84">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="252">
       <c r="A90">
         <v>89</v>
       </c>
@@ -8022,10 +9912,10 @@
         <v>9</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1611</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="84">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="252">
       <c r="A91">
         <v>90</v>
       </c>
@@ -8045,10 +9935,10 @@
         <v>9</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1612</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="84">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="315">
       <c r="A92">
         <v>91</v>
       </c>
@@ -8068,10 +9958,10 @@
         <v>9</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>1613</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="84">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="315">
       <c r="A93">
         <v>92</v>
       </c>
@@ -8091,10 +9981,10 @@
         <v>9</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1614</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="84">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="273">
       <c r="A94">
         <v>93</v>
       </c>
@@ -8114,10 +10004,10 @@
         <v>9</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="105">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="273">
       <c r="A95">
         <v>94</v>
       </c>
@@ -8137,10 +10027,10 @@
         <v>9</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="84">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="252">
       <c r="A96">
         <v>95</v>
       </c>
@@ -8160,10 +10050,10 @@
         <v>9</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1617</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="84">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="315">
       <c r="A97">
         <v>96</v>
       </c>
@@ -8183,10 +10073,10 @@
         <v>9</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>1618</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="84">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="273">
       <c r="A98">
         <v>97</v>
       </c>
@@ -8206,10 +10096,10 @@
         <v>9</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>1619</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="84">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="252">
       <c r="A99">
         <v>98</v>
       </c>
@@ -8229,10 +10119,10 @@
         <v>9</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="84">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="273">
       <c r="A100">
         <v>99</v>
       </c>
@@ -8252,10 +10142,10 @@
         <v>9</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="84">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="252">
       <c r="A101">
         <v>100</v>
       </c>
@@ -8275,10 +10165,10 @@
         <v>9</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1622</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="84">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="294">
       <c r="A102">
         <v>101</v>
       </c>
@@ -8298,10 +10188,10 @@
         <v>9</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="84">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="252">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8321,10 +10211,10 @@
         <v>9</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="84">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="294">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8344,10 +10234,10 @@
         <v>9</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="84">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="273">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8367,10 +10257,10 @@
         <v>9</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="84">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="294">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8390,10 +10280,10 @@
         <v>9</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="84">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="252">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8413,10 +10303,10 @@
         <v>9</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="84">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="294">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8436,10 +10326,10 @@
         <v>9</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="84">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="294">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8459,10 +10349,10 @@
         <v>9</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="84">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="273">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8482,10 +10372,10 @@
         <v>9</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="84">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="294">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8505,10 +10395,10 @@
         <v>9</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="84">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="294">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8528,10 +10418,10 @@
         <v>9</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="84">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="294">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8551,10 +10441,10 @@
         <v>9</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="84">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="273">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8574,10 +10464,10 @@
         <v>9</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="84">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="294">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8597,10 +10487,10 @@
         <v>9</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="84">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="315">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8620,10 +10510,10 @@
         <v>9</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="84">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="294">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8643,10 +10533,10 @@
         <v>9</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="84">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="294">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8666,10 +10556,10 @@
         <v>9</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="84">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="252">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8689,10 +10579,10 @@
         <v>9</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="84">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="273">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8712,10 +10602,10 @@
         <v>9</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="84">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="294">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8735,10 +10625,10 @@
         <v>9</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="84">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="273">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8758,10 +10648,10 @@
         <v>9</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="84">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="252">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8781,10 +10671,10 @@
         <v>9</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="84">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="252">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8804,10 +10694,10 @@
         <v>9</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="84">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="294">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8827,10 +10717,10 @@
         <v>9</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="84">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="273">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8850,10 +10740,10 @@
         <v>9</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="84">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="273">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8873,10 +10763,10 @@
         <v>9</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="84">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="273">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8896,10 +10786,10 @@
         <v>9</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="84">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="273">
       <c r="A129">
         <v>128</v>
       </c>
@@ -8919,10 +10809,10 @@
         <v>9</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="84">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="315">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8942,10 +10832,10 @@
         <v>9</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="84">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="336">
       <c r="A131">
         <v>130</v>
       </c>
@@ -8965,10 +10855,10 @@
         <v>9</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="84">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="315">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8988,10 +10878,10 @@
         <v>9</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="84">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="273">
       <c r="A133">
         <v>132</v>
       </c>
@@ -9011,10 +10901,10 @@
         <v>9</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="84">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="252">
       <c r="A134">
         <v>133</v>
       </c>
@@ -9034,10 +10924,10 @@
         <v>9</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="84">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="273">
       <c r="A135">
         <v>134</v>
       </c>
@@ -9057,10 +10947,10 @@
         <v>9</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="84">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="231">
       <c r="A136">
         <v>135</v>
       </c>
@@ -9080,10 +10970,10 @@
         <v>9</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="84">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="273">
       <c r="A137">
         <v>136</v>
       </c>
@@ -9103,10 +10993,10 @@
         <v>9</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="84">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="273">
       <c r="A138">
         <v>137</v>
       </c>
@@ -9126,10 +11016,10 @@
         <v>9</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="84">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="273">
       <c r="A139">
         <v>138</v>
       </c>
@@ -9149,10 +11039,10 @@
         <v>9</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="84">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="273">
       <c r="A140">
         <v>139</v>
       </c>
@@ -9172,10 +11062,10 @@
         <v>9</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="84">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="294">
       <c r="A141">
         <v>140</v>
       </c>
@@ -9195,10 +11085,10 @@
         <v>9</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="84">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="273">
       <c r="A142">
         <v>141</v>
       </c>
@@ -9218,10 +11108,10 @@
         <v>9</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="84">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="273">
       <c r="A143">
         <v>142</v>
       </c>
@@ -9241,10 +11131,10 @@
         <v>9</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="84">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="273">
       <c r="A144">
         <v>143</v>
       </c>
@@ -9264,10 +11154,10 @@
         <v>9</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="84">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="252">
       <c r="A145">
         <v>144</v>
       </c>
@@ -9287,10 +11177,10 @@
         <v>9</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="84">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="273">
       <c r="A146">
         <v>145</v>
       </c>
@@ -9310,10 +11200,10 @@
         <v>9</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="84">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="315">
       <c r="A147">
         <v>146</v>
       </c>
@@ -9333,10 +11223,10 @@
         <v>9</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="84">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="294">
       <c r="A148">
         <v>147</v>
       </c>
@@ -9356,10 +11246,10 @@
         <v>9</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="84">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="273">
       <c r="A149">
         <v>148</v>
       </c>
@@ -9379,10 +11269,10 @@
         <v>9</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="84">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="294">
       <c r="A150">
         <v>149</v>
       </c>
@@ -9402,10 +11292,10 @@
         <v>9</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="84">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="315">
       <c r="A151">
         <v>150</v>
       </c>
@@ -9425,10 +11315,10 @@
         <v>9</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="84">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="357">
       <c r="A152">
         <v>151</v>
       </c>
@@ -9448,10 +11338,10 @@
         <v>9</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="84">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="294">
       <c r="A153">
         <v>152</v>
       </c>
@@ -9471,10 +11361,10 @@
         <v>9</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="84">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="294">
       <c r="A154">
         <v>153</v>
       </c>
@@ -9494,10 +11384,10 @@
         <v>9</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="84">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="273">
       <c r="A155">
         <v>154</v>
       </c>
@@ -9517,10 +11407,10 @@
         <v>9</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="84">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="294">
       <c r="A156">
         <v>155</v>
       </c>
@@ -9540,10 +11430,10 @@
         <v>9</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="84">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="294">
       <c r="A157">
         <v>156</v>
       </c>
@@ -9563,10 +11453,10 @@
         <v>9</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="84">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="273">
       <c r="A158">
         <v>157</v>
       </c>
@@ -9586,10 +11476,10 @@
         <v>9</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="84">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="252">
       <c r="A159">
         <v>158</v>
       </c>
@@ -9609,10 +11499,10 @@
         <v>9</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="84">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="273">
       <c r="A160">
         <v>159</v>
       </c>
@@ -9632,10 +11522,10 @@
         <v>9</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="84">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="357">
       <c r="A161">
         <v>160</v>
       </c>
@@ -9655,10 +11545,10 @@
         <v>9</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="84">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="357">
       <c r="A162">
         <v>161</v>
       </c>
@@ -9678,10 +11568,10 @@
         <v>9</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="84">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="252">
       <c r="A163">
         <v>162</v>
       </c>
@@ -9701,10 +11591,10 @@
         <v>9</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="84">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="357">
       <c r="A164">
         <v>163</v>
       </c>
@@ -9724,10 +11614,10 @@
         <v>9</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="84">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="315">
       <c r="A165">
         <v>164</v>
       </c>
@@ -9747,10 +11637,10 @@
         <v>9</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="84">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="273">
       <c r="A166">
         <v>165</v>
       </c>
@@ -9770,10 +11660,10 @@
         <v>9</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="63">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="315">
       <c r="A167">
         <v>166</v>
       </c>
@@ -9793,10 +11683,10 @@
         <v>9</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="84">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="273">
       <c r="A168">
         <v>167</v>
       </c>
@@ -9816,10 +11706,10 @@
         <v>9</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="84">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="294">
       <c r="A169">
         <v>168</v>
       </c>
@@ -9839,10 +11729,10 @@
         <v>9</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="84">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="294">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9862,10 +11752,10 @@
         <v>9</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="84">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="294">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9885,10 +11775,10 @@
         <v>9</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="84">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="315">
       <c r="A172">
         <v>171</v>
       </c>
@@ -9908,10 +11798,10 @@
         <v>9</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="84">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="315">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9931,10 +11821,10 @@
         <v>9</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="84">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="294">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9954,10 +11844,10 @@
         <v>9</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="84">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="273">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9977,10 +11867,10 @@
         <v>9</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="84">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="294">
       <c r="A176">
         <v>175</v>
       </c>
@@ -10000,10 +11890,10 @@
         <v>9</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="84">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="252">
       <c r="A177">
         <v>176</v>
       </c>
@@ -10023,10 +11913,10 @@
         <v>9</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="84">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="273">
       <c r="A178">
         <v>177</v>
       </c>
@@ -10046,10 +11936,10 @@
         <v>9</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="84">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="294">
       <c r="A179">
         <v>178</v>
       </c>
@@ -10069,10 +11959,10 @@
         <v>9</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="84">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="294">
       <c r="A180">
         <v>179</v>
       </c>
@@ -10092,10 +11982,10 @@
         <v>9</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="84">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="252">
       <c r="A181">
         <v>180</v>
       </c>
@@ -10115,10 +12005,10 @@
         <v>9</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="84">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="294">
       <c r="A182">
         <v>181</v>
       </c>
@@ -10138,10 +12028,10 @@
         <v>9</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="84">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="294">
       <c r="A183">
         <v>182</v>
       </c>
@@ -10161,10 +12051,10 @@
         <v>9</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="84">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="273">
       <c r="A184">
         <v>183</v>
       </c>
@@ -10184,10 +12074,10 @@
         <v>9</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="84">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="315">
       <c r="A185">
         <v>184</v>
       </c>
@@ -10207,10 +12097,10 @@
         <v>9</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="84">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="294">
       <c r="A186">
         <v>185</v>
       </c>
@@ -10230,10 +12120,10 @@
         <v>9</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="84">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="294">
       <c r="A187">
         <v>186</v>
       </c>
@@ -10253,10 +12143,10 @@
         <v>9</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="84">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="273">
       <c r="A188">
         <v>187</v>
       </c>
@@ -10276,10 +12166,10 @@
         <v>9</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="84">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="273">
       <c r="A189">
         <v>188</v>
       </c>
@@ -10299,10 +12189,10 @@
         <v>9</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="84">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="315">
       <c r="A190">
         <v>189</v>
       </c>
@@ -10322,10 +12212,10 @@
         <v>9</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="84">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="273">
       <c r="A191">
         <v>190</v>
       </c>
@@ -10345,10 +12235,10 @@
         <v>9</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="84">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="273">
       <c r="A192">
         <v>191</v>
       </c>
@@ -10368,10 +12258,10 @@
         <v>9</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="84">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="252">
       <c r="A193">
         <v>192</v>
       </c>
@@ -10391,10 +12281,10 @@
         <v>9</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="84">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="294">
       <c r="A194">
         <v>193</v>
       </c>
@@ -10414,10 +12304,10 @@
         <v>9</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="84">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="273">
       <c r="A195">
         <v>194</v>
       </c>
@@ -10437,10 +12327,10 @@
         <v>9</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="84">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="252">
       <c r="A196">
         <v>195</v>
       </c>
@@ -10460,10 +12350,10 @@
         <v>9</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="84">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="294">
       <c r="A197">
         <v>196</v>
       </c>
@@ -10483,10 +12373,10 @@
         <v>9</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="84">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="294">
       <c r="A198">
         <v>197</v>
       </c>
@@ -10506,10 +12396,10 @@
         <v>9</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="84">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="252">
       <c r="A199">
         <v>198</v>
       </c>
@@ -10529,10 +12419,10 @@
         <v>9</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="84">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="273">
       <c r="A200">
         <v>199</v>
       </c>
@@ -10552,10 +12442,10 @@
         <v>9</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="84">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="273">
       <c r="A201">
         <v>200</v>
       </c>
@@ -10575,10 +12465,10 @@
         <v>9</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="63">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="273">
       <c r="A202">
         <v>201</v>
       </c>
@@ -10598,10 +12488,10 @@
         <v>9</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="42">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="231">
       <c r="A203">
         <v>202</v>
       </c>
@@ -10621,10 +12511,10 @@
         <v>9</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" ht="42">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="252">
       <c r="A204">
         <v>203</v>
       </c>
@@ -10644,10 +12534,10 @@
         <v>9</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="63">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="273">
       <c r="A205">
         <v>204</v>
       </c>
@@ -10667,10 +12557,10 @@
         <v>9</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="42">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="273">
       <c r="A206">
         <v>205</v>
       </c>
@@ -10690,10 +12580,10 @@
         <v>9</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="63">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="273">
       <c r="A207">
         <v>206</v>
       </c>
@@ -10713,10 +12603,10 @@
         <v>9</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="63">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="357">
       <c r="A208">
         <v>207</v>
       </c>
@@ -10736,10 +12626,10 @@
         <v>9</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="42">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="273">
       <c r="A209">
         <v>208</v>
       </c>
@@ -10759,10 +12649,10 @@
         <v>9</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="42">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="273">
       <c r="A210">
         <v>209</v>
       </c>
@@ -10782,10 +12672,10 @@
         <v>9</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="42">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="315">
       <c r="A211">
         <v>210</v>
       </c>
@@ -10805,10 +12695,10 @@
         <v>9</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" ht="63">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" ht="294">
       <c r="A212">
         <v>211</v>
       </c>
@@ -10828,10 +12718,10 @@
         <v>9</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="42">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="294">
       <c r="A213">
         <v>212</v>
       </c>
@@ -10851,10 +12741,10 @@
         <v>9</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" ht="63">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="294">
       <c r="A214">
         <v>213</v>
       </c>
@@ -10874,10 +12764,10 @@
         <v>9</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" ht="63">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="315">
       <c r="A215">
         <v>214</v>
       </c>
@@ -10897,10 +12787,10 @@
         <v>9</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" ht="42">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="294">
       <c r="A216">
         <v>215</v>
       </c>
@@ -10920,10 +12810,10 @@
         <v>9</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" ht="42">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="357">
       <c r="A217">
         <v>216</v>
       </c>
@@ -10943,10 +12833,10 @@
         <v>9</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="63">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="294">
       <c r="A218">
         <v>217</v>
       </c>
@@ -10966,10 +12856,10 @@
         <v>9</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="63">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="273">
       <c r="A219">
         <v>218</v>
       </c>
@@ -10989,10 +12879,10 @@
         <v>9</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="42">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="273">
       <c r="A220">
         <v>219</v>
       </c>
@@ -11012,10 +12902,10 @@
         <v>9</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="63">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="294">
       <c r="A221">
         <v>220</v>
       </c>
@@ -11035,10 +12925,10 @@
         <v>9</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="42">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="315">
       <c r="A222">
         <v>221</v>
       </c>
@@ -11058,10 +12948,10 @@
         <v>9</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="63">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="315">
       <c r="A223">
         <v>222</v>
       </c>
@@ -11081,10 +12971,10 @@
         <v>9</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="42">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="294">
       <c r="A224">
         <v>223</v>
       </c>
@@ -11104,10 +12994,10 @@
         <v>9</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="63">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="273">
       <c r="A225">
         <v>224</v>
       </c>
@@ -11127,10 +13017,10 @@
         <v>9</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="63">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="336">
       <c r="A226">
         <v>225</v>
       </c>
@@ -11150,10 +13040,10 @@
         <v>9</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1387</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="42">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="273">
       <c r="A227">
         <v>226</v>
       </c>
@@ -11173,10 +13063,10 @@
         <v>9</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="63">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="294">
       <c r="A228">
         <v>227</v>
       </c>
@@ -11196,10 +13086,10 @@
         <v>9</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="63">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="315">
       <c r="A229">
         <v>228</v>
       </c>
@@ -11219,10 +13109,10 @@
         <v>9</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="63">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="315">
       <c r="A230">
         <v>229</v>
       </c>
@@ -11242,10 +13132,10 @@
         <v>9</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="63">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="315">
       <c r="A231">
         <v>230</v>
       </c>
@@ -11265,10 +13155,10 @@
         <v>9</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="63">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="252">
       <c r="A232">
         <v>231</v>
       </c>
@@ -11287,11 +13177,11 @@
       <c r="F232" t="s">
         <v>9</v>
       </c>
-      <c r="G232" s="1" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="42">
+      <c r="G232" s="2" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="294">
       <c r="A233">
         <v>232</v>
       </c>
@@ -11311,10 +13201,10 @@
         <v>9</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="42">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="294">
       <c r="A234">
         <v>233</v>
       </c>
@@ -11334,10 +13224,10 @@
         <v>9</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="63">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="294">
       <c r="A235">
         <v>234</v>
       </c>
@@ -11357,10 +13247,10 @@
         <v>9</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1396</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="42">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="273">
       <c r="A236">
         <v>235</v>
       </c>
@@ -11380,10 +13270,10 @@
         <v>9</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="42">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="273">
       <c r="A237">
         <v>236</v>
       </c>
@@ -11403,10 +13293,10 @@
         <v>9</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="63">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="294">
       <c r="A238">
         <v>237</v>
       </c>
@@ -11426,10 +13316,10 @@
         <v>9</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1399</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="42">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="315">
       <c r="A239">
         <v>238</v>
       </c>
@@ -11449,10 +13339,10 @@
         <v>9</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="63">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="273">
       <c r="A240">
         <v>239</v>
       </c>
@@ -11472,10 +13362,10 @@
         <v>9</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" ht="42">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="273">
       <c r="A241">
         <v>240</v>
       </c>
@@ -11495,10 +13385,10 @@
         <v>9</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1402</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="42">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="294">
       <c r="A242">
         <v>241</v>
       </c>
@@ -11518,10 +13408,10 @@
         <v>9</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1403</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="63">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="252">
       <c r="A243">
         <v>242</v>
       </c>
@@ -11541,10 +13431,10 @@
         <v>9</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1404</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" ht="42">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="273">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11564,10 +13454,10 @@
         <v>9</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" ht="42">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="273">
       <c r="A245">
         <v>244</v>
       </c>
@@ -11587,10 +13477,10 @@
         <v>9</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" ht="63">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" ht="336">
       <c r="A246">
         <v>245</v>
       </c>
@@ -11610,10 +13500,10 @@
         <v>9</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="63">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="252">
       <c r="A247">
         <v>246</v>
       </c>
@@ -11633,10 +13523,10 @@
         <v>9</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" ht="63">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="273">
       <c r="A248">
         <v>247</v>
       </c>
@@ -11656,10 +13546,10 @@
         <v>9</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" ht="63">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="273">
       <c r="A249">
         <v>248</v>
       </c>
@@ -11679,10 +13569,10 @@
         <v>9</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" ht="42">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="273">
       <c r="A250">
         <v>249</v>
       </c>
@@ -11702,10 +13592,10 @@
         <v>9</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" ht="63">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="294">
       <c r="A251">
         <v>250</v>
       </c>
@@ -11725,10 +13615,10 @@
         <v>9</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" ht="84">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" ht="315">
       <c r="A252">
         <v>251</v>
       </c>
@@ -11748,10 +13638,10 @@
         <v>9</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" ht="84">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="336">
       <c r="A253">
         <v>252</v>
       </c>
@@ -11771,10 +13661,10 @@
         <v>9</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" ht="84">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" ht="294">
       <c r="A254">
         <v>253</v>
       </c>
@@ -11794,10 +13684,10 @@
         <v>9</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" ht="84">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="294">
       <c r="A255">
         <v>254</v>
       </c>
@@ -11817,10 +13707,10 @@
         <v>9</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="84">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="273">
       <c r="A256">
         <v>255</v>
       </c>
@@ -11840,10 +13730,10 @@
         <v>9</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" ht="84">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" ht="315">
       <c r="A257">
         <v>256</v>
       </c>
@@ -11863,10 +13753,10 @@
         <v>9</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1418</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" ht="84">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" ht="273">
       <c r="A258">
         <v>257</v>
       </c>
@@ -11886,10 +13776,10 @@
         <v>9</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1419</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" ht="84">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="273">
       <c r="A259">
         <v>258</v>
       </c>
@@ -11909,10 +13799,10 @@
         <v>9</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" ht="84">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="315">
       <c r="A260">
         <v>259</v>
       </c>
@@ -11932,10 +13822,10 @@
         <v>9</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="84">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="294">
       <c r="A261">
         <v>260</v>
       </c>
@@ -11955,10 +13845,10 @@
         <v>9</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" ht="84">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" ht="252">
       <c r="A262">
         <v>261</v>
       </c>
@@ -11978,10 +13868,10 @@
         <v>9</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" ht="84">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" ht="294">
       <c r="A263">
         <v>262</v>
       </c>
@@ -12001,10 +13891,10 @@
         <v>9</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" ht="84">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" ht="315">
       <c r="A264">
         <v>263</v>
       </c>
@@ -12024,10 +13914,10 @@
         <v>9</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" ht="84">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" ht="315">
       <c r="A265">
         <v>264</v>
       </c>
@@ -12047,10 +13937,10 @@
         <v>9</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1426</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" ht="84">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" ht="294">
       <c r="A266">
         <v>265</v>
       </c>
@@ -12070,10 +13960,10 @@
         <v>9</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" ht="84">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" ht="315">
       <c r="A267">
         <v>266</v>
       </c>
@@ -12093,10 +13983,10 @@
         <v>9</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="84">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="252">
       <c r="A268">
         <v>267</v>
       </c>
@@ -12116,10 +14006,10 @@
         <v>9</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="84">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="273">
       <c r="A269">
         <v>268</v>
       </c>
@@ -12139,10 +14029,10 @@
         <v>9</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" ht="84">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" ht="273">
       <c r="A270">
         <v>269</v>
       </c>
@@ -12162,10 +14052,10 @@
         <v>9</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1431</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" ht="84">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" ht="273">
       <c r="A271">
         <v>270</v>
       </c>
@@ -12185,7 +14075,7 @@
         <v>9</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1432</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="272" spans="1:7" ht="84">
@@ -12208,7 +14098,7 @@
         <v>9</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1433</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="84">
@@ -12231,7 +14121,7 @@
         <v>9</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1434</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="84">
@@ -12254,7 +14144,7 @@
         <v>9</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1435</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="84">
@@ -12277,7 +14167,7 @@
         <v>9</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1436</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="84">
@@ -12300,7 +14190,7 @@
         <v>9</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1437</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="84">
@@ -12323,7 +14213,7 @@
         <v>9</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1438</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="84">
@@ -12346,7 +14236,7 @@
         <v>9</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1439</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="84">
@@ -12369,7 +14259,7 @@
         <v>9</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1440</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="84">
@@ -12392,7 +14282,7 @@
         <v>9</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1441</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="84">
@@ -12415,7 +14305,7 @@
         <v>9</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1442</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="84">
@@ -12438,7 +14328,7 @@
         <v>9</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1443</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="84">
@@ -12461,7 +14351,7 @@
         <v>9</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1444</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="284" spans="1:7" ht="84">
@@ -12484,7 +14374,7 @@
         <v>9</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1445</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="84">
@@ -12507,7 +14397,7 @@
         <v>9</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1446</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="84">
@@ -12530,7 +14420,7 @@
         <v>9</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1447</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="84">
@@ -12553,7 +14443,7 @@
         <v>9</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1448</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="84">
@@ -12576,7 +14466,7 @@
         <v>9</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1449</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="84">
@@ -12599,7 +14489,7 @@
         <v>9</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1450</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="290" spans="1:7" ht="84">
@@ -12622,7 +14512,7 @@
         <v>9</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1451</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="84">
@@ -12645,7 +14535,7 @@
         <v>9</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1452</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="84">
@@ -12668,7 +14558,7 @@
         <v>9</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1453</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="84">
@@ -12691,7 +14581,7 @@
         <v>9</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1454</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="84">
@@ -12714,7 +14604,7 @@
         <v>9</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>1455</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="295" spans="1:7" ht="84">
@@ -12737,7 +14627,7 @@
         <v>9</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1456</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="296" spans="1:7" ht="84">
@@ -12760,7 +14650,7 @@
         <v>9</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1457</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="297" spans="1:7" ht="84">
@@ -12783,7 +14673,7 @@
         <v>9</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1458</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="298" spans="1:7" ht="84">
@@ -12806,7 +14696,7 @@
         <v>9</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>1459</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="299" spans="1:7" ht="84">
@@ -12829,7 +14719,7 @@
         <v>9</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>1460</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="300" spans="1:7" ht="84">
@@ -12852,7 +14742,7 @@
         <v>9</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>1461</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="301" spans="1:7" ht="84">
@@ -12875,7 +14765,7 @@
         <v>9</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>1462</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="302" spans="1:7" ht="105">
@@ -12898,7 +14788,7 @@
         <v>9</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>1463</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="303" spans="1:7" ht="84">
@@ -12921,7 +14811,7 @@
         <v>9</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>1464</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="304" spans="1:7" ht="84">
@@ -12944,7 +14834,7 @@
         <v>9</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>1465</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="305" spans="1:7" ht="84">
@@ -12967,7 +14857,7 @@
         <v>9</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>1466</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="306" spans="1:7" ht="84">
@@ -12990,7 +14880,7 @@
         <v>9</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1467</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="307" spans="1:7" ht="84">
@@ -13013,7 +14903,7 @@
         <v>9</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1468</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="308" spans="1:7" ht="84">
@@ -13036,7 +14926,7 @@
         <v>9</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1469</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="309" spans="1:7" ht="84">
@@ -13059,7 +14949,7 @@
         <v>9</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1470</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="310" spans="1:7" ht="84">
@@ -13082,7 +14972,7 @@
         <v>9</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>1471</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="311" spans="1:7" ht="84">
@@ -13105,7 +14995,7 @@
         <v>9</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1472</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="312" spans="1:7" ht="84">
@@ -13128,7 +15018,7 @@
         <v>9</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>1473</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="313" spans="1:7" ht="84">
@@ -13151,7 +15041,7 @@
         <v>9</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>1474</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="314" spans="1:7" ht="84">
@@ -13174,7 +15064,7 @@
         <v>9</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>1475</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="315" spans="1:7" ht="84">
@@ -13197,7 +15087,7 @@
         <v>9</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>1476</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="316" spans="1:7" ht="84">
@@ -13220,7 +15110,7 @@
         <v>9</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>1477</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="317" spans="1:7" ht="84">
@@ -13243,7 +15133,7 @@
         <v>9</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1478</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="318" spans="1:7" ht="84">
@@ -13266,7 +15156,7 @@
         <v>9</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1479</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="319" spans="1:7" ht="84">
@@ -13289,7 +15179,7 @@
         <v>9</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>1480</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="320" spans="1:7" ht="84">
@@ -13312,7 +15202,7 @@
         <v>9</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1481</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="321" spans="1:7" ht="84">
@@ -13335,7 +15225,7 @@
         <v>9</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>1482</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="322" spans="1:7" ht="84">
@@ -13358,7 +15248,7 @@
         <v>9</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>1483</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="323" spans="1:7" ht="84">
@@ -13381,7 +15271,7 @@
         <v>9</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>1484</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="324" spans="1:7" ht="84">
@@ -13404,7 +15294,7 @@
         <v>9</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1485</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="325" spans="1:7" ht="84">
@@ -13427,7 +15317,7 @@
         <v>9</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>1486</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="326" spans="1:7" ht="84">
@@ -13450,7 +15340,7 @@
         <v>9</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1487</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="327" spans="1:7" ht="84">
@@ -13473,7 +15363,7 @@
         <v>9</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>1488</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="328" spans="1:7" ht="84">
@@ -13496,7 +15386,7 @@
         <v>9</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>1489</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="329" spans="1:7" ht="84">
@@ -13519,7 +15409,7 @@
         <v>9</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>1490</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="330" spans="1:7" ht="84">
@@ -13542,7 +15432,7 @@
         <v>9</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>1491</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="331" spans="1:7" ht="84">
@@ -13565,7 +15455,7 @@
         <v>9</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>1492</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="332" spans="1:7" ht="84">
@@ -13588,7 +15478,7 @@
         <v>9</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>1493</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="333" spans="1:7" ht="84">
@@ -13611,7 +15501,7 @@
         <v>9</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>1494</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="334" spans="1:7" ht="84">
@@ -13634,7 +15524,7 @@
         <v>9</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>1495</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="335" spans="1:7" ht="84">
@@ -13657,7 +15547,7 @@
         <v>9</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>1496</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="336" spans="1:7" ht="84">
@@ -13680,7 +15570,7 @@
         <v>9</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>1497</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="337" spans="1:7" ht="84">
@@ -13703,7 +15593,7 @@
         <v>9</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>1498</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="338" spans="1:7" ht="84">
@@ -13726,7 +15616,7 @@
         <v>9</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1499</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="339" spans="1:7" ht="84">
@@ -13749,7 +15639,7 @@
         <v>9</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>1500</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="340" spans="1:7" ht="84">
@@ -13772,7 +15662,7 @@
         <v>9</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>1501</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="341" spans="1:7" ht="84">
@@ -13795,7 +15685,7 @@
         <v>9</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>1502</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="342" spans="1:7" ht="84">
@@ -13818,7 +15708,7 @@
         <v>9</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1503</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="343" spans="1:7" ht="84">
@@ -13841,7 +15731,7 @@
         <v>9</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>1504</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="344" spans="1:7" ht="84">
@@ -13864,7 +15754,7 @@
         <v>9</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>1505</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="345" spans="1:7" ht="84">
@@ -13887,7 +15777,7 @@
         <v>9</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1506</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="346" spans="1:7" ht="84">
@@ -13910,7 +15800,7 @@
         <v>9</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>1507</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="347" spans="1:7" ht="84">
@@ -13933,7 +15823,7 @@
         <v>9</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>1508</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="348" spans="1:7" ht="84">
@@ -13956,7 +15846,7 @@
         <v>9</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>1509</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="349" spans="1:7" ht="84">
@@ -13979,7 +15869,7 @@
         <v>9</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>1510</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="350" spans="1:7" ht="84">
@@ -14002,7 +15892,7 @@
         <v>9</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>1511</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="351" spans="1:7" ht="84">
@@ -14025,7 +15915,7 @@
         <v>9</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>1512</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="352" spans="1:7" ht="84">
@@ -14048,7 +15938,7 @@
         <v>9</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1513</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="353" spans="1:7" ht="84">
@@ -14071,7 +15961,7 @@
         <v>9</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>1514</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="354" spans="1:7" ht="84">
@@ -14094,7 +15984,7 @@
         <v>9</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>1515</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="355" spans="1:7" ht="84">
@@ -14117,7 +16007,7 @@
         <v>9</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>1516</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="356" spans="1:7" ht="84">
@@ -14140,7 +16030,7 @@
         <v>9</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>1517</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="357" spans="1:7" ht="84">
@@ -14163,7 +16053,7 @@
         <v>9</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>1518</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="358" spans="1:7" ht="84">
@@ -14186,7 +16076,7 @@
         <v>9</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>1519</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="359" spans="1:7" ht="84">
@@ -14209,7 +16099,7 @@
         <v>9</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>1520</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="360" spans="1:7" ht="84">
@@ -14232,7 +16122,7 @@
         <v>9</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>1521</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="361" spans="1:7" ht="84">
@@ -14255,7 +16145,7 @@
         <v>9</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>1522</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="362" spans="1:7" ht="105">
@@ -14278,7 +16168,7 @@
         <v>9</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>1523</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="363" spans="1:7" ht="84">
@@ -14301,7 +16191,7 @@
         <v>9</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>1524</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="364" spans="1:7" ht="84">
@@ -14324,7 +16214,7 @@
         <v>9</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>1525</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="365" spans="1:7" ht="105">
@@ -14347,7 +16237,7 @@
         <v>9</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>1526</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="366" spans="1:7" ht="84">
@@ -14358,11 +16248,12 @@
         <v>256</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>1527</v>
+        <v>1357</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>